--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,6 +99,10 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -169,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -226,6 +230,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -591,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1450,6 +1457,49 @@
       <c r="B103" t="inlineStr">
         <is>
           <t>Backlog</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Sprint 21 -- My Work - task management</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>MyWork.js, Tasks.js, lib/taskAccess.js, routers/tasks.py, routers/desk.py, services/tasks.py, services/finance_signals.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Founder plan 2026-09-14: everyone sees the work they are part of, clear people and stages on a task, approval as a step, access rules, and stuck work that climbs to the manager before the owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>In progress -- 13 of 15 Done; open: Flutter app parity, separate test database</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1493,7 +1543,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 64 of 153 items Done  (42%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.</t>
+          <t>Epic 6 progress: 64 of 153 items Done  (42%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 13 of 15 Done.</t>
         </is>
       </c>
     </row>
@@ -2191,6 +2241,39 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>See 'UI Redesign Log' sheet — 105 karma / RD / NM / MPWA UI commits, all shipped to Backend_optimization. Sprint 19 carries the KM-* / KR-14.2-24 mobile pass entries in Backlog to keep the totals clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sprint 21</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>My Work - task management</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Task management plan (docs/TASK_MANAGEMENT_PLAN.md), ASK-28 + ASK-29, 2026-09-14/15: New Task form, Asked by me / Waiting for my approval / My team views, links that land, approval moment, who is on a task, stages and flags, task access, who may change a task, stuck work reaches the manager first. Open: Flutter app, separate test database.</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4983,6 +5066,303 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>9b88efc</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>ASK-29 - New Task form: what, department, who, when; the rest under More options</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>72e0598</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-01 - Asked by me view</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>b1c9daf</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-02 - Waiting for my approval (Approvals view + Desk card)</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>8eac435</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-03 - My team for managers</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>ae6675d</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-05 - approval before work starts or before it is marked done</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>564732d</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-04 - task links always land; every view is an address</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>009bd2d</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 - phone pass, approver check, real-save journeys, old audit scripts made safe</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>93686c2</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-06 - who is on a task: Doer, Helpers, Asked by, Approver</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>abe4b40</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-07 - stages and flags: To do / Doing / Done, Waiting on someone</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>b2ae273</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-08 - task access: who may assign, who sees all tasks</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>92c3d0f</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>ASK-28 item 7 + Phase 7 - who may change a task; stuck work reaches the manager first</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4994,7 +5374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:L196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15251,6 +15631,846 @@
       <c r="L181" t="inlineStr">
         <is>
           <t>Epic 3 (moved 2026-09-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.1</t>
+        </is>
+      </c>
+      <c r="B182" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, Tasks.js (NewTaskDialog)</t>
+        </is>
+      </c>
+      <c r="C182" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D182" s="28" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="E182" s="28" t="inlineStr">
+        <is>
+          <t>New Task form -- what, department, who, when; the rest under More options</t>
+        </is>
+      </c>
+      <c r="F182" s="28" t="inlineStr">
+        <is>
+          <t>ASK-29 / plan Phase 5. Quick add: title with an inline error, Department, one Assign to (a person, or a team routed to its least busy member), due presets No date / Today / Tomorrow / In a week / Pick a date. More options: priority, helpers, description, due time, expected result, approval + approver + when, proof, reference files. Operational category and Supporting employee dropped from the form. Due Today no longer reads Overdue the same morning.</t>
+        </is>
+      </c>
+      <c r="G182" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H182" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I182" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J182" s="28" t="n"/>
+      <c r="K182" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 9b88efc (2026-09-14). Glass pass 0eaa411 moved it onto GlassSelect. Acceptance ux_newtask_form_0914.py re-run green through TK-08.</t>
+        </is>
+      </c>
+      <c r="L182" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.2</t>
+        </is>
+      </c>
+      <c r="B183" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, services/tasks.py</t>
+        </is>
+      </c>
+      <c r="C183" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D183" s="28" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E183" s="28" t="inlineStr">
+        <is>
+          <t>Asked by me -- see the work you handed to other people</t>
+        </is>
+      </c>
+      <c r="F183" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-01 / plan 1.1. GET /tasks?view=asked (tasks I created that are not mine to do) + an Asked by me view in the switcher, kept in ?view=, with Department / Person / Status filters and its own empty state. The person who asked may leave a note.</t>
+        </is>
+      </c>
+      <c r="G183" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H183" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I183" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J183" s="28" t="n"/>
+      <c r="K183" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 72e0598 (2026-09-14). Real-save journey test_asked_by_me_non_owner_keeps_sight_of_work_they_hand_out; browser 20/20 writes blocked.</t>
+        </is>
+      </c>
+      <c r="L183" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.3</t>
+        </is>
+      </c>
+      <c r="B184" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, Desk.js, services/tasks.py</t>
+        </is>
+      </c>
+      <c r="C184" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D184" s="28" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E184" s="28" t="inlineStr">
+        <is>
+          <t>Waiting for my approval -- every approver sees what waits on them</t>
+        </is>
+      </c>
+      <c r="F184" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-02 / plan 1.2 + 1.5. GET /tasks?view=approvals (the owner all; a named approver their own; an approvals holder also the unnamed ones). Feeds the Approvals view in My Work (with its count) and the Decision Desk Task approvals card. Approval notifications open the task in Approvals.</t>
+        </is>
+      </c>
+      <c r="G184" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H184" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I184" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J184" s="28" t="n"/>
+      <c r="K184" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED b1c9daf (2026-09-14). Real-save journey with a non-owner named approver; browser checks owner 7/7 vs API.</t>
+        </is>
+      </c>
+      <c r="L184" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.4</t>
+        </is>
+      </c>
+      <c r="B185" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, services/tasks.py</t>
+        </is>
+      </c>
+      <c r="C185" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D185" s="28" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="E185" s="28" t="inlineStr">
+        <is>
+          <t>My team -- a manager sees the work of the people who report to them</t>
+        </is>
+      </c>
+      <c r="F185" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-03 / plan 1.3 (D3). GET /tasks?view=team through the Reporting Manager field (direct reports, as doer or helper). Shown to a non-owner with reports; the owner keeps All Tasks. The manager opens a report's task, its activity, and notes on it.</t>
+        </is>
+      </c>
+      <c r="G185" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H185" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I185" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J185" s="28" t="n"/>
+      <c r="K185" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 8eac435 (2026-09-14). Real data (Sunita Rao manages sai) 21/21 writes blocked; real-save journey test_my_team_manager_sees_opens_and_notes_on_reports_work.</t>
+        </is>
+      </c>
+      <c r="L185" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.5</t>
+        </is>
+      </c>
+      <c r="B186" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js</t>
+        </is>
+      </c>
+      <c r="C186" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D186" s="28" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="E186" s="28" t="inlineStr">
+        <is>
+          <t>Links always land -- a task link opens its task, and every view is an address</t>
+        </is>
+      </c>
+      <c r="F186" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-04 / plan 1.4. /my-work?task=&lt;id&gt; (and ?focus=task:&lt;id&gt;) opens the drawer whatever the view, from the single-task request when the task is not in the list; missing and refused tasks say so. Every view lives in ?view= and survives refresh, Back and Forward.</t>
+        </is>
+      </c>
+      <c r="G186" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H186" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I186" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J186" s="28" t="n"/>
+      <c r="K186" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 564732d + tracker 7aa4031 (2026-09-14). Acceptance ux_task_links_0914.py 23/23 on real data, writes blocked.</t>
+        </is>
+      </c>
+      <c r="L186" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.6</t>
+        </is>
+      </c>
+      <c r="B187" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, routers/tasks.py</t>
+        </is>
+      </c>
+      <c r="C187" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D187" s="28" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="E187" s="28" t="inlineStr">
+        <is>
+          <t>Approval moment -- before work starts, or before it is marked done</t>
+        </is>
+      </c>
+      <c r="F187" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-05 / plan Phase 4 (D2). The creator picks per task. Before closing: Complete sends it to the approver (Under review), Approve closes it, Request changes returns it with the reason. The server checks the named approver can actually approve (4.3). Cards say Approval to start / Approval to close.</t>
+        </is>
+      </c>
+      <c r="G187" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H187" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I187" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J187" s="28" t="n"/>
+      <c r="K187" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED ae6675d; approver check in 009bd2d (2026-09-14). 17 unit tests; real-save journeys for both moments; browser 19/19.</t>
+        </is>
+      </c>
+      <c r="L187" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.7</t>
+        </is>
+      </c>
+      <c r="B188" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, Tasks.js (phone)</t>
+        </is>
+      </c>
+      <c r="C188" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D188" s="28" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E188" s="28" t="inlineStr">
+        <is>
+          <t>Phone pass -- New Task and every My Work view on a phone</t>
+        </is>
+      </c>
+      <c r="F188" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 / plan 5.4. New Task as a full-screen sheet with Create in reach; one view pill opening a sheet of the person's views (My Tasks, Asked by me, My team, All Tasks, Approvals with its count). Checked at 390x844. Later (8fbe532, Chinmay) the task itself opens full screen on a phone.</t>
+        </is>
+      </c>
+      <c r="G188" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H188" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I188" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J188" s="28" t="n"/>
+      <c r="K188" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 009bd2d (2026-09-14). ux_task_phone_0914.py 21/21, re-run green after the full-screen change.</t>
+        </is>
+      </c>
+      <c r="L188" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.8</t>
+        </is>
+      </c>
+      <c r="B189" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, routers/tasks.py, mobile/work_screen.dart</t>
+        </is>
+      </c>
+      <c r="C189" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D189" s="28" t="inlineStr">
+        <is>
+          <t>Data model</t>
+        </is>
+      </c>
+      <c r="E189" s="28" t="inlineStr">
+        <is>
+          <t>Who is on a task -- Doer, Helpers, Asked by, Approver</t>
+        </is>
+      </c>
+      <c r="F189" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-06 / plan Phase 2 (D4). Supporting employee removed everywhere (0 of 185 stored tasks used it). The drawer names who asked and who approves and when; team tasks say who they went to (fewest open tasks). Helpers hear status changes and overdue reminders.</t>
+        </is>
+      </c>
+      <c r="G189" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H189" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I189" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J189" s="28" t="n"/>
+      <c r="K189" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 93686c2 + tracker c365e38 (2026-09-14). 3 real-save journeys; browser check writes blocked.</t>
+        </is>
+      </c>
+      <c r="L189" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.9</t>
+        </is>
+      </c>
+      <c r="B190" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, services/tasks.py + counts</t>
+        </is>
+      </c>
+      <c r="C190" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D190" s="28" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E190" s="28" t="inlineStr">
+        <is>
+          <t>Stages and flags -- To do / Doing / Done, Waiting on someone</t>
+        </is>
+      </c>
+      <c r="F190" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-07 / plan Phase 3 (D6). Screens show three stages; stored statuses unchanged (no migration). Waiting on a colleague or a typed name, with since when; the colleague is told and can answer with a note. Status filter To do / Doing / Waiting on someone / Needs approval / Overdue / Due today / Done. Operating Score, calendar, dashboard, Brief, prioritisation and leave impact count waiting and review as open work.</t>
+        </is>
+      </c>
+      <c r="G190" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H190" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I190" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J190" s="28" t="n"/>
+      <c r="K190" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED abe4b40 (2026-09-14). 10 unit tests, 2 real-save journeys, browser 13/13. Dex counts handed to Yokesh (agent_tools.py, brain.py), not changed here.</t>
+        </is>
+      </c>
+      <c r="L190" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.10</t>
+        </is>
+      </c>
+      <c r="B191" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, lib/taskAccess.js, routers/tasks.py</t>
+        </is>
+      </c>
+      <c r="C191" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D191" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E191" s="28" t="inlineStr">
+        <is>
+          <t>Task access -- who may assign, who sees all tasks</t>
+        </is>
+      </c>
+      <c r="F191" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 TK-08 / plan 6.1-6.6 (D1). New permissions Assign tasks to anyone and See all tasks, off for every role (finance included). Without the first, work goes to yourself, your team or your reports -- on create, change and reassign, and the pickers list only those. All Tasks for the owner and See all tasks holders. Creating needs the Tasks permission. /auth/me sends effective_permissions.</t>
+        </is>
+      </c>
+      <c r="G191" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H191" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I191" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J191" s="28" t="n"/>
+      <c r="K191" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED b2ae273 (2026-09-14). Browser 49/49 across 4 roles desktop + phone; 7 unit tests; real-save journeys for every refusal.</t>
+        </is>
+      </c>
+      <c r="L191" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.11</t>
+        </is>
+      </c>
+      <c r="B192" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js, lib/taskAccess.js, routers/tasks.py</t>
+        </is>
+      </c>
+      <c r="C192" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D192" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E192" s="28" t="inlineStr">
+        <is>
+          <t>Who may change a task -- the people who run it, not the whole company</t>
+        </is>
+      </c>
+      <c r="F192" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 item 7 / plan 6.7. PATCH /tasks/{id} was open to any member. Now: stage / progress / waiting -- doer, helpers, asker, manager, owner; done / cancel / reopen -- the same minus helpers; people -- asker, manager, Manage Team, owner; priority -- asker, manager, owner; needs proof -- asker and owner. See all tasks, the approver and a colleague waited on leave notes. Drawer and bulk Complete / Reassign follow it.</t>
+        </is>
+      </c>
+      <c r="G192" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H192" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I192" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J192" s="28" t="n"/>
+      <c r="K192" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 92c3d0f (2026-09-15). Browser 96/96 per relationship desktop + phone; 6 unit tests; real-save journey test_who_may_change_a_task.</t>
+        </is>
+      </c>
+      <c r="L192" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.12</t>
+        </is>
+      </c>
+      <c r="B193" s="28" t="inlineStr">
+        <is>
+          <t>finance_signals.py, routers/desk.py, MyWork.js</t>
+        </is>
+      </c>
+      <c r="C193" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D193" s="28" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="E193" s="28" t="inlineStr">
+        <is>
+          <t>Stuck work reaches the manager first -- reminders, Escalate, Desk Slipping</t>
+        </is>
+      </c>
+      <c r="F193" s="28" t="inlineStr">
+        <is>
+          <t>ASK-28 plan Phase 7 (D7). Overdue: the people who can move it (the approver for approval, the colleague waited on); 1 day: again; 2 days: the doer's reporting manager (the owner only without one); 4 days: owner alert (was 3). Escalate goes to your manager first. Desk Slipping shows a manager their reports' work from 2 days, and now shows escalations at all (it read the wrong field names).</t>
+        </is>
+      </c>
+      <c r="G193" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H193" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I193" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J193" s="28" t="n"/>
+      <c r="K193" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 92c3d0f (2026-09-15). 4 unit tests + ladder test updated; real-save journey test_stuck_work_reaches_the_right_person; Escalate browser 15/15; Desk probe 4/4 read-only on real data. Goes live when the backend is restarted or deployed.</t>
+        </is>
+      </c>
+      <c r="L193" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.13</t>
+        </is>
+      </c>
+      <c r="B194" s="28" t="inlineStr">
+        <is>
+          <t>backend/tests, backend/scripts</t>
+        </is>
+      </c>
+      <c r="C194" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D194" s="28" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="E194" s="28" t="inlineStr">
+        <is>
+          <t>Safe testing -- real saves in an isolated database, browser checks with writes blocked</t>
+        </is>
+      </c>
+      <c r="F194" s="28" t="inlineStr">
+        <is>
+          <t>The local database is production, so every browser acceptance script aborts POST/PATCH/PUT/DELETE after sign-in, and real saves run in tests/test_task_management_e2e.py against a throwaway with_test_db. The two old My Work audit scripts that created real tasks now refuse to run without UX_ALLOW_WRITES=1.</t>
+        </is>
+      </c>
+      <c r="G194" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H194" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I194" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J194" s="28" t="n"/>
+      <c r="K194" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 009bd2d and with each phase (2026-09-14/15). Full suite 1452 passed at 92c3d0f.</t>
+        </is>
+      </c>
+      <c r="L194" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.14</t>
+        </is>
+      </c>
+      <c r="B195" s="28" t="inlineStr">
+        <is>
+          <t>mobile/ (Flutter)</t>
+        </is>
+      </c>
+      <c r="C195" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D195" s="28" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E195" s="28" t="inlineStr">
+        <is>
+          <t>Flutter app catches up with the task changes</t>
+        </is>
+      </c>
+      <c r="F195" s="28" t="inlineStr">
+        <is>
+          <t>The Flutter app still shows stored status words (not To do / Doing / Done), still offers Complete to helpers (the server refuses with the reason), and its Escalate does not say it goes to the manager. It keeps working because nothing stored changed.</t>
+        </is>
+      </c>
+      <c r="G195" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H195" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I195" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J195" s="28" t="n"/>
+      <c r="K195" s="28" t="inlineStr">
+        <is>
+          <t>Open follow-up from the task management plan (plan 0.5).</t>
+        </is>
+      </c>
+      <c r="L195" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.15</t>
+        </is>
+      </c>
+      <c r="B196" s="28" t="inlineStr">
+        <is>
+          <t>backend/.env, test setup</t>
+        </is>
+      </c>
+      <c r="C196" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D196" s="28" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="E196" s="28" t="inlineStr">
+        <is>
+          <t>Separate the local database from production</t>
+        </is>
+      </c>
+      <c r="F196" s="28" t="inlineStr">
+        <is>
+          <t>Local MONGO_URL points at production, so real-click testing is impossible and the local backend cannot be restarted with new reminder rules without messaging real people. A separate test database unblocks both.</t>
+        </is>
+      </c>
+      <c r="G196" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H196" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I196" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J196" s="28" t="n"/>
+      <c r="K196" s="28" t="inlineStr">
+        <is>
+          <t>Open follow-up from the task management plan (plan 0.1).</t>
+        </is>
+      </c>
+      <c r="L196" s="28" t="inlineStr">
+        <is>
+          <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1500,6 +1500,49 @@
       <c r="B108" t="inlineStr">
         <is>
           <t>In progress -- 13 of 15 Done; open: Flutter app parity, separate test database</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Sprint 22 -- Decision Desk - decision flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>services/voice.py, services/decision_flow.py, routers/decisions.py, routers/voice_notes.py, routers/desk.py, DecisionDialog.js, Dex hooks and phone Dex, MyWork.js, Workflows.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Dex created work before anyone approved, duplicated workflows, sent every decision to the owner, and the decision screen showed only a reference of what would happen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>In progress -- 12 of 13 Done; open: Phase 5 capture feedback</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1543,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 64 of 153 items Done  (42%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 13 of 15 Done.</t>
+          <t>Epic 6 progress: 64 of 153 items Done  (42%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 13 of 15 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 12 of 13 Done.</t>
         </is>
       </c>
     </row>
@@ -2274,6 +2317,39 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>Task management plan (docs/TASK_MANAGEMENT_PLAN.md), ASK-28 + ASK-29, 2026-09-14/15: New Task form, Asked by me / Waiting for my approval / My team views, links that land, approval moment, who is on a task, stages and flags, task access, who may change a task, stuck work reaches the manager first. Open: Flutter app, separate test database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sprint 22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Decision Desk - decision flow</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12</v>
+      </c>
+      <c r="D27" t="n">
+        <v>13</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves. Open: Phase 5 (capture feedback on desktop, retry, My captures).</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5363,6 +5439,87 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>Decision Desk decision flow</t>
+        </is>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 1 - nothing created until a decision is approved; phone Dex fixes</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>Decision Desk decision flow</t>
+        </is>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 2 - who decides and who is told</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>Decision Desk decision flow</t>
+        </is>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>ASK-32 Phases 3-4 - simple decision screen with edits; workflows matched and moved by themselves</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5374,7 +5531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L196"/>
+  <dimension ref="A1:L209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16471,6 +16628,734 @@
       <c r="L196" s="28" t="inlineStr">
         <is>
           <t>Founder ask 2026-09-14 (docs/TASK_MANAGEMENT_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.1</t>
+        </is>
+      </c>
+      <c r="B197" s="28" t="inlineStr">
+        <is>
+          <t>services/voice.py, decision_flow.py, DecisionDialog.js</t>
+        </is>
+      </c>
+      <c r="C197" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D197" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E197" s="28" t="inlineStr">
+        <is>
+          <t>Nothing is created until a decision is approved</t>
+        </is>
+      </c>
+      <c r="F197" s="28" t="inlineStr">
+        <is>
+          <t>Phase 1.1. A Dex capture stores a proposal (tasks with who and when, workflows, meetings, reminders, notes) on the waiting decision; approving creates it all.</t>
+        </is>
+      </c>
+      <c r="G197" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H197" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I197" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J197" s="28" t="n"/>
+      <c r="K197" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 1. Real-save journeys + browser checks in a throwaway database.</t>
+        </is>
+      </c>
+      <c r="L197" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.2</t>
+        </is>
+      </c>
+      <c r="B198" s="28" t="inlineStr">
+        <is>
+          <t>routers/decisions.py, routers/tasks.py, MyWork.js</t>
+        </is>
+      </c>
+      <c r="C198" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D198" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E198" s="28" t="inlineStr">
+        <is>
+          <t>Approve / reject guards and locked older tasks</t>
+        </is>
+      </c>
+      <c r="F198" s="28" t="inlineStr">
+        <is>
+          <t>Phase 1.2-1.3. Only while undecided, only by the named approver or an owner; reject creates nothing and never deletes work under way; tasks of an older undecided decision cannot start.</t>
+        </is>
+      </c>
+      <c r="G198" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H198" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I198" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J198" s="28" t="n"/>
+      <c r="K198" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 1.</t>
+        </is>
+      </c>
+      <c r="L198" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.3</t>
+        </is>
+      </c>
+      <c r="B199" s="28" t="inlineStr">
+        <is>
+          <t>services/voice.py, useDexConversation.js</t>
+        </is>
+      </c>
+      <c r="C199" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D199" s="28" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="E199" s="28" t="inlineStr">
+        <is>
+          <t>No decision for questions; repeats flagged; failures say why</t>
+        </is>
+      </c>
+      <c r="F199" s="28" t="inlineStr">
+        <is>
+          <t>Phase 1.4-1.5. A capture with nothing to act on makes no decision; the same capture within a day is marked Possible repeat; a failed capture explains why.</t>
+        </is>
+      </c>
+      <c r="G199" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H199" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I199" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J199" s="28" t="n"/>
+      <c r="K199" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 1.</t>
+        </is>
+      </c>
+      <c r="L199" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.4</t>
+        </is>
+      </c>
+      <c r="B200" s="28" t="inlineStr">
+        <is>
+          <t>useDexCapture.js, DexChat.jsx, DexFab.jsx, DexStage.jsx</t>
+        </is>
+      </c>
+      <c r="C200" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D200" s="28" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E200" s="28" t="inlineStr">
+        <is>
+          <t>Phone Dex: one spoken decision, Attach, first-tap Send</t>
+        </is>
+      </c>
+      <c r="F200" s="28" t="inlineStr">
+        <is>
+          <t>Phase 1.6. A recording is held for review and sent once (was two decisions); Attach and Photo files are read with the decision; the Send tap after a recording works first time; /brain keeps an attached file for the next note.</t>
+        </is>
+      </c>
+      <c r="G200" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H200" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I200" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J200" s="28" t="n"/>
+      <c r="K200" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 1.</t>
+        </is>
+      </c>
+      <c r="L200" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.5</t>
+        </is>
+      </c>
+      <c r="B201" s="28" t="inlineStr">
+        <is>
+          <t>notif.js, services/captures.py, routers/dex.py, routers/desk.py</t>
+        </is>
+      </c>
+      <c r="C201" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D201" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E201" s="28" t="inlineStr">
+        <is>
+          <t>Notification opens the decision; WhatsApp approve; capture permission; Desk order</t>
+        </is>
+      </c>
+      <c r="F201" s="28" t="inlineStr">
+        <is>
+          <t>Phase 1.7-1.9. Decision notifications open the decision; WhatsApp capture approval uses the same path; /dex/capture checks voice capture; Desk decisions oldest first.</t>
+        </is>
+      </c>
+      <c r="G201" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H201" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I201" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J201" s="28" t="n"/>
+      <c r="K201" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 1.</t>
+        </is>
+      </c>
+      <c r="L201" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.6</t>
+        </is>
+      </c>
+      <c r="B202" s="28" t="inlineStr">
+        <is>
+          <t>services/decision_flow.py, services/voice.py</t>
+        </is>
+      </c>
+      <c r="C202" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D202" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E202" s="28" t="inlineStr">
+        <is>
+          <t>Every decision names who decides</t>
+        </is>
+      </c>
+      <c r="F202" s="28" t="inlineStr">
+        <is>
+          <t>Phase 2.1-2.2. The capturer when they may approve, else their reporting manager, else the owner; one permission (decisions_approve) routes and approves; older waiting decisions backfilled by a migration.</t>
+        </is>
+      </c>
+      <c r="G202" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H202" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I202" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J202" s="28" t="n"/>
+      <c r="K202" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 2.</t>
+        </is>
+      </c>
+      <c r="L202" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.7</t>
+        </is>
+      </c>
+      <c r="B203" s="28" t="inlineStr">
+        <is>
+          <t>services/decision_flow.py, routers/desk.py, DecisionDialog.js</t>
+        </is>
+      </c>
+      <c r="C203" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D203" s="28" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="E203" s="28" t="inlineStr">
+        <is>
+          <t>The right people are told; the capturer follows it</t>
+        </is>
+      </c>
+      <c r="F203" s="28" t="inlineStr">
+        <is>
+          <t>Phase 2.3-2.4. The decider is told when a decision arrives; approval tells the assignees and the capturer; rejection tells the capturer; the capturer sees Waiting on Sunita on the Desk (not counted) and no Approve button.</t>
+        </is>
+      </c>
+      <c r="G203" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H203" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I203" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J203" s="28" t="n"/>
+      <c r="K203" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 2.</t>
+        </is>
+      </c>
+      <c r="L203" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.8</t>
+        </is>
+      </c>
+      <c r="B204" s="28" t="inlineStr">
+        <is>
+          <t>routers/decisions.py, DecisionDialog.js</t>
+        </is>
+      </c>
+      <c r="C204" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D204" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E204" s="28" t="inlineStr">
+        <is>
+          <t>Change who decides</t>
+        </is>
+      </c>
+      <c r="F204" s="28" t="inlineStr">
+        <is>
+          <t>Phase 2.5. An owner or the person it waits on hands it to someone who may approve; timeline and notification.</t>
+        </is>
+      </c>
+      <c r="G204" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H204" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I204" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J204" s="28" t="n"/>
+      <c r="K204" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 2.</t>
+        </is>
+      </c>
+      <c r="L204" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.9</t>
+        </is>
+      </c>
+      <c r="B205" s="28" t="inlineStr">
+        <is>
+          <t>DecisionDialog.js, routers/voice_notes.py, services/enrich.py</t>
+        </is>
+      </c>
+      <c r="C205" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D205" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E205" s="28" t="inlineStr">
+        <is>
+          <t>Decision screen: what was said, plain work rows</t>
+        </is>
+      </c>
+      <c r="F205" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3.1-3.2. The words (voice note with play, typed, WhatsApp), files sent with it; tasks shown like normal tasks with Part of &lt;workflow&gt;; no AI or confidence labels.</t>
+        </is>
+      </c>
+      <c r="G205" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H205" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I205" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J205" s="28" t="n"/>
+      <c r="K205" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 3.</t>
+        </is>
+      </c>
+      <c r="L205" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.10</t>
+        </is>
+      </c>
+      <c r="B206" s="28" t="inlineStr">
+        <is>
+          <t>DecisionDialog.js, routers/decisions.py, services/decision_flow.py</t>
+        </is>
+      </c>
+      <c r="C206" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D206" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E206" s="28" t="inlineStr">
+        <is>
+          <t>Change the work before approving</t>
+        </is>
+      </c>
+      <c r="F206" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3.3-3.4. Pick who does a task (unmatched names ask Pick who does this), change the due date, remove a task / workflow / meeting / reminder / note; after approving the popup links to what was made.</t>
+        </is>
+      </c>
+      <c r="G206" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H206" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I206" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J206" s="28" t="n"/>
+      <c r="K206" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 3.</t>
+        </is>
+      </c>
+      <c r="L206" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.11</t>
+        </is>
+      </c>
+      <c r="B207" s="28" t="inlineStr">
+        <is>
+          <t>services/voice.py, services/decision_flow.py</t>
+        </is>
+      </c>
+      <c r="C207" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D207" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E207" s="28" t="inlineStr">
+        <is>
+          <t>Existing workflows matched; tasks join their workflow</t>
+        </is>
+      </c>
+      <c r="F207" s="28" t="inlineStr">
+        <is>
+          <t>Phase 4.1-4.2. Proposals use the open card on the board for the same customer/supplier (moving it to a named stage) instead of duplicating; tasks naming a customer/supplier join that workflow; other tasks stay plain.</t>
+        </is>
+      </c>
+      <c r="G207" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H207" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I207" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J207" s="28" t="n"/>
+      <c r="K207" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 4.</t>
+        </is>
+      </c>
+      <c r="L207" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.12</t>
+        </is>
+      </c>
+      <c r="B208" s="28" t="inlineStr">
+        <is>
+          <t>services/decision_flow.py, MyWork.js, Workflows.js, agent_tools.py</t>
+        </is>
+      </c>
+      <c r="C208" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D208" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E208" s="28" t="inlineStr">
+        <is>
+          <t>Workflows move by themselves; links both ways; Dex chat proposals</t>
+        </is>
+      </c>
+      <c r="F208" s="28" t="inlineStr">
+        <is>
+          <t>Phase 4.3-4.5. On approval new workflows fire their first-stage automation, named cards move, workflows before their approval stage move into it for every pipeline and for managers; task drawer and workflow card link to the decision; Dex chat proposals create nothing until approved.</t>
+        </is>
+      </c>
+      <c r="G208" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H208" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I208" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J208" s="28" t="n"/>
+      <c r="K208" s="28" t="inlineStr">
+        <is>
+          <t>ASK-32 Phase 4.</t>
+        </is>
+      </c>
+      <c r="L208" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.13</t>
+        </is>
+      </c>
+      <c r="B209" s="28" t="inlineStr">
+        <is>
+          <t>DecisionDialog.js, useDexCapture.js</t>
+        </is>
+      </c>
+      <c r="C209" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D209" s="28" t="inlineStr">
+        <is>
+          <t>Dex</t>
+        </is>
+      </c>
+      <c r="E209" s="28" t="inlineStr">
+        <is>
+          <t>Result after capture on desktop, failure retry, My captures list</t>
+        </is>
+      </c>
+      <c r="F209" s="28" t="inlineStr">
+        <is>
+          <t>Phase 5.1-5.3 (to ideate): the desktop Dex page shows what Dex made after a capture; a failed capture offers Retry; a list of past captures.</t>
+        </is>
+      </c>
+      <c r="G209" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H209" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I209" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J209" s="28" t="n"/>
+      <c r="K209" s="28" t="inlineStr">
+        <is>
+          <t>Open from docs/DECISION_DESK_PLAN.md Phase 5.</t>
+        </is>
+      </c>
+      <c r="L209" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2299,14 +2299,14 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Task management plan (docs/TASK_MANAGEMENT_PLAN.md), ASK-28 + ASK-29, 2026-09-14/15: New Task form, Asked by me / Waiting for my approval / My team views, links that land, approval moment, who is on a task, stages and flags, task access, who may change a task, stuck work reaches the manager first. Open: Flutter app, separate test database.</t>
+          <t>Task management plan (docs/TASK_MANAGEMENT_PLAN.md), ASK-28 + ASK-29, 2026-09-14/15: New Task form, Asked by me / Waiting for my approval / My team views, links that land, approval moment, who is on a task, stages and flags, task access, who may change a task, stuck work reaches the manager first, proof stays once work is completed. Open: Flutter app, separate test database.</t>
         </is>
       </c>
     </row>
@@ -2335,11 +2335,11 @@
         <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves. Open: Phase 5 (capture feedback on desktop, retry, My captures).</t>
+          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves. Open: sign-off before done on decision tasks (3.5, another team), Phase 5 (capture feedback on desktop, retry, My captures).</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>(this push)</t>
+          <t>9dcb046</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>(this push)</t>
+          <t>9dcb046</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
@@ -5501,20 +5501,47 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
+          <t>9dcb046</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>ASK-32 Phases 3-4 - simple decision screen with edits; workflows matched and moved by themselves</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
           <t>(this push)</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="C120" s="7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>ASK-32 Phases 3-4 - simple decision screen with edits; workflows matched and moved by themselves</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Proof stays once the work is completed (done or sent for sign-off); reopen to change it</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5531,7 +5558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17354,6 +17381,118 @@
         </is>
       </c>
       <c r="L209" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="28" t="inlineStr">
+        <is>
+          <t>U7-21.16</t>
+        </is>
+      </c>
+      <c r="B210" s="28" t="inlineStr">
+        <is>
+          <t>routers/tasks.py, MyWork.js</t>
+        </is>
+      </c>
+      <c r="C210" s="28" t="n">
+        <v>21</v>
+      </c>
+      <c r="D210" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E210" s="28" t="inlineStr">
+        <is>
+          <t>Proof stays once the work is completed</t>
+        </is>
+      </c>
+      <c r="F210" s="28" t="inlineStr">
+        <is>
+          <t>Removing an attachment (DELETE /tasks/{id}/attachments/{att_id}, added in bb0a9e8) let the uploader, the creator or the owner remove proof at any time, so a closed task could lose its evidence. Now nobody, the owner included, removes proof while the task is done or sent for sign-off; reopen the task to change it. Reference material stays removable. My Work hides the remove button in the same cases.</t>
+        </is>
+      </c>
+      <c r="G210" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H210" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I210" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J210" s="28" t="n"/>
+      <c r="K210" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-15). Real-save journey test_proof_stays_once_the_work_is_completed (open, sent for sign-off, done, reopened).</t>
+        </is>
+      </c>
+      <c r="L210" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.14</t>
+        </is>
+      </c>
+      <c r="B211" s="28" t="inlineStr">
+        <is>
+          <t>DecisionDialog.js, services/decision_flow.py, services/voice.py</t>
+        </is>
+      </c>
+      <c r="C211" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D211" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E211" s="28" t="inlineStr">
+        <is>
+          <t>Needs sign-off before done on decision tasks</t>
+        </is>
+      </c>
+      <c r="F211" s="28" t="inlineStr">
+        <is>
+          <t>Plan 3.5. One checkbox per task row on the decision screen (only for whoever decides). On approval the task needs sign-off before it closes, and the decision's approver signs off. Dex ticks it in advance for Finance tasks or amounts at or above the high-value threshold. No approval before start.</t>
+        </is>
+      </c>
+      <c r="G211" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H211" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I211" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J211" s="28" t="n"/>
+      <c r="K211" s="28" t="inlineStr">
+        <is>
+          <t>Planned in docs/DECISION_DESK_PLAN.md 3.5. Being built by another team (Yokesh 2026-09-15).</t>
+        </is>
+      </c>
+      <c r="L211" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2332,14 +2332,14 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves. Open: sign-off before done on decision tasks (3.5, another team), Phase 5 (capture feedback on desktop, retry, My captures).</t>
+          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves; Needs approval is task approvals only; the card says who raised it and who decides; test data cleared. Open: sign-off before done on decision tasks (3.5, another team), Phase 5 (capture feedback on desktop, retry, My captures).</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5528,20 +5528,47 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
+          <t>5dad142</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Proof stays once the work is completed (done or sent for sign-off); reopen to change it</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="7" t="inlineStr">
+        <is>
+          <t>Decision Desk decision flow</t>
+        </is>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
           <t>(this push)</t>
         </is>
       </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="C121" s="7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="D120" s="7" t="inlineStr">
-        <is>
-          <t>Proof stays once the work is completed (done or sent for sign-off); reopen to change it</t>
-        </is>
-      </c>
-      <c r="E120" s="7" t="inlineStr">
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Needs approval is task approvals only; decision card says who raised it and who decides</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5558,7 +5585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:L214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17493,6 +17520,174 @@
         </is>
       </c>
       <c r="L211" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.15</t>
+        </is>
+      </c>
+      <c r="B212" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js</t>
+        </is>
+      </c>
+      <c r="C212" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D212" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E212" s="28" t="inlineStr">
+        <is>
+          <t>Needs approval is task approvals only</t>
+        </is>
+      </c>
+      <c r="F212" s="28" t="inlineStr">
+        <is>
+          <t>My Work's Needs approval filter counted every blocked task, so 32 tasks waiting for a decision sat beside the 7 task approvals (39). Decisions are approved on the Desk only; the filter now lists task approvals (before start, sent back, sign-off). Decision-locked tasks stay in All tasks with Waiting for a decision and a link.</t>
+        </is>
+      </c>
+      <c r="G212" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H212" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I212" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J212" s="28" t="n"/>
+      <c r="K212" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-15).</t>
+        </is>
+      </c>
+      <c r="L212" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.16</t>
+        </is>
+      </c>
+      <c r="B213" s="28" t="inlineStr">
+        <is>
+          <t>routers/desk.py</t>
+        </is>
+      </c>
+      <c r="C213" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D213" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E213" s="28" t="inlineStr">
+        <is>
+          <t>Decision card says who raised it and who decides</t>
+        </is>
+      </c>
+      <c r="F213" s="28" t="inlineStr">
+        <is>
+          <t>Desk decision card: Raised by Priya · You decide · Waiting 13 days · Unblocks 2 tasks; the person following it sees Raised by you · Sunita decides.</t>
+        </is>
+      </c>
+      <c r="G213" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H213" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I213" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J213" s="28" t="n"/>
+      <c r="K213" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-15). test_decision_flow_e2e asserts both lines.</t>
+        </is>
+      </c>
+      <c r="L213" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.17</t>
+        </is>
+      </c>
+      <c r="B214" s="28" t="inlineStr">
+        <is>
+          <t>scripts/cleanup_test_data_0915.py</t>
+        </is>
+      </c>
+      <c r="C214" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D214" s="28" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E214" s="28" t="inlineStr">
+        <is>
+          <t>Old test tasks and empty decisions cleared</t>
+        </is>
+      </c>
+      <c r="F214" s="28" t="inlineStr">
+        <is>
+          <t>Sharma company (dev data): 60 test tasks, 22 decisions with nothing to act on, and their 62 notifications and 113 activity entries. Archived to cleanup_archive first; --restore puts a run back.</t>
+        </is>
+      </c>
+      <c r="G214" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H214" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I214" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J214" s="28" t="n"/>
+      <c r="K214" s="28" t="inlineStr">
+        <is>
+          <t>DONE (2026-09-15).</t>
+        </is>
+      </c>
+      <c r="L214" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2332,14 +2332,14 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves; Needs approval is task approvals only; the card says who raised it and who decides; test data cleared. Open: sign-off before done on decision tasks (3.5, another team), Phase 5 (capture feedback on desktop, retry, My captures).</t>
+          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves; Needs approval is task approvals only; the card says who raised it and who decides; test data cleared; every approval task names who approves (manager, else owner). Open: sign-off before done on decision tasks (3.5, another team), Phase 5 (capture feedback on desktop, retry, My captures).</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5555,20 +5555,47 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
+          <t>963e7d3</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Needs approval is task approvals only; decision card says who raised it and who decides</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>My Work task management</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
           <t>(this push)</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>Needs approval is task approvals only; decision card says who raised it and who decides</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Every approval task names who approves: the creator's manager, else the owner</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5585,7 +5612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L214"/>
+  <dimension ref="A1:L215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17688,6 +17715,62 @@
         </is>
       </c>
       <c r="L214" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="28" t="inlineStr">
+        <is>
+          <t>U7-22.18</t>
+        </is>
+      </c>
+      <c r="B215" s="28" t="inlineStr">
+        <is>
+          <t>routers/tasks.py, Tasks.js</t>
+        </is>
+      </c>
+      <c r="C215" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D215" s="28" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="E215" s="28" t="inlineStr">
+        <is>
+          <t>Every approval task names who approves</t>
+        </is>
+      </c>
+      <c r="F215" s="28" t="inlineStr">
+        <is>
+          <t>Needs approval with nobody picked: the creator's reporting manager when they may approve tasks, else the owner (an owner creating it approves it; with several owners the first). A picked approver wins. New Task shows the default in the Approver list instead of Anyone with approval access, so My approvals covers every task and only that person is told.</t>
+        </is>
+      </c>
+      <c r="G215" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H215" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I215" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J215" s="28" t="n"/>
+      <c r="K215" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-15). Real-save journey test_nobody_picked_the_manager_approves_else_the_owner.</t>
+        </is>
+      </c>
+      <c r="L215" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1557,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2353,6 +2353,39 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sprint 23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Settings, Team and access (RBAC)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only. Open: remove/deactivate member, manage access by role, then the P1/P2 list.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2364,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5582,20 +5615,47 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
+          <t>e92cba9</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Every approval task names who approves: the creator's manager, else the owner</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>Settings, Team and access</t>
+        </is>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
           <t>(this push)</t>
         </is>
       </c>
-      <c r="C122" s="7" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
-        <is>
-          <t>Every approval task names who approves: the creator's manager, else the owner</t>
-        </is>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>RBAC P0: capture approval, files and checklist rules, Manage team cannot raise access, Money card</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5612,7 +5672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L215"/>
+  <dimension ref="A1:L222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17773,6 +17833,398 @@
       <c r="L215" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-15 (docs/DECISION_DESK_PLAN.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.1</t>
+        </is>
+      </c>
+      <c r="B216" s="28" t="inlineStr">
+        <is>
+          <t>services/captures.py, routers/captures.py</t>
+        </is>
+      </c>
+      <c r="C216" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D216" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E216" s="28" t="inlineStr">
+        <is>
+          <t>Capture approval no longer approves a decision for someone who may not decide</t>
+        </is>
+      </c>
+      <c r="F216" s="28" t="inlineStr">
+        <is>
+          <t>Approving a WhatsApp capture needed only Approve tasks and then approved its decision, skipping the named decider and Approve decisions. Now it approves the decision only when the reviewer may decide it; otherwise the decision waits for the person it names, who is told.</t>
+        </is>
+      </c>
+      <c r="G216" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H216" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I216" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J216" s="28" t="n"/>
+      <c r="K216" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-15). Real-save journey test_capture_approver_who_cannot_decide_leaves_the_decision_waiting.</t>
+        </is>
+      </c>
+      <c r="L216" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/SETTINGS_RBAC_REVIEW.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.2</t>
+        </is>
+      </c>
+      <c r="B217" s="28" t="inlineStr">
+        <is>
+          <t>routers/tasks.py</t>
+        </is>
+      </c>
+      <c r="C217" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D217" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E217" s="28" t="inlineStr">
+        <is>
+          <t>Only the people on a task add files to it</t>
+        </is>
+      </c>
+      <c r="F217" s="28" t="inlineStr">
+        <is>
+          <t>POST /tasks/{id}/attachments had no access check: any member could attach proof to any task. Now the people who may work it (doer, helpers, the person who asked, their manager, owner).</t>
+        </is>
+      </c>
+      <c r="G217" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H217" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I217" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J217" s="28" t="n"/>
+      <c r="K217" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-15). test_files_and_checklist_follow_the_task_rules.</t>
+        </is>
+      </c>
+      <c r="L217" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/SETTINGS_RBAC_REVIEW.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.3</t>
+        </is>
+      </c>
+      <c r="B218" s="28" t="inlineStr">
+        <is>
+          <t>routers/tasks.py</t>
+        </is>
+      </c>
+      <c r="C218" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D218" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E218" s="28" t="inlineStr">
+        <is>
+          <t>The checklist follows the task's rules</t>
+        </is>
+      </c>
+      <c r="F218" s="28" t="inlineStr">
+        <is>
+          <t>Anyone in the task's department could tick a named task's checklist, and ticking the last step closed it without the right to finish or its proof. Now the people who may work it; every step ticked completes it only for someone who may finish it and only with its proof.</t>
+        </is>
+      </c>
+      <c r="G218" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H218" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I218" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J218" s="28" t="n"/>
+      <c r="K218" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-15). test_files_and_checklist_follow_the_task_rules.</t>
+        </is>
+      </c>
+      <c r="L218" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/SETTINGS_RBAC_REVIEW.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.4</t>
+        </is>
+      </c>
+      <c r="B219" s="28" t="inlineStr">
+        <is>
+          <t>routers/team.py, routers/access.py, routers/tenant_settings.py, Team.js</t>
+        </is>
+      </c>
+      <c r="C219" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D219" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E219" s="28" t="inlineStr">
+        <is>
+          <t>Manage team cannot raise access</t>
+        </is>
+      </c>
+      <c r="F219" s="28" t="inlineStr">
+        <is>
+          <t>Manage team could give itself any permission (own list, temporary grants, role permissions). Now: nobody but an owner changes their own role or access; a non-owner gives only access they hold, the person already has, or that person's role defaults; only an owner changes what a role can do. The Team dialog greys out access you can't give.</t>
+        </is>
+      </c>
+      <c r="G219" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H219" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I219" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J219" s="28" t="n"/>
+      <c r="K219" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-15). tests/test_rbac_p0_access.py (2 journeys).</t>
+        </is>
+      </c>
+      <c r="L219" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/SETTINGS_RBAC_REVIEW.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.5</t>
+        </is>
+      </c>
+      <c r="B220" s="28" t="inlineStr">
+        <is>
+          <t>Settings.js</t>
+        </is>
+      </c>
+      <c r="C220" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D220" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E220" s="28" t="inlineStr">
+        <is>
+          <t>Money &amp; Approvals card only for owners</t>
+        </is>
+      </c>
+      <c r="F220" s="28" t="inlineStr">
+        <is>
+          <t>Manage team without owner saw the card and got Could not save (the server lets only an owner save it).</t>
+        </is>
+      </c>
+      <c r="G220" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H220" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I220" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J220" s="28" t="n"/>
+      <c r="K220" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-15).</t>
+        </is>
+      </c>
+      <c r="L220" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/SETTINGS_RBAC_REVIEW.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.6</t>
+        </is>
+      </c>
+      <c r="B221" s="28" t="inlineStr">
+        <is>
+          <t>Team.js, routers/team.py</t>
+        </is>
+      </c>
+      <c r="C221" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D221" s="28" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="E221" s="28" t="inlineStr">
+        <is>
+          <t>Remove / deactivate a member, revoke an invite</t>
+        </is>
+      </c>
+      <c r="F221" s="28" t="inlineStr">
+        <is>
+          <t>The backend has deprovision (reassigns tasks) and uninvite, but nothing in the app calls them. Check decisions waiting on the person before building.</t>
+        </is>
+      </c>
+      <c r="G221" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H221" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I221" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J221" s="28" t="n"/>
+      <c r="K221" s="28" t="inlineStr">
+        <is>
+          <t>Open from docs/SETTINGS_RBAC_REVIEW.md section 3.</t>
+        </is>
+      </c>
+      <c r="L221" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/SETTINGS_RBAC_REVIEW.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.7</t>
+        </is>
+      </c>
+      <c r="B222" s="28" t="inlineStr">
+        <is>
+          <t>Settings.js, Team.js, core/permissions.py</t>
+        </is>
+      </c>
+      <c r="C222" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D222" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E222" s="28" t="inlineStr">
+        <is>
+          <t>Manage access by role</t>
+        </is>
+      </c>
+      <c r="F222" s="28" t="inlineStr">
+        <is>
+          <t>No screen for a role's permissions, and Add member saves a personal list that overrides the role forever. A role permission editor, and people follow their role unless deliberately overridden.</t>
+        </is>
+      </c>
+      <c r="G222" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H222" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I222" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J222" s="28" t="n"/>
+      <c r="K222" s="28" t="inlineStr">
+        <is>
+          <t>Open from docs/SETTINGS_RBAC_REVIEW.md section 4.</t>
+        </is>
+      </c>
+      <c r="L222" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-15 (docs/SETTINGS_RBAC_REVIEW.md)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1590,6 +1590,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -2365,24 +2366,24 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
         <v>7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only. Open: remove/deactivate member, manage access by role, then the P1/P2 list.</t>
+          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. Open: the P1/P2 list in the review.</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5642,20 +5643,47 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
+          <t>1fca68d</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>RBAC P0: capture approval, files and checklist rules, Manage team cannot raise access, Money card</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="7" t="inlineStr">
+        <is>
+          <t>Settings, Team and access</t>
+        </is>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
           <t>(this push)</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>RBAC P0: capture approval, files and checklist rules, Manage team cannot raise access, Money card</t>
-        </is>
-      </c>
-      <c r="E123" s="7" t="inlineStr">
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Remove a member with hand-over; role permission editor; people follow their role</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -18157,13 +18185,13 @@
       </c>
       <c r="I221" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J221" s="28" t="n"/>
       <c r="K221" s="28" t="inlineStr">
         <is>
-          <t>Open from docs/SETTINGS_RBAC_REVIEW.md section 3.</t>
+          <t>SHIPPED (this push, 2026-09-15). Profile &gt; Remove from company with a summary of what they hold and who takes over; open tasks, contacts and reports to that person, approvals and decisions to them when allowed else the owner; Cancel invite for pending. Also fixed: removed people stayed in the member list and could sign in through the legacy fallback; accounts from before memberships can be removed and take work over. Tests: test_remove_member_hands_over_work_and_ends_access, test_remove_works_for_accounts_from_before_memberships; browser ux_rbac_team_0915.py 25/25 on a throwaway database.</t>
         </is>
       </c>
       <c r="L221" s="28" t="inlineStr">
@@ -18213,13 +18241,13 @@
       </c>
       <c r="I222" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J222" s="28" t="n"/>
       <c r="K222" s="28" t="inlineStr">
         <is>
-          <t>Open from docs/SETTINGS_RBAC_REVIEW.md section 4.</t>
+          <t>SHIPPED (this push, 2026-09-15). Settings &gt; Team roles &gt; Access (owner only), built-in default, make people with their own access follow the role; member dialog 'Use the role's access' (on by default); GET /users returns effective_permissions. Test: test_role_access_editor_reaches_people_who_follow_the_role; browser 25/25.</t>
         </is>
       </c>
       <c r="L222" s="28" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1590,7 +1590,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
@@ -2366,24 +2365,24 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. Open: the P1/P2 list in the review.</t>
+          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. P1 (2026-09-16): AI processing section, approval rules removed, edit name/email, welcome message, Team tile, No access, People access for CRM, no self-approval, real access everywhere, decisions list. P2 (2026-09-16): Workspace tab, overdue work days, while-you're-away delegation, Settings/Team tidy-up, reassign/hand-off/dictation rules. Open: separate Finance from Ledger.</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5670,20 +5669,74 @@
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
+          <t>59e9684</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>Remove a member with hand-over; role permission editor; people follow their role</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>Settings, Team and access</t>
+        </is>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
           <t>(this push)</t>
         </is>
       </c>
-      <c r="C124" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="D124" s="7" t="inlineStr">
-        <is>
-          <t>Remove a member with hand-over; role permission editor; people follow their role</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>RBAC P1: AI processing, no self-approval, No access, name/email, welcome message, real access, decisions list</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr">
+        <is>
+          <t>Settings, Team and access</t>
+        </is>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>RBAC P2: Workspace tab, overdue work, delegation, tidy-up, reassign/hand-off/dictation</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -5700,7 +5753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L222"/>
+  <dimension ref="A1:L238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18253,6 +18306,902 @@
       <c r="L222" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-15 (docs/SETTINGS_RBAC_REVIEW.md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.8</t>
+        </is>
+      </c>
+      <c r="B223" s="28" t="inlineStr">
+        <is>
+          <t>Settings.js, api.js</t>
+        </is>
+      </c>
+      <c r="C223" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D223" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E223" s="28" t="inlineStr">
+        <is>
+          <t>AI processing section in Settings</t>
+        </is>
+      </c>
+      <c r="F223" s="28" t="inlineStr">
+        <is>
+          <t>The AI-consent message linked to a Settings section that didn't exist. Settings &gt; Business &gt; AI processing shows whether it's on and who agreed; an owner turns it on or off; teammates see it read-only; the message links straight to it.</t>
+        </is>
+      </c>
+      <c r="G223" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H223" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I223" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J223" s="28" t="n"/>
+      <c r="K223" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop). Also fixed DELETE /tenant/ai-consent (updated_at outside $set: every turn-off failed with a 500); test_ai_consent_turns_on_and_off.</t>
+        </is>
+      </c>
+      <c r="L223" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.9</t>
+        </is>
+      </c>
+      <c r="B224" s="28" t="inlineStr">
+        <is>
+          <t>CompanyDetails.js, BuildReveal.js</t>
+        </is>
+      </c>
+      <c r="C224" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D224" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E224" s="28" t="inlineStr">
+        <is>
+          <t>Free-text approval rules removed</t>
+        </is>
+      </c>
+      <c r="F224" s="28" t="inlineStr">
+        <is>
+          <t>Nothing enforced them. Removed from Settings (section renamed Task templates) and from the onboarding summary. Approvals live on each task and on workflow stages.</t>
+        </is>
+      </c>
+      <c r="G224" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H224" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I224" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J224" s="28" t="n"/>
+      <c r="K224" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop).</t>
+        </is>
+      </c>
+      <c r="L224" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.10</t>
+        </is>
+      </c>
+      <c r="B225" s="28" t="inlineStr">
+        <is>
+          <t>routers/team.py, Team.js</t>
+        </is>
+      </c>
+      <c r="C225" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D225" s="28" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="E225" s="28" t="inlineStr">
+        <is>
+          <t>Edit a member's name and email</t>
+        </is>
+      </c>
+      <c r="F225" s="28" t="inlineStr">
+        <is>
+          <t>Name editable by whoever manages the team; email by an owner only (it's how they sign in), and it must not belong to another account.</t>
+        </is>
+      </c>
+      <c r="G225" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H225" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I225" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J225" s="28" t="n"/>
+      <c r="K225" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop).</t>
+        </is>
+      </c>
+      <c r="L225" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.11</t>
+        </is>
+      </c>
+      <c r="B226" s="28" t="inlineStr">
+        <is>
+          <t>Team.js</t>
+        </is>
+      </c>
+      <c r="C226" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D226" s="28" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="E226" s="28" t="inlineStr">
+        <is>
+          <t>Welcome message for password members; invite link only for pending invites</t>
+        </is>
+      </c>
+      <c r="F226" s="28" t="inlineStr">
+        <is>
+          <t>After adding someone with a password, a message to copy or send on WhatsApp with where to sign in and their email (never the password). Get invite link shows only for invites not yet accepted.</t>
+        </is>
+      </c>
+      <c r="G226" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H226" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I226" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J226" s="28" t="n"/>
+      <c r="K226" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop).</t>
+        </is>
+      </c>
+      <c r="L226" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.12</t>
+        </is>
+      </c>
+      <c r="B227" s="28" t="inlineStr">
+        <is>
+          <t>AllAppsPanel.jsx</t>
+        </is>
+      </c>
+      <c r="C227" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D227" s="28" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E227" s="28" t="inlineStr">
+        <is>
+          <t>Team tile on the phone for everyone</t>
+        </is>
+      </c>
+      <c r="F227" s="28" t="inlineStr">
+        <is>
+          <t>The tile was hidden without Manage team although /team is open to everyone (read-only).</t>
+        </is>
+      </c>
+      <c r="G227" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H227" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I227" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J227" s="28" t="n"/>
+      <c r="K227" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop).</t>
+        </is>
+      </c>
+      <c r="L227" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.13</t>
+        </is>
+      </c>
+      <c r="B228" s="28" t="inlineStr">
+        <is>
+          <t>core/permissions.py, routers/team.py, Team.js</t>
+        </is>
+      </c>
+      <c r="C228" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D228" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E228" s="28" t="inlineStr">
+        <is>
+          <t>No access option</t>
+        </is>
+      </c>
+      <c r="F228" s="28" t="inlineStr">
+        <is>
+          <t>An empty list meant the role's access, so nobody could be given none. 'Use the role's access' is stored on its own (permissions_custom); their own access with nothing ticked is No access.</t>
+        </is>
+      </c>
+      <c r="G228" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H228" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I228" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J228" s="28" t="n"/>
+      <c r="K228" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop).</t>
+        </is>
+      </c>
+      <c r="L228" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.14</t>
+        </is>
+      </c>
+      <c r="B229" s="28" t="inlineStr">
+        <is>
+          <t>contacts.py, complaints.py, crm.py, CRM.js, ContactProfile.js</t>
+        </is>
+      </c>
+      <c r="C229" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D229" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E229" s="28" t="inlineStr">
+        <is>
+          <t>Contacts, CRM and complaints use People access</t>
+        </is>
+      </c>
+      <c r="F229" s="28" t="inlineStr">
+        <is>
+          <t>Writes checked the owner/sales role names, so a custom role with People was refused while the buttons showed.</t>
+        </is>
+      </c>
+      <c r="G229" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H229" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I229" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J229" s="28" t="n"/>
+      <c r="K229" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop).</t>
+        </is>
+      </c>
+      <c r="L229" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.15</t>
+        </is>
+      </c>
+      <c r="B230" s="28" t="inlineStr">
+        <is>
+          <t>routers/tasks.py, MyWork.js, Desk.js, Tasks.js</t>
+        </is>
+      </c>
+      <c r="C230" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D230" s="28" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="E230" s="28" t="inlineStr">
+        <is>
+          <t>Nobody approves their own work (owners exempt)</t>
+        </is>
+      </c>
+      <c r="F230" s="28" t="inlineStr">
+        <is>
+          <t>A non-owner can't approve a task they do, help on or asked for: naming them is refused, the default approver skips a manager on the task, and completing a before-done task you'd approve yourself sends it for sign-off.</t>
+        </is>
+      </c>
+      <c r="G230" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H230" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I230" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J230" s="28" t="n"/>
+      <c r="K230" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop).</t>
+        </is>
+      </c>
+      <c r="L230" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.16</t>
+        </is>
+      </c>
+      <c r="B231" s="28" t="inlineStr">
+        <is>
+          <t>services/auth/membership.py, decision_flow.py, notifications.py, routers/tasks.py</t>
+        </is>
+      </c>
+      <c r="C231" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D231" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E231" s="28" t="inlineStr">
+        <is>
+          <t>Real access for deciders, approvers and notifications</t>
+        </is>
+      </c>
+      <c r="F231" s="28" t="inlineStr">
+        <is>
+          <t>Decision routing, the deciders list, the task approver check, approval notifications and the member list read membership, role settings, temporary grants and owner exclusions (members_effective_perms), not the bare user record.</t>
+        </is>
+      </c>
+      <c r="G231" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H231" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I231" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J231" s="28" t="n"/>
+      <c r="K231" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop).</t>
+        </is>
+      </c>
+      <c r="L231" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.17</t>
+        </is>
+      </c>
+      <c r="B232" s="28" t="inlineStr">
+        <is>
+          <t>routers/decisions.py</t>
+        </is>
+      </c>
+      <c r="C232" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D232" s="28" t="inlineStr">
+        <is>
+          <t>Decisions</t>
+        </is>
+      </c>
+      <c r="E232" s="28" t="inlineStr">
+        <is>
+          <t>Decisions list shows only what you can open; adding a task to a decision is checked</t>
+        </is>
+      </c>
+      <c r="F232" s="28" t="inlineStr">
+        <is>
+          <t>The list returned every decision's title; now only decisions you can open (helpers on its tasks count). Adding a task needs you on the decision or able to decide it, and follows the assign rules.</t>
+        </is>
+      </c>
+      <c r="G232" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H232" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I232" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J232" s="28" t="n"/>
+      <c r="K232" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Browser ux_rbac_p1_0916.py 23/23 on a throwaway database (owner desktop, sales phone and desktop).</t>
+        </is>
+      </c>
+      <c r="L232" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.18</t>
+        </is>
+      </c>
+      <c r="B233" s="28" t="inlineStr">
+        <is>
+          <t>Settings.js, routers/tenant_settings.py</t>
+        </is>
+      </c>
+      <c r="C233" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D233" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E233" s="28" t="inlineStr">
+        <is>
+          <t>Workspace tab: plan and seats, AI keys, what owners can open, audit log</t>
+        </is>
+      </c>
+      <c r="F233" s="28" t="inlineStr">
+        <is>
+          <t>Owner-only tab for what the backend had without a screen. AI keys set one provider at a time (new PATCH /tenant/ai-keys/{provider}; PUT replaced the whole map). Owners can't be excluded from Manage team.</t>
+        </is>
+      </c>
+      <c r="G233" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H233" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I233" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J233" s="28" t="n"/>
+      <c r="K233" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_rbac_p2.py; browser ux_rbac_p2_0916.py 31/31 on a throwaway database (owner desktop and phone, sales desktop).</t>
+        </is>
+      </c>
+      <c r="L233" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.19</t>
+        </is>
+      </c>
+      <c r="B234" s="28" t="inlineStr">
+        <is>
+          <t>Settings.js, services/tasks.py, finance_signals.py, desk.py, notifications.py</t>
+        </is>
+      </c>
+      <c r="C234" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D234" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E234" s="28" t="inlineStr">
+        <is>
+          <t>Overdue work: escalation days and owner alert email</t>
+        </is>
+      </c>
+      <c r="F234" s="28" t="inlineStr">
+        <is>
+          <t>Owner sets the days before the doer's manager and then the owner hear about a late task, and whether owners also get it by email. The reminder sweep and the Desk's slipping list use them.</t>
+        </is>
+      </c>
+      <c r="G234" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H234" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I234" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J234" s="28" t="n"/>
+      <c r="K234" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_rbac_p2.py; browser ux_rbac_p2_0916.py 31/31 on a throwaway database (owner desktop and phone, sales desktop).</t>
+        </is>
+      </c>
+      <c r="L234" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.20</t>
+        </is>
+      </c>
+      <c r="B235" s="28" t="inlineStr">
+        <is>
+          <t>services/delegation.py, core/deps.py, routers/tasks.py, decision_flow.py, desk.py, Settings.js</t>
+        </is>
+      </c>
+      <c r="C235" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D235" s="28" t="inlineStr">
+        <is>
+          <t>Approval</t>
+        </is>
+      </c>
+      <c r="E235" s="28" t="inlineStr">
+        <is>
+          <t>Approve on my behalf while I'm away</t>
+        </is>
+      </c>
+      <c r="F235" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Account &gt; While you're away. The delegate approves tasks and decides decisions that wait on the person away, sees them in Approvals and on the Desk, and is told when new ones arrive. It was stored but never read.</t>
+        </is>
+      </c>
+      <c r="G235" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H235" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I235" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J235" s="28" t="n"/>
+      <c r="K235" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_rbac_p2.py; browser ux_rbac_p2_0916.py 31/31 on a throwaway database (owner desktop and phone, sales desktop). Also fixed: dates were compared with the UTC date, so 'from today' stayed off until 5:30 am in India; and older accounts without a membership never picked up delegated approvals.</t>
+        </is>
+      </c>
+      <c r="L235" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.21</t>
+        </is>
+      </c>
+      <c r="B236" s="28" t="inlineStr">
+        <is>
+          <t>Settings.js, CompanyDetails.js, Team.js, perms.js, App.js, BuildReveal.js</t>
+        </is>
+      </c>
+      <c r="C236" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D236" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E236" s="28" t="inlineStr">
+        <is>
+          <t>Settings and Team tidy-up</t>
+        </is>
+      </c>
+      <c r="F236" s="28" t="inlineStr">
+        <is>
+          <t>Currency only on the Money card; Language and Theme for everyone; the app's own dialog for making/removing an owner; /people removed (redirects to Team); one name 'Team' on screen; Decision Desk and captures labels; Export Company Brain toggle.</t>
+        </is>
+      </c>
+      <c r="G236" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H236" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I236" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J236" s="28" t="n"/>
+      <c r="K236" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_rbac_p2.py; browser ux_rbac_p2_0916.py 31/31 on a throwaway database (owner desktop and phone, sales desktop). The owner-change confirmation sits inside the member dialog (a stacked dialog rendered underneath).</t>
+        </is>
+      </c>
+      <c r="L236" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.22</t>
+        </is>
+      </c>
+      <c r="B237" s="28" t="inlineStr">
+        <is>
+          <t>routers/tasks.py, voice_notes.py, MyWork.js</t>
+        </is>
+      </c>
+      <c r="C237" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D237" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E237" s="28" t="inlineStr">
+        <is>
+          <t>Reassign, hand-off, dictation and AI priority follow the rules</t>
+        </is>
+      </c>
+      <c r="F237" s="28" t="inlineStr">
+        <is>
+          <t>/reassign uses the task's people rule then the assign rules; hand-off follows the assign rules; /transcribe needs Ask AI or Voice capture; the AI-priority toggle shows only for owners and Manage team.</t>
+        </is>
+      </c>
+      <c r="G237" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H237" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I237" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J237" s="28" t="n"/>
+      <c r="K237" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_rbac_p2.py; browser ux_rbac_p2_0916.py 31/31 on a throwaway database (owner desktop and phone, sales desktop).</t>
+        </is>
+      </c>
+      <c r="L237" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.23</t>
+        </is>
+      </c>
+      <c r="B238" s="28" t="inlineStr">
+        <is>
+          <t>routers/ledger.py, Ledger.js</t>
+        </is>
+      </c>
+      <c r="C238" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D238" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E238" s="28" t="inlineStr">
+        <is>
+          <t>Separate Finance from Ledger</t>
+        </is>
+      </c>
+      <c r="F238" s="28" t="inlineStr">
+        <is>
+          <t>31 ledger endpoints accept either permission and the Finance page has no per-tab gate; separating needs the tabs gated one by one.</t>
+        </is>
+      </c>
+      <c r="G238" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H238" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I238" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J238" s="28" t="n"/>
+      <c r="K238" s="28" t="inlineStr">
+        <is>
+          <t>Open from docs/SETTINGS_RBAC_REVIEW.md section 4.</t>
+        </is>
+      </c>
+      <c r="L238" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P2)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2365,14 +2365,14 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. P1 (2026-09-16): AI processing section, approval rules removed, edit name/email, welcome message, Team tile, No access, People access for CRM, no self-approval, real access everywhere, decisions list. P2 (2026-09-16): Workspace tab, overdue work days, while-you're-away delegation, Settings/Team tidy-up, reassign/hand-off/dictation rules. Open: separate Finance from Ledger.</t>
+          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. P1 (2026-09-16): AI processing section, approval rules removed, edit name/email, welcome message, Team tile, No access, People access for CRM, no self-approval, real access everywhere, decisions list. P2 (2026-09-16): Workspace tab, overdue work days, while-you're-away delegation, Settings/Team tidy-up, reassign/hand-off/dictation rules. Re-checked after Sakthivel's Team redesign (8b60707): invited members could not use the app at all (a pending membership was never accepted) — fixed; an invite link kept its OTP cooldown; the audit scripts follow the new Team canvas. Open: separate Finance from Ledger; a team manager can change a teammate's mobile, which is their login.</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5742,6 +5742,33 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr">
+        <is>
+          <t>Settings, Team and access</t>
+        </is>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>Invited members can sign in again (pending membership was never accepted); invite links keep the OTP cooldown; audit scripts follow the new Team canvas</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5753,7 +5780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L238"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19202,6 +19229,174 @@
       <c r="L238" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-16 (docs/SETTINGS_RBAC_REVIEW.md, P2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.24</t>
+        </is>
+      </c>
+      <c r="B239" s="28" t="inlineStr">
+        <is>
+          <t>services/auth/membership.py, routers/auth_otp.py, routers/auth.py</t>
+        </is>
+      </c>
+      <c r="C239" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D239" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E239" s="28" t="inlineStr">
+        <is>
+          <t>An invited member can actually get in</t>
+        </is>
+      </c>
+      <c r="F239" s="28" t="inlineStr">
+        <is>
+          <t>A member is created as a pending membership and nothing moved it to active, so since 59e9684 the invitee signed in with the texted code and was refused on their very next request. Signing in now accepts the invite, on the code door and the password door; suspended and removed rows are untouched; the seat is recounted, so a workspace that filled up after the invite still admits them.</t>
+        </is>
+      </c>
+      <c r="G239" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H239" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I239" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J239" s="28" t="n"/>
+      <c r="K239" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_invite_accept.py (7); browser ux_invite_accept_0916.py 17/17 on a throwaway database, and it fails on exactly those checks with the fix taken out.</t>
+        </is>
+      </c>
+      <c r="L239" s="28" t="inlineStr">
+        <is>
+          <t>Found re-checking the Team page after 8b60707</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.25</t>
+        </is>
+      </c>
+      <c r="B240" s="28" t="inlineStr">
+        <is>
+          <t>routers/auth_otp.py</t>
+        </is>
+      </c>
+      <c r="C240" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D240" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E240" s="28" t="inlineStr">
+        <is>
+          <t>An invite link cannot text someone on a loop</t>
+        </is>
+      </c>
+      <c r="F240" s="28" t="inlineStr">
+        <is>
+          <t>/auth/invite/{token}/start skipped the 30s OTP cooldown, so anyone holding a forwarded link could make the app text that member over and over. It now keeps the ordinary cooldown, and a re-tap inside the window still returns the number and name the device needs instead of an error.</t>
+        </is>
+      </c>
+      <c r="G240" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H240" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I240" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J240" s="28" t="n"/>
+      <c r="K240" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_invite_accept.py. This is what the 'invite link only while pending' rule was really guarding against; Sakthivel's redesign (8b60707) keeps the icon for every member but an owner.</t>
+        </is>
+      </c>
+      <c r="L240" s="28" t="inlineStr">
+        <is>
+          <t>Found re-checking the Team page after 8b60707</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.26</t>
+        </is>
+      </c>
+      <c r="B241" s="28" t="inlineStr">
+        <is>
+          <t>PATCH /users/{id} (routers/team.py)</t>
+        </is>
+      </c>
+      <c r="C241" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D241" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E241" s="28" t="inlineStr">
+        <is>
+          <t>A team manager can take over a teammate's account</t>
+        </is>
+      </c>
+      <c r="F241" s="28" t="inlineStr">
+        <is>
+          <t>Manage team can change another member's mobile number, and the number is the login — so a manager can point a colleague's account at their own phone and sign in as them. An owner is already protected. Fix: a manager may add a number where there is none (the invite icon needs that), only an owner may change one already set.</t>
+        </is>
+      </c>
+      <c r="G241" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H241" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I241" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J241" s="28" t="n"/>
+      <c r="K241" s="28" t="inlineStr">
+        <is>
+          <t>Open from docs/SETTINGS_RBAC_REVIEW.md, 'Found while re-checking the Team page'.</t>
+        </is>
+      </c>
+      <c r="L241" s="28" t="inlineStr">
+        <is>
+          <t>Found re-checking the Team page after 8b60707</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2365,14 +2365,14 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5769,6 +5769,33 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="7" t="inlineStr">
+        <is>
+          <t>Settings, Team and access</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>Settings opens again for everyone but an owner (the Appearance card was removed from one branch only)</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5780,7 +5807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L241"/>
+  <dimension ref="A1:L242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19397,6 +19424,62 @@
       <c r="L241" s="28" t="inlineStr">
         <is>
           <t>Found re-checking the Team page after 8b60707</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.27</t>
+        </is>
+      </c>
+      <c r="B242" s="28" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/Settings.js</t>
+        </is>
+      </c>
+      <c r="C242" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D242" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E242" s="28" t="inlineStr">
+        <is>
+          <t>Settings opened again for everyone but an owner</t>
+        </is>
+      </c>
+      <c r="F242" s="28" t="inlineStr">
+        <is>
+          <t>ASK-33 Phase 5 (2eed722) dropped the Appearance card with the theme switch, but the non-owner view still rendered &lt;ThemeCard /&gt;: the page threw "ThemeCard is not defined" and every teammate got the broken-panel notice instead of Settings — language, profile, password, hand-over and sign out all unreachable.</t>
+        </is>
+      </c>
+      <c r="G242" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H242" s="28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I242" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J242" s="28" t="n"/>
+      <c r="K242" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). Caught by the P1/P2 browser checks after rebasing onto 2eed722; browser ux_rbac_p1_0916.py 23/23 and ux_rbac_p2_0916.py 32/32 on a throwaway database.</t>
+        </is>
+      </c>
+      <c r="L242" s="28" t="inlineStr">
+        <is>
+          <t>Found re-running the RBAC browser checks</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. P1 (2026-09-16): AI processing section, approval rules removed, edit name/email, welcome message, Team tile, No access, People access for CRM, no self-approval, real access everywhere, decisions list. P2 (2026-09-16): Workspace tab, overdue work days, while-you're-away delegation, Settings/Team tidy-up, reassign/hand-off/dictation rules. Re-checked after Sakthivel's Team redesign (8b60707): invited members could not use the app at all (a pending membership was never accepted) — fixed; an invite link kept its OTP cooldown; the audit scripts follow the new Team canvas. Open: separate Finance from Ledger; a team manager can change a teammate's mobile, which is their login.</t>
+          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. P1 (2026-09-16): AI processing section, approval rules removed, edit name/email, welcome message, Team tile, No access, People access for CRM, no self-approval, real access everywhere, decisions list. P2 (2026-09-16): Workspace tab, overdue work days, while-you're-away delegation, Settings/Team tidy-up, reassign/hand-off/dictation rules. Re-checked after Sakthivel's Team redesign (8b60707): invited members could not use the app at all (a pending membership was never accepted) — fixed; an invite link kept its OTP cooldown; the audit scripts follow the new Team canvas. Only an owner changes a teammate's mobile (it is the sign-in), and a person keeps their own details — name, job title, what they handle, mobile, email — without a manager. Open: separate Finance from Ledger.</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5796,6 +5796,33 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>Settings, Team and access</t>
+        </is>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>Only an owner changes a teammate's mobile (it is the sign-in); a person keeps their own name, title, what they handle, mobile and email</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5807,7 +5834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L242"/>
+  <dimension ref="A1:L244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19412,13 +19439,13 @@
       </c>
       <c r="I241" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J241" s="28" t="n"/>
       <c r="K241" s="28" t="inlineStr">
         <is>
-          <t>Open from docs/SETTINGS_RBAC_REVIEW.md, 'Found while re-checking the Team page'.</t>
+          <t>Superseded by the shipped row below (same ID, same day).</t>
         </is>
       </c>
       <c r="L241" s="28" t="inlineStr">
@@ -19480,6 +19507,118 @@
       <c r="L242" s="28" t="inlineStr">
         <is>
           <t>Found re-running the RBAC browser checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.26</t>
+        </is>
+      </c>
+      <c r="B243" s="28" t="inlineStr">
+        <is>
+          <t>routers/team.py, Team.js</t>
+        </is>
+      </c>
+      <c r="C243" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D243" s="28" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="E243" s="28" t="inlineStr">
+        <is>
+          <t>A team manager can take over a teammate's account</t>
+        </is>
+      </c>
+      <c r="F243" s="28" t="inlineStr">
+        <is>
+          <t>Manage team could change any member's mobile, and the mobile is the sign-in: point a colleague's account at your own phone, ask for a code, and you are them — with their access, and their name on what you do. Now: a manager may FILL IN a number where there is none (they cannot sign in at all until then, and the invite link needs one), and changing one already set is the owner's call, the same line email draws. One mobile, one member inside a workspace; the same number in another workspace is still fine.</t>
+        </is>
+      </c>
+      <c r="G243" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H243" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I243" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J243" s="28" t="n"/>
+      <c r="K243" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_own_profile_and_phone.py; browser ux_profile_phone_0916.py 19/19 on a throwaway database (the field is closed with the reason shown, the server refuses it, everything else about the member still saves, and a missing number can still be filled in).</t>
+        </is>
+      </c>
+      <c r="L243" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.28</t>
+        </is>
+      </c>
+      <c r="B244" s="28" t="inlineStr">
+        <is>
+          <t>routers/auth.py, models/auth.py, services/otp.py, ProfileDialog.js</t>
+        </is>
+      </c>
+      <c r="C244" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D244" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E244" s="28" t="inlineStr">
+        <is>
+          <t>A person keeps their own details current</t>
+        </is>
+      </c>
+      <c r="F244" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Your Profile now holds name, job title, what they handle, mobile and email — no manager needed, and nothing on that card touches role, permissions or the reporting line. The email is the sign-in, so a change is confirmed by the current password (or, for a mobile-only member, a code texted to them, checked the way the sign-in door checks it) and the new address goes back to unverified until the link is clicked. What someone handles shows on their Team profile, in their own words.</t>
+        </is>
+      </c>
+      <c r="G244" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H244" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I244" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J244" s="28" t="n"/>
+      <c r="K244" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_own_profile_and_phone.py; browser ux_profile_phone_0916.py 19/19. Also fixed: the form re-filled itself on every auth refresh, wiping whatever was half-typed.</t>
+        </is>
+      </c>
+      <c r="L244" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2365,14 +2365,14 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28" t="n">
         <v>29</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. P1 (2026-09-16): AI processing section, approval rules removed, edit name/email, welcome message, Team tile, No access, People access for CRM, no self-approval, real access everywhere, decisions list. P2 (2026-09-16): Workspace tab, overdue work days, while-you're-away delegation, Settings/Team tidy-up, reassign/hand-off/dictation rules. Re-checked after Sakthivel's Team redesign (8b60707): invited members could not use the app at all (a pending membership was never accepted) — fixed; an invite link kept its OTP cooldown; the audit scripts follow the new Team canvas. Only an owner changes a teammate's mobile (it is the sign-in), and a person keeps their own details — name, job title, what they handle, mobile, email — without a manager. Open: separate Finance from Ledger.</t>
+          <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. P1 (2026-09-16): AI processing section, approval rules removed, edit name/email, welcome message, Team tile, No access, People access for CRM, no self-approval, real access everywhere, decisions list. P2 (2026-09-16): Workspace tab, overdue work days, while-you're-away delegation, Settings/Team tidy-up, reassign/hand-off/dictation rules. Re-checked after Sakthivel's Team redesign (8b60707): invited members could not use the app at all (a pending membership was never accepted) — fixed; an invite link kept its OTP cooldown; the audit scripts follow the new Team canvas. Only an owner changes a teammate's mobile (it is the sign-in), and a person keeps their own details — name, job title, what they handle, mobile, email — without a manager. Finance is one permission (the second Ledger toggle promised a wall nothing enforced; merged, with a boot migration so nobody loses the page).</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5818,6 +5818,33 @@
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t>Settings, Team and access</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Finance is one permission — the second 'Finance Ledger' toggle is gone, and everyone who held it keeps the page</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -19251,12 +19278,12 @@
       </c>
       <c r="E238" s="28" t="inlineStr">
         <is>
-          <t>Separate Finance from Ledger</t>
+          <t>Finance is one permission (was: separate Finance from Ledger)</t>
         </is>
       </c>
       <c r="F238" s="28" t="inlineStr">
         <is>
-          <t>31 ledger endpoints accept either permission and the Finance page has no per-tab gate; separating needs the tabs gated one by one.</t>
+          <t>Two toggles for one page — 'Finance (invoices, payments, 360°)' and 'Finance Ledger (expenses, assets, inventory)' — with nothing behind them: all 31 ledger endpoints accepted either key and the page has no per-tab gate. Closed by MERGING rather than splitting (founder, Yokesh 2026-09-16: a small business has one finance person). 'ledger' is out of the key list, the endpoints ask for 'finance', and a boot migration gives 'finance' to everyone who held 'ledger' — user lists, memberships, a tenant's own roles, and owner exclusions.</t>
         </is>
       </c>
       <c r="G238" s="28" t="inlineStr">
@@ -19271,13 +19298,13 @@
       </c>
       <c r="I238" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J238" s="28" t="n"/>
       <c r="K238" s="28" t="inlineStr">
         <is>
-          <t>Open from docs/SETTINGS_RBAC_REVIEW.md section 4.</t>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_finance_one_permission.py; browser ux_finance_one_perm_0916.py 14/14 on a throwaway database (one toggle in the form, the whole page opens on it, taking it away closes the page and 403s the calls).</t>
         </is>
       </c>
       <c r="L238" s="28" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2332,14 +2332,14 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves; Needs approval is task approvals only; the card says who raised it and who decides; test data cleared; every approval task names who approves (manager, else owner). Open: sign-off before done on decision tasks (3.5, another team), Phase 5 (capture feedback on desktop, retry, My captures).</t>
+          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves; Needs approval is task approvals only; the card says who raised it and who decides; test data cleared; every approval task names who approves (manager, else owner). Open: sign-off before done on decision tasks (3.5, another team), Phase 5 (capture feedback on desktop, retry, My captures). Driven in the browser end-to-end on 2026-09-16 (login → Desk → capture → decision → approve → task): the AI's routing is good, and three faults came out of it — a remark being raised as a decision (FIXED: prompt 1.1 decision guard + a pipeline gate), a capture that AI-consent blocked reported as "Nothing to decide" (open, next), and an approved meeting that writes a real calendar event plus a dateless companion to-do (verified, deferred).</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5850,6 +5850,33 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>A remark is no longer a decision: the extraction prompt gets a decision guard and the pipeline raises a decision only for work or a rule</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5861,7 +5888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L244"/>
+  <dimension ref="A1:L247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19646,6 +19673,174 @@
       <c r="L244" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.29</t>
+        </is>
+      </c>
+      <c r="B245" s="28" t="inlineStr">
+        <is>
+          <t>prompts/extraction.py, services/voice.py</t>
+        </is>
+      </c>
+      <c r="C245" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D245" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E245" s="28" t="inlineStr">
+        <is>
+          <t>A remark is not a decision</t>
+        </is>
+      </c>
+      <c r="F245" s="28" t="inlineStr">
+        <is>
+          <t>Found by driving the Desk in the browser: "The new office chairs arrived and everyone likes them" came back as a decision — "Office chairs received and approved by team", 0 tasks — waiting for the owner to approve it. The AI had read it right (type observation, confidence 0.95); the pipeline raised a decision anyway, because the only gate asked whether the capture produced NOTHING and a single memory note got past it. Now: the extraction prompt (1.1) carries a decision guard with examples of what is not a decision — a report on how things are, small talk, a question, thinking out loud, an unintelligible fragment — and forbids inventing a follow-up task to wrap around a remark; and the pipeline raises a decision only when the proposal would CREATE something (task, workflow, meeting, reminder) or the owner stated a directive/approval/policy. News with a lasting fact is kept in the Company Brain and says so; chatter is kept nowhere.</t>
+        </is>
+      </c>
+      <c r="G245" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H245" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I245" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J245" s="28" t="n"/>
+      <c r="K245" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_capture_is_a_decision.py (16); live-AI acceptance scripts/ux_capture_guard_0916.py 10/10 on a throwaway workspace — a meeting, a vendor switch, a policy, a discount and a Tanglish directive all raise decisions; two status remarks, a greeting, a question and thinking-out-loud raise none.</t>
+        </is>
+      </c>
+      <c r="L245" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16, from the browser run</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.30</t>
+        </is>
+      </c>
+      <c r="B246" s="28" t="inlineStr">
+        <is>
+          <t>services/voice.py, Ledger/calendar</t>
+        </is>
+      </c>
+      <c r="C246" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D246" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E246" s="28" t="inlineStr">
+        <is>
+          <t>A capture that cannot be read says so</t>
+        </is>
+      </c>
+      <c r="F246" s="28" t="inlineStr">
+        <is>
+          <t>With AI processing off, a capture is stored, marked done with no proposal, and the Desk says "Nothing to decide in that" — while the server logs ai_consent_required. The one failure ASK-33 was built to surface (14 of 15 failures in the live data) still has no face, and it hits a new workspace on its very first capture because consent starts off.</t>
+        </is>
+      </c>
+      <c r="G246" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H246" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I246" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J246" s="28" t="n"/>
+      <c r="K246" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-16 driving the Desk in the browser. Next after the decision guard.</t>
+        </is>
+      </c>
+      <c r="L246" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16, from the browser run</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.31</t>
+        </is>
+      </c>
+      <c r="B247" s="28" t="inlineStr">
+        <is>
+          <t>services/voice.py _create_meetings, Calendar.js</t>
+        </is>
+      </c>
+      <c r="C247" s="28" t="n">
+        <v>23</v>
+      </c>
+      <c r="D247" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E247" s="28" t="inlineStr">
+        <is>
+          <t>An approved meeting looks like a stray to-do</t>
+        </is>
+      </c>
+      <c r="F247" s="28" t="inlineStr">
+        <is>
+          <t>Approving a decision with a meeting writes a real calendar_events row (it shows on /calendar) AND a companion task titled "Meeting with X (Tomorrow at 4:00 PM)" assigned to the capturer with NO due date, which lands in My Work looking like a to-do with the time glued into its title. There is no Meetings section in the main nav, so the calendar entry is easy to miss. Verified 2026-09-16: the event IS created — the task is the ugly part.</t>
+        </is>
+      </c>
+      <c r="G247" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H247" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I247" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J247" s="28" t="n"/>
+      <c r="K247" s="28" t="inlineStr">
+        <is>
+          <t>Verified only, at the founder's instruction (2026-09-16): fix later.</t>
+        </is>
+      </c>
+      <c r="L247" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-16, from the browser run</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2332,14 +2332,14 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D27" t="n">
         <v>21</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves; Needs approval is task approvals only; the card says who raised it and who decides; test data cleared; every approval task names who approves (manager, else owner). Open: sign-off before done on decision tasks (3.5, another team), Phase 5 (capture feedback on desktop, retry, My captures). Driven in the browser end-to-end on 2026-09-16 (login → Desk → capture → decision → approve → task): the AI's routing is good, and three faults came out of it — a remark being raised as a decision (FIXED: prompt 1.1 decision guard + a pipeline gate), a capture that AI-consent blocked reported as "Nothing to decide" (open, next), and an approved meeting that writes a real calendar event plus a dateless companion to-do (verified, deferred).</t>
+          <t>Decision Desk decision flow (docs/DECISION_DESK_PLAN.md), ASK-32, 2026-09-15: proposals until approval, who decides and who is told, a simple editable decision screen, workflows matched and moved by themselves; Needs approval is task approvals only; the card says who raised it and who decides; test data cleared; every approval task names who approves (manager, else owner). Open: sign-off before done on decision tasks (3.5, another team), Phase 5 (capture feedback on desktop, retry, My captures). Driven in the browser end-to-end on 2026-09-16 (login → Desk → capture → decision → approve → task): the AI's routing is good, and three faults came out of it — a remark being raised as a decision (FIXED: prompt 1.1 decision guard + a pipeline gate), a capture that AI-consent blocked reported as "Nothing to decide" (FIXED: the seeded workspace agrees to AI like a signup does, and any AI failure now reaches the Desk with its reason), and an approved meeting that writes a real calendar event plus a dateless companion to-do (verified, deferred).</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5872,6 +5872,33 @@
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>A capture that could not be read says why (and a fresh workspace has AI on, like a real signup)</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
@@ -19740,7 +19767,7 @@
       </c>
       <c r="B246" s="28" t="inlineStr">
         <is>
-          <t>services/voice.py, Ledger/calendar</t>
+          <t>bootstrap/seed.py, services/ai/extraction.py, services/voice.py, services/meetings.py, services/ai_consent.py</t>
         </is>
       </c>
       <c r="C246" s="28" t="n">
@@ -19758,7 +19785,7 @@
       </c>
       <c r="F246" s="28" t="inlineStr">
         <is>
-          <t>With AI processing off, a capture is stored, marked done with no proposal, and the Desk says "Nothing to decide in that" — while the server logs ai_consent_required. The one failure ASK-33 was built to surface (14 of 15 failures in the live data) still has no face, and it hits a new workspace on its very first capture because consent starts off.</t>
+          <t>Three faults in one symptom. (1) A freshly seeded workspace had NO ai_consent record — a real signup records consent at the signup click, but the demo/seeded workspace did not, so every new install, dev machine and demo had AI off. (2) ai_extract caught the 451 and returned a clean empty extraction, so no caller could tell 'the AI read this and found nothing' from 'the AI never ran'. (3) The capture was therefore stored as done/nothing_to_decide, and the screen that says 'AI is off for this company' with a link to Settings — already built — was unreachable. Now: the seeder agrees to AI processing the way signup does; ai_extract carries the reason back as ai_error; the pipeline checks consent BEFORE speech-to-text and the model, and marks the capture failed with the reason for any AI failure (outage, rate limit, bad key, consent revoked mid-flight); the meeting pipeline does the same.</t>
         </is>
       </c>
       <c r="G246" s="28" t="inlineStr">
@@ -19773,13 +19800,13 @@
       </c>
       <c r="I246" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J246" s="28" t="n"/>
       <c r="K246" s="28" t="inlineStr">
         <is>
-          <t>Found 2026-09-16 driving the Desk in the browser. Next after the decision guard.</t>
+          <t>SHIPPED (this push, 2026-09-16). tests/test_capture_says_why_it_failed.py (8); browser acceptance scripts/ux_capture_ai_off_0916.py 10/10 on a FRESHLY seeded throwaway workspace — AI on from the first minute, the first capture becomes a decision, revoking consent makes the next capture fail with the reason and raise nothing, granting it again works. Confirmed on screen: the Desk shows 'AI is off for this company — an owner has to turn on AI consent before Dex can read anything' with Open Settings and Retry. No paid call is spent on a capture that cannot be read.</t>
         </is>
       </c>
       <c r="L246" s="28" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2397,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5904,6 +5904,33 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>A workspace is created in seconds and a second press signs the founder in — the AI setup fills in behind them</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5915,7 +5942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L247"/>
+  <dimension ref="A1:L250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19868,6 +19895,174 @@
       <c r="L247" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-16, from the browser run</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.01</t>
+        </is>
+      </c>
+      <c r="B248" s="28" t="inlineStr">
+        <is>
+          <t>routers/auth.py, services/ai/ai_setup.py, BuildReveal.js, Signup.js</t>
+        </is>
+      </c>
+      <c r="C248" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D248" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E248" s="28" t="inlineStr">
+        <is>
+          <t>Creating a workspace no longer waits on the AI</t>
+        </is>
+      </c>
+      <c r="F248" s="28" t="inlineStr">
+        <is>
+          <t>Reported: "everything passed, and finally it said it couldn't create a workspace — email already registered, but the email was new." Reproduced by walking the real signup: check-email said the address was free, POST /auth/register took 14,425 ms (three AI generations, slowest 10,012 ms), a retry returned 400 Email already registered, and the account existed with a working password. The generators ran INSIDE the request, BEFORE the user row, so any client that gave up first (KM-61 caught the proxy doing exactly that at its 60s ceiling) left a finished workspace behind an error screen. Now the tenant, owner and membership are written first and the AI setup runs behind the response (ai_setup_status 'pending' until it lands; every reader already tolerated absent AI fields). Register: 14.4s -&gt; 4-5s.</t>
+        </is>
+      </c>
+      <c r="G248" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H248" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I248" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J248" s="28" t="n"/>
+      <c r="K248" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-17). tests/test_signup_survives_a_slow_ai.py (6); browser acceptance scripts/ux_signup_0917.py 24/24, clicked through every step on a throwaway database.</t>
+        </is>
+      </c>
+      <c r="L248" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17, from testing signup in the browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.02</t>
+        </is>
+      </c>
+      <c r="B249" s="28" t="inlineStr">
+        <is>
+          <t>routers/auth.py, BuildReveal.js</t>
+        </is>
+      </c>
+      <c r="C249" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D249" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E249" s="28" t="inlineStr">
+        <is>
+          <t>Pressing Create twice ends in the workspace, not a wall</t>
+        </is>
+      </c>
+      <c r="F249" s="28" t="inlineStr">
+        <is>
+          <t>The second press is almost never someone else's account — it is the same founder whose first answer was lost. If the password they typed opens the existing account, register now signs them in and hands them their workspace; if it does not, the refusal carries the code email_registered and the words the signup form uses at the email step, and the screen shows a Sign in instead button. The screen also re-checks the email right before the long call, and falls back to signing in when creating fails at all — which also carries a founder past the per-network registration rate limit.</t>
+        </is>
+      </c>
+      <c r="G249" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H249" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I249" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J249" s="28" t="n"/>
+      <c r="K249" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-17). Found and fixed a crash on the way: Signup.js passed a `login` it had not destructured from the auth context, which broke the whole signup screen at the build step — caught by the browser walk-through, not by any test.</t>
+        </is>
+      </c>
+      <c r="L249" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17, from testing signup in the browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.03</t>
+        </is>
+      </c>
+      <c r="B250" s="28" t="inlineStr">
+        <is>
+          <t>routers/auth.py</t>
+        </is>
+      </c>
+      <c r="C250" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D250" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E250" s="28" t="inlineStr">
+        <is>
+          <t>The signup rate limit says how long, and names the other door</t>
+        </is>
+      </c>
+      <c r="F250" s="28" t="inlineStr">
+        <is>
+          <t>Three workspaces per hour is counted per NETWORK, so an office behind one address reaches it quickly and a founder who hits one error cannot retry. "Too many registrations from this network. Try again later." left them with nothing to do and no idea when. It now says about how many minutes, and that signing in is the way in if they already have a workspace.</t>
+        </is>
+      </c>
+      <c r="G250" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H250" s="28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I250" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J250" s="28" t="n"/>
+      <c r="K250" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-17). Seen in the browser run: "Three workspaces have already been created from this network in the last hour. Try again in about 58 minutes — or sign in if you already have a workspace."</t>
+        </is>
+      </c>
+      <c r="L250" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17, from testing signup in the browser</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2397,7 +2397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5931,6 +5931,33 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>(this push)</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Signup resumes where it was left — each step saved, only the password asked again</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5942,7 +5969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L250"/>
+  <dimension ref="A1:L251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20063,6 +20090,62 @@
       <c r="L250" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-17, from testing signup in the browser</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.04</t>
+        </is>
+      </c>
+      <c r="B251" s="28" t="inlineStr">
+        <is>
+          <t>lib/onboardingDraft.js, Signup.js, BasicsFlow.js, BuildReveal.js</t>
+        </is>
+      </c>
+      <c r="C251" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D251" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E251" s="28" t="inlineStr">
+        <is>
+          <t>Signup is saved as it goes, so closing the tab is not starting over</t>
+        </is>
+      </c>
+      <c r="F251" s="28" t="inlineStr">
+        <is>
+          <t>The draft store had been there since FIX-001-D — create, resume, patch, a signed token per draft, a 30-day TTL, and /register already merging a draft — and the wizard called none of it. Now each step is saved as it completes; reopening /signup restores what was typed and reopens at the password, the one field never stored (the store refuses it by design), with a line saying so; a blueprint already built comes back rather than being generated again. Validate each step, save each step, create nothing until the end. A draft that expired, was used, or whose token no longer verifies starts a clean signup with no error; a browser with storage disabled signs up exactly as before.</t>
+        </is>
+      </c>
+      <c r="G251" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H251" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I251" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J251" s="28" t="n"/>
+      <c r="K251" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-17). tests/test_signup_survives_a_slow_ai.py (9, three of them the draft invariants); browser acceptance scripts/ux_signup_resume_0917.py 12/12 — answers typed, browser thrown away, answers back, nothing created until the end — and the fresh path still 24/24.</t>
+        </is>
+      </c>
+      <c r="L251" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -5969,7 +5969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L251"/>
+  <dimension ref="A1:L256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20144,6 +20144,286 @@
         </is>
       </c>
       <c r="L251" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.05</t>
+        </is>
+      </c>
+      <c r="B252" s="28" t="inlineStr">
+        <is>
+          <t>docs/BACKEND_NOT_WIRED.md</t>
+        </is>
+      </c>
+      <c r="C252" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D252" s="28" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="E252" s="28" t="inlineStr">
+        <is>
+          <t>What is built in the backend but never reached from the app</t>
+        </is>
+      </c>
+      <c r="F252" s="28" t="inlineStr">
+        <is>
+          <t>After the signup-draft find (a whole resume mechanism sitting unused), a full sweep: 329 API routes matched against every api.* and fetch call in frontend/src, then each candidate checked a second time against the literal path (which cleared a dozen false alarms). The list is in docs/BACKEND_NOT_WIRED.md, grouped by whether a person hits a wall, a whole feature has no way in, a safety feature is unreachable, or it is small and cheap.</t>
+        </is>
+      </c>
+      <c r="G252" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H252" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I252" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J252" s="28" t="n"/>
+      <c r="K252" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-17). Findings, not fixes — the fixes are the rows below.</t>
+        </is>
+      </c>
+      <c r="L252" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.06</t>
+        </is>
+      </c>
+      <c r="B253" s="28" t="inlineStr">
+        <is>
+          <t>Login.js, App.js, routers/auth.py (built)</t>
+        </is>
+      </c>
+      <c r="C253" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D253" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E253" s="28" t="inlineStr">
+        <is>
+          <t>Forgot password, and the verify-email link that 404s</t>
+        </is>
+      </c>
+      <c r="F253" s="28" t="inlineStr">
+        <is>
+          <t>POST /auth/password/forgot and /reset are built with tokens and emails; the sign-in screen has no link and there is no reset page, so someone without a mobile number on file cannot get back in. Registration emails {APP_BASE_URL}/verify-email?token=... and App.js has no such route, so that link lands on a 404. /auth/email/send-verification (re-send from Settings) is unused too.</t>
+        </is>
+      </c>
+      <c r="G253" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H253" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I253" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J253" s="28" t="n"/>
+      <c r="K253" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-17 by the backend-vs-frontend sweep. A link and a page.</t>
+        </is>
+      </c>
+      <c r="L253" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.07</t>
+        </is>
+      </c>
+      <c r="B254" s="28" t="inlineStr">
+        <is>
+          <t>Login.js, AuthContext.js, routers/auth.py (built)</t>
+        </is>
+      </c>
+      <c r="C254" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D254" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E254" s="28" t="inlineStr">
+        <is>
+          <t>A person in two workspaces cannot reach the second</t>
+        </is>
+      </c>
+      <c r="F254" s="28" t="inlineStr">
+        <is>
+          <t>Memberships are per workspace; GET /auth/me/workspaces and POST /auth/me/switch-workspace exist; /auth/login answers {ambiguous: true, choices: [...]} when one person belongs to several. The frontend calls neither and does not handle that answer, so they are stuck in whichever workspace login picks — the consultant-with-two-clients case the phone routing was built around.</t>
+        </is>
+      </c>
+      <c r="G254" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H254" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I254" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J254" s="28" t="n"/>
+      <c r="K254" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-17 by the backend-vs-frontend sweep.</t>
+        </is>
+      </c>
+      <c r="L254" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.08</t>
+        </is>
+      </c>
+      <c r="B255" s="28" t="inlineStr">
+        <is>
+          <t>Brain.js / a notes view, GET /api/memory (built)</t>
+        </is>
+      </c>
+      <c r="C255" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D255" s="28" t="inlineStr">
+        <is>
+          <t>Company Brain</t>
+        </is>
+      </c>
+      <c r="E255" s="28" t="inlineStr">
+        <is>
+          <t>The company's own notes are written and never shown</t>
+        </is>
+      </c>
+      <c r="F255" s="28" t="inlineStr">
+        <is>
+          <t>GET/POST /api/memory holds the plain notes a company keeps. The Decision Desk writes them — a capture that is news rather than a decision now answers 'Kept in the Company Brain' — and nothing in the app lists them. The promise is kept in the database and broken on screen.</t>
+        </is>
+      </c>
+      <c r="G255" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H255" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I255" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J255" s="28" t="n"/>
+      <c r="K255" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-17. Note: the writing half shipped 2026-09-16 (U7-23.29).</t>
+        </is>
+      </c>
+      <c r="L255" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.09</t>
+        </is>
+      </c>
+      <c r="B256" s="28" t="inlineStr">
+        <is>
+          <t>App.js /meetings redirect, routers/meetings.py (built)</t>
+        </is>
+      </c>
+      <c r="C256" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D256" s="28" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="E256" s="28" t="inlineStr">
+        <is>
+          <t>Meetings: a whole feature behind a redirect</t>
+        </is>
+      </c>
+      <c r="F256" s="28" t="inlineStr">
+        <is>
+          <t>POST /meetings (audio) and /meetings/text transcribe a meeting, summarise it and turn its action items into tasks; GET /meetings lists them. The app's /meetings route redirects to the home page, so nothing records a meeting and nothing shows one.</t>
+        </is>
+      </c>
+      <c r="G256" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H256" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I256" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J256" s="28" t="n"/>
+      <c r="K256" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-17 by the backend-vs-frontend sweep.</t>
+        </is>
+      </c>
+      <c r="L256" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-17</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1557,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 64 of 153 items Done  (42%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 13 of 15 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 12 of 13 Done.</t>
+          <t>Epic 6 progress: 163 of 256 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 6 of 10 Done.</t>
         </is>
       </c>
     </row>
@@ -2332,14 +2332,14 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" t="n">
         <v>18</v>
       </c>
-      <c r="D27" t="n">
-        <v>21</v>
-      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2383,6 +2383,39 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>Settings / Team / RBAC review (docs/SETTINGS_RBAC_REVIEW.md), 2026-09-15: capture approval respects the decider, files and checklist follow the task rules, Manage team cannot raise access, Money card for owners only, remove a member with hand-over, manage access by role. P1 (2026-09-16): AI processing section, approval rules removed, edit name/email, welcome message, Team tile, No access, People access for CRM, no self-approval, real access everywhere, decisions list. P2 (2026-09-16): Workspace tab, overdue work days, while-you're-away delegation, Settings/Team tidy-up, reassign/hand-off/dictation rules. Re-checked after Sakthivel's Team redesign (8b60707): invited members could not use the app at all (a pending membership was never accepted) — fixed; an invite link kept its OTP cooldown; the audit scripts follow the new Team canvas. Only an owner changes a teammate's mobile (it is the sign-in), and a person keeps their own details — name, job title, what they handle, mobile, email — without a manager. Finance is one permission (the second Ledger toggle promised a wall nothing enforced; merged, with a boot migration so nobody loses the page).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sprint 24</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Onboarding + auth (signup, forgot password)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), and forgetting a password now has a screen. Open: the verify-email 404, the workspace picker, the company's own notes, Meetings.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L256"/>
+  <dimension ref="A1:L257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20213,7 +20246,7 @@
       </c>
       <c r="B253" s="28" t="inlineStr">
         <is>
-          <t>Login.js, App.js, routers/auth.py (built)</t>
+          <t>PasswordReset.js (new), App.js, Login.js, routers/auth.py (built)</t>
         </is>
       </c>
       <c r="C253" s="28" t="n">
@@ -20226,12 +20259,12 @@
       </c>
       <c r="E253" s="28" t="inlineStr">
         <is>
-          <t>Forgot password, and the verify-email link that 404s</t>
+          <t>Forgetting a password has a screen</t>
         </is>
       </c>
       <c r="F253" s="28" t="inlineStr">
         <is>
-          <t>POST /auth/password/forgot and /reset are built with tokens and emails; the sign-in screen has no link and there is no reset page, so someone without a mobile number on file cannot get back in. Registration emails {APP_BASE_URL}/verify-email?token=... and App.js has no such route, so that link lands on a 404. /auth/email/send-verification (re-send from Settings) is unused too.</t>
+          <t>POST /auth/password/forgot and /auth/password/reset shipped with FIX-003-D — tokens, one-hour TTL, single use, sibling links revoked on success, and an answer that is identical whether or not the address is registered. Every part a person touches was missing: the sign-in screen had no link, /reset-password was not a route, and so the link in every reset email we had ever sent landed on a 404. Someone who forgot their password and had no mobile number on file could not get back in at all. Now: 'Forgot your password?' sits under the Sign in button; /forgot-password asks for the link and answers the same way for an address we know and one we do not (the API's promise, kept in the copy) and points a mobile-OTP member at the door that does open, because they have no password to reset; /reset-password sets the new one, checks the six-character floor and the confirmation before the round trip, and a link that is spent, expired or half-copied offers a new one instead of a form that keeps failing. Both forms write their own error line rather than handing the moment to the browser's bubble.</t>
         </is>
       </c>
       <c r="G253" s="28" t="inlineStr">
@@ -20246,13 +20279,13 @@
       </c>
       <c r="I253" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J253" s="28" t="n"/>
       <c r="K253" s="28" t="inlineStr">
         <is>
-          <t>Found 2026-09-17 by the backend-vs-frontend sweep. A link and a page.</t>
+          <t>SHIPPED (this push, 2026-09-17). tests/test_forgot_password_has_a_screen.py (9) guards the seam that broke — the path in the reset email has to be a route App.js serves — plus the no-enumeration copy and the dead-link escape; the token model itself is covered by tests/test_email_verification_and_reset.py. Browser acceptance on a throwaway DB: scripts/ux_forgot_password_0917.py, 17/17 — registers a workspace, walks the link from the sign-in page, refuses a malformed address, proves an unknown address gets the identical answer, requests the real link, reads the token the way the email would carry it, sets the new password, then signs in (401 with the old, 200 with the new) and finds the spent link refused.</t>
         </is>
       </c>
       <c r="L253" s="28" t="inlineStr">
@@ -20424,6 +20457,62 @@
         </is>
       </c>
       <c r="L256" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.10</t>
+        </is>
+      </c>
+      <c r="B257" s="28" t="inlineStr">
+        <is>
+          <t>App.js /verify-email (missing), Settings.js, routers/auth.py (built)</t>
+        </is>
+      </c>
+      <c r="C257" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D257" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E257" s="28" t="inlineStr">
+        <is>
+          <t>The verification link in every registration email is a 404</t>
+        </is>
+      </c>
+      <c r="F257" s="28" t="inlineStr">
+        <is>
+          <t>Split out of U7-24.06 when the reset half shipped. Registration emails {APP_BASE_URL}/verify-email?token=… and App.js has no such route, so that link has always landed on a 404 — the endpoint behind it is GET /auth/email/verify/{token}, built, single-use, three-day TTL. POST /auth/email/send-verification (re-send) is unused too, and nothing in the app reads email_verified_at, so a founder is never told the address is unconfirmed and has no way to ask for another link. Same shape of work as the reset screens: a page that spends the token, a dead-link escape, and a line in Settings that says the email is unverified with a button to re-send.</t>
+        </is>
+      </c>
+      <c r="G257" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H257" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I257" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J257" s="28" t="n"/>
+      <c r="K257" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-17 by the backend-vs-frontend sweep; the other half of the original U7-24.06.</t>
+        </is>
+      </c>
+      <c r="L257" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-17</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 163 of 256 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 6 of 10 Done.</t>
+          <t>Epic 6 progress: 164 of 256 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 7 of 10 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
         <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), and forgetting a password now has a screen. Open: the verify-email 404, the workspace picker, the company's own notes, Meetings.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), and both inbox errands now have screens — forgetting a password, and confirming an email. Open: the workspace picker, the company's own notes, Meetings.</t>
         </is>
       </c>
     </row>
@@ -20470,7 +20470,7 @@
       </c>
       <c r="B257" s="28" t="inlineStr">
         <is>
-          <t>App.js /verify-email (missing), Settings.js, routers/auth.py (built)</t>
+          <t>EmailVerify.js (new), components/auth/AuthShell.js (new), App.js, ProfileDialog.js, routers/auth.py (built)</t>
         </is>
       </c>
       <c r="C257" s="28" t="n">
@@ -20483,12 +20483,12 @@
       </c>
       <c r="E257" s="28" t="inlineStr">
         <is>
-          <t>The verification link in every registration email is a 404</t>
+          <t>Confirming an email has a screen</t>
         </is>
       </c>
       <c r="F257" s="28" t="inlineStr">
         <is>
-          <t>Split out of U7-24.06 when the reset half shipped. Registration emails {APP_BASE_URL}/verify-email?token=… and App.js has no such route, so that link has always landed on a 404 — the endpoint behind it is GET /auth/email/verify/{token}, built, single-use, three-day TTL. POST /auth/email/send-verification (re-send) is unused too, and nothing in the app reads email_verified_at, so a founder is never told the address is unconfirmed and has no way to ask for another link. Same shape of work as the reset screens: a page that spends the token, a dead-link escape, and a line in Settings that says the email is unverified with a button to re-send.</t>
+          <t>The other half of U7-24.06, and the same shape of fault. Registration has emailed {APP_BASE_URL}/verify-email?token=… since FIX-003-D and App.js had no such route, so the link in every welcome email this product has ever sent landed on a 404; POST /auth/email/send-verification had no caller anywhere; and nothing in the app read email_verified_at, so nobody was ever told the address was unconfirmed or given a way to ask for another link. Now: /verify-email spends the token where the endpoint actually takes it (GET /auth/email/verify/{token} — a path parameter, not the query the link carries), names the address it confirmed, and ends where the person came from: the way home if they are signed in, the sign-in door if they are not. A spent or expired link offers a fresh one to someone signed in and says where to get one to someone who is not, because the re-send emails the address on the account rather than one typed into a page. An email that is already confirmed says so instead of 'this link won't work'. Settings › Your Profile carries the state under the sign-in address — Confirmed, or 'Not confirmed yet' with a Send the link button — about the SAVED address, not a half-typed new one. Two traps kept clear: the token is single-use and StrictMode runs an effect twice (a ref guard, or our own dev server condemns a good link), and the already-confirmed verdict waits for /auth/me instead of flashing the wrong heading. The card both inbox errands wear moved to components/auth/AuthShell.js.</t>
         </is>
       </c>
       <c r="G257" s="28" t="inlineStr">
@@ -20503,13 +20503,13 @@
       </c>
       <c r="I257" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J257" s="28" t="n"/>
       <c r="K257" s="28" t="inlineStr">
         <is>
-          <t>Found 2026-09-17 by the backend-vs-frontend sweep; the other half of the original U7-24.06.</t>
+          <t>SHIPPED (this push, 2026-09-17). tests/test_verify_email_has_a_screen.py (11): the link the email builds has to be a route App.js serves, the screen calls the endpoint that exists (path parameter, not query), the StrictMode guard, the verdict waiting for the account, the re-send still requiring a signed-in account, and the Settings state. Browser acceptance on a throwaway DB: scripts/ux_verify_email_0917.py, 21/21 — registers a workspace, checks nothing is confirmed, walks a half-copied link, takes a fresh link from the page's own button, confirms from the real one signed out, finds the link spent, sees 'Already confirmed' signed in, reads both Settings states, sends another link from Settings and confirms with it. Also re-ran ux_forgot_password_0917.py (17/17) after the shell moved out of PasswordReset.js.</t>
         </is>
       </c>
       <c r="L257" s="28" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 164 of 256 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 7 of 10 Done.</t>
+          <t>Epic 6 progress: 167 of 261 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 10 of 15 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), and both inbox errands now have screens — forgetting a password, and confirming an email. Open: the workspace picker, the company's own notes, Meetings.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace. Open: the workspace picker on email sign-in, the company's own notes, Meetings, confirming a mobile changed in Settings, OTP in the Flutter app.</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L257"/>
+  <dimension ref="A1:L262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20515,6 +20515,281 @@
       <c r="L257" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.11</t>
+        </is>
+      </c>
+      <c r="B258" s="28" t="inlineStr">
+        <is>
+          <t>BasicsFlow.js, lib/phone.js, routers/signup.py, services/auth/phone_proof.py, routers/auth.py</t>
+        </is>
+      </c>
+      <c r="C258" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D258" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E258" s="28" t="inlineStr">
+        <is>
+          <t>The founder's mobile is confirmed before it is trusted</t>
+        </is>
+      </c>
+      <c r="F258" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: the email is the business address; the mobile is how the founder signs in on the mobile app, so it is required and has to be right. Step 05 was optional with an '8 digits' check and the backend stored whatever arrived - but the number is a sign-in (Mobile OTP) and a route (WhatsApp from it lands as that person). A slip locked the founder out of Mobile OTP and handed whoever owns the mistyped number an OTP sign-in as the OWNER, with their WhatsApp filed as the owner's captures. Now: required; a real Indian mobile (10 digits, 6-9, +91/91/0 prefixes; one rule in phone.py and phone.js); confirmed by a texted code at the step (wrong codes refused and counted, resend after 30s, Change number); /signup/phone/verify issues a 24h proof for that exact number on a key derived from the session secret; /auth/register refuses a phone without it (phone_unverified) or one that cannot be a mobile (phone_invalid), stores '+91 98765 43210' and marks phone_verified_at. The proof rides the draft, so a resumed signup isn't texted twice; a proof that lapses on the last screen offers 'Confirm my mobile' and returns to the built OS. The public send-code endpoint is capped at 5 codes/hour per NUMBER on top of the per-network limits.</t>
+        </is>
+      </c>
+      <c r="G258" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H258" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I258" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K258" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-19). tests/test_founder_mobile_is_confirmed.py (34), fake gateway - nothing texted. Browser: scripts/ux_founder_mobile_0919.py 29/29 on a throwaway DB (bad numbers refused, wrong code refused, resume not re-texted, owner stored with the confirmed number, Mobile OTP sign-in, two-workspace picker). ux_signup_0917.py updated for the required step and re-run 24/24.</t>
+        </is>
+      </c>
+      <c r="L258" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.12</t>
+        </is>
+      </c>
+      <c r="B259" s="28" t="inlineStr">
+        <is>
+          <t>Login.js, AuthContext.js, routers/auth_otp.py (built)</t>
+        </is>
+      </c>
+      <c r="C259" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D259" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E259" s="28" t="inlineStr">
+        <is>
+          <t>Mobile OTP asks which workspace, instead of claiming a code was sent</t>
+        </is>
+      </c>
+      <c r="F259" s="28" t="inlineStr">
+        <is>
+          <t>/auth/otp/request sends NOTHING for a number registered in two workspaces and answers with the list. The sign-in page ignored the list, showed 'OTP sent to your mobile' and the code boxes, and waited for a text that was never coming; verify then answered 409. Now it asks 'Which one are you signing in to?' (the workspaces are the buttons), texts the code for the one chosen, and verify names that workspace. Invite sign-ins carry their workspace through resend and verify too. Sakthivel's migration found shared numbers in the production dump.</t>
+        </is>
+      </c>
+      <c r="G259" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H259" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I259" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K259" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-19). Covered by ux_founder_mobile_0919.py (picker, choice, signed into the chosen workspace) and the screen guards in test_founder_mobile_is_confirmed.py.</t>
+        </is>
+      </c>
+      <c r="L259" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19, from checking the OTP workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.13</t>
+        </is>
+      </c>
+      <c r="B260" s="28" t="inlineStr">
+        <is>
+          <t>services/otp.py</t>
+        </is>
+      </c>
+      <c r="C260" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D260" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E260" s="28" t="inlineStr">
+        <is>
+          <t>The Twilio fallback texted the number as it was typed</t>
+        </is>
+      </c>
+      <c r="F260" s="28" t="inlineStr">
+        <is>
+          <t>_issue_otp handed Twilio the display number, so '98765 43210' - how most people write it - was refused (Twilio needs E.164) and nobody got a code. It now sends '+91' + the ten digits. The APM gateway, the live provider, already used the ten digits and was unaffected.</t>
+        </is>
+      </c>
+      <c r="G260" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H260" s="28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I260" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K260" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-19). test_twilio_is_handed_an_e164_number_not_what_was_typed.</t>
+        </is>
+      </c>
+      <c r="L260" s="28" t="inlineStr">
+        <is>
+          <t>Found checking the OTP workflow, 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.14</t>
+        </is>
+      </c>
+      <c r="B261" s="28" t="inlineStr">
+        <is>
+          <t>ProfileDialog.js, routers/auth.py update_profile</t>
+        </is>
+      </c>
+      <c r="C261" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D261" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E261" s="28" t="inlineStr">
+        <is>
+          <t>Changing your own mobile in Settings is saved on trust</t>
+        </is>
+      </c>
+      <c r="F261" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Your Profile saves a new mobile after checking only that nobody else in the workspace has it - the U7-24.11 hole, after signup: a slip locks you out of Mobile OTP and gives the stranger with that number a sign-in as you. Fix: text a code to the NEW number and save it only once it is confirmed, the way signup now does; apply the same Indian-mobile rule (today a 5-digit number saves).</t>
+        </is>
+      </c>
+      <c r="G261" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H261" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I261" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K261" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-19 while checking the whole phone workflow; not changed in this push.</t>
+        </is>
+      </c>
+      <c r="L261" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.15</t>
+        </is>
+      </c>
+      <c r="B262" s="28" t="inlineStr">
+        <is>
+          <t>mobile/lib/screens/auth/login_screen.dart (Flutter)</t>
+        </is>
+      </c>
+      <c r="C262" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D262" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E262" s="28" t="inlineStr">
+        <is>
+          <t>The Flutter app has no Mobile OTP sign-in</t>
+        </is>
+      </c>
+      <c r="F262" s="28" t="inlineStr">
+        <is>
+          <t>The native app signs in with email and password only (auth_repository.dart has no OTP call). Mobile OTP works on the web and the installed web app. When the Flutter app resumes, it needs the request -&gt; workspace choice -&gt; verify flow the web now has.</t>
+        </is>
+      </c>
+      <c r="G262" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H262" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I262" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K262" s="28" t="inlineStr">
+        <is>
+          <t>Flutter is on hold; recorded so the mobile-login promise is not assumed to cover it.</t>
+        </is>
+      </c>
+      <c r="L262" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-19</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 167 of 261 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 10 of 15 Done.</t>
+          <t>Epic 6 progress: 168 of 261 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 11 of 15 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29" t="n">
         <v>15</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace. Open: the workspace picker on email sign-in, the company's own notes, Meetings, confirming a mobile changed in Settings, OTP in the Flutter app.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app.</t>
         </is>
       </c>
     </row>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="B261" s="28" t="inlineStr">
         <is>
-          <t>ProfileDialog.js, routers/auth.py update_profile</t>
+          <t>ProfileDialog.js, routers/auth.py (update_profile + POST /auth/phone/send-code), models/auth.py</t>
         </is>
       </c>
       <c r="C261" s="28" t="n">
@@ -20704,12 +20704,12 @@
       </c>
       <c r="E261" s="28" t="inlineStr">
         <is>
-          <t>Changing your own mobile in Settings is saved on trust</t>
+          <t>Changing your own mobile is confirmed by a code to the new number</t>
         </is>
       </c>
       <c r="F261" s="28" t="inlineStr">
         <is>
-          <t>Settings &gt; Your Profile saves a new mobile after checking only that nobody else in the workspace has it - the U7-24.11 hole, after signup: a slip locks you out of Mobile OTP and gives the stranger with that number a sign-in as you. Fix: text a code to the NEW number and save it only once it is confirmed, the way signup now does; apply the same Indian-mobile rule (today a 5-digit number saves).</t>
+          <t>Settings &gt; Your Profile saved a new mobile after checking only that nobody else in the workspace had it - the U7-24.11 hole after signup: a slip locked you out of Mobile OTP and gave the stranger with that number a sign-in as you, with their WhatsApp filed as yours; a 5-digit number saved too. Now POST /auth/phone/send-code (signed-in only) texts the NEW number after the checks Save would make (a real Indian mobile, actually different, not a colleague's), capped per person and per number; PATCH /auth/profile saves a new number only with that code (phone_unconfirmed / phone_invalid otherwise), stores '+91 98765 43210', marks phone_verified_at and re-enables WhatsApp matching. The old number keeps working until the save. The code has its own scope (a sign-in code can't confirm a change; a change code can't sign in) and is checked last, so a refusal elsewhere in the form doesn't spend it. The same number written differently is not a change; an old malformed number rides along until changed; a mobile-only member can change their number but not remove it. Also: the email-change code for a mobile-only member now goes to the number on file (what the server checks), not whatever is in the phone box.</t>
         </is>
       </c>
       <c r="G261" s="28" t="inlineStr">
@@ -20724,12 +20724,12 @@
       </c>
       <c r="I261" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K261" s="28" t="inlineStr">
         <is>
-          <t>Found 2026-09-19 while checking the whole phone workflow; not changed in this push.</t>
+          <t>SHIPPED (this push, 2026-09-19). tests/test_own_mobile_change_is_confirmed.py (19, fake gateway - nothing texted); test_own_profile_and_phone.py updated. Browser: scripts/ux_own_mobile_0919.py 15/15 on a throwaway DB - 5-digit refused, colleague's number refused before texting, Save without the code changes nothing, the code saves it, other edits need no code, the old number stops signing in and the new one signs in by Mobile OTP.</t>
         </is>
       </c>
       <c r="L261" s="28" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 168 of 261 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 11 of 15 Done.</t>
+          <t>Epic 6 progress: 170 of 264 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 13 of 18 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, and new passwords are 8+ with a letter and a number. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app, slow saves while AI calls run.</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L262"/>
+  <dimension ref="A1:L265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20788,6 +20788,171 @@
         </is>
       </c>
       <c r="L262" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.16</t>
+        </is>
+      </c>
+      <c r="B263" s="28" t="inlineStr">
+        <is>
+          <t>Team.js, routers/team.py, routers/auth_otp.py, routers/auth.py, WelcomeMemberCard.js, OwnerCredentialsGate.js, Login.js, bootstrap/lifecycle.py</t>
+        </is>
+      </c>
+      <c r="C263" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D263" s="28" t="inlineStr">
+        <is>
+          <t>Team / Auth</t>
+        </is>
+      </c>
+      <c r="E263" s="28" t="inlineStr">
+        <is>
+          <t>Members sign in by mobile; owners have both</t>
+        </is>
+      </c>
+      <c r="F263" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: a manager or HR person adds each member on Team and the member makes the account their own. The loop was half built: a 'temporary' password nothing asked the member to replace (the manager kept a way in), OTP-only members who could never add a password, the mobile never marked confirmed, a Team form taking any 10+ digits, plain Mobile OTP opening a just-invited account to whoever held a mistyped number, and a first sign-in straight onto the Desk. Now (Yokesh's call): members sign in with their mobile only, owners with email+password and mobile. Team &gt; Add member: no password, no toggle; mobile required and a real Indian mobile; email optional (users.email is now a partial unique index). The first sign-in goes through the invite link - until then the number alone opens nothing (403 'Open the invite link...', nobody texted). OTP sign-in marks phone_verified_at; the first time, a one-time welcome card confirms the mobile and asks for name, job title, what they handle and an optional email (one request; Save or Later). A mobile-only member's email is contact detail and needs no code. Someone added as, or promoted to, owner is asked for an email and password at their next sign-in, before anything else.</t>
+        </is>
+      </c>
+      <c r="G263" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H263" s="28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I263" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K263" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-19). tests/test_member_loop.py (38); test_invite_accept.py and test_own_profile_and_phone.py updated to the new rules. Browser: scripts/ux_member_loop_0919.py 26/26 with an owner's and a member's session on a throwaway DB. Earlier walks re-run: ux_own_mobile 15/15, ux_founder_mobile 29/29. Live-HTTP iteration suites that create password members (skipped in CI) were not updated.</t>
+        </is>
+      </c>
+      <c r="L263" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.17</t>
+        </is>
+      </c>
+      <c r="B264" s="28" t="inlineStr">
+        <is>
+          <t>services/auth/passwords.py, lib/password.js, BasicsFlow.js, PasswordReset.js, ProfileDialog.js</t>
+        </is>
+      </c>
+      <c r="C264" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D264" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E264" s="28" t="inlineStr">
+        <is>
+          <t>A new password is 8+ characters with a letter and a number</t>
+        </is>
+      </c>
+      <c r="F264" s="28" t="inlineStr">
+        <is>
+          <t>'At least 6 characters' allowed '123456' on the owner's account. The rule is now checked wherever a password is chosen - signup, reset (before the link is spent), change, and an owner setting one - never at sign-in, so existing passwords keep working until changed. One rule in passwords.py and password.js.</t>
+        </is>
+      </c>
+      <c r="G264" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H264" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I264" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K264" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-19). Covered in test_member_loop.py and ux_member_loop_0919.py.</t>
+        </is>
+      </c>
+      <c r="L264" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.18</t>
+        </is>
+      </c>
+      <c r="B265" s="28" t="inlineStr">
+        <is>
+          <t>backend (to be found)</t>
+        </is>
+      </c>
+      <c r="C265" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D265" s="28" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E265" s="28" t="inlineStr">
+        <is>
+          <t>Saves wait several seconds while the Desk's AI calls run</t>
+        </is>
+      </c>
+      <c r="F265" s="28" t="inlineStr">
+        <is>
+          <t>Seen in the member-loop browser runs: a profile save and the owner-credentials save each took 6-8 s (one run ~30 s) while the Desk behind them was loading its AI calls; nothing slow in those handlers. Not investigated - find whether AI work is holding up other requests on the server.</t>
+        </is>
+      </c>
+      <c r="G265" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H265" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I265" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K265" s="28" t="inlineStr">
+        <is>
+          <t>Observed 2026-09-19; not changed.</t>
+        </is>
+      </c>
+      <c r="L265" s="28" t="inlineStr">
         <is>
           <t>Found 2026-09-19</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 170 of 264 items Done  (64%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 13 of 18 Done.</t>
+          <t>Epic 6 progress: 171 of 265 items Done  (65%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 14 of 19 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L265"/>
+  <dimension ref="A1:L266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20955,6 +20955,61 @@
       <c r="L265" s="28" t="inlineStr">
         <is>
           <t>Found 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.19</t>
+        </is>
+      </c>
+      <c r="B266" s="28" t="inlineStr">
+        <is>
+          <t>Team.js (member form + profile), routers/team.py update_user</t>
+        </is>
+      </c>
+      <c r="C266" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D266" s="28" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="E266" s="28" t="inlineStr">
+        <is>
+          <t>A member's email is contact detail on Team, too</t>
+        </is>
+      </c>
+      <c r="F266" s="28" t="inlineStr">
+        <is>
+          <t>Found checking the Add member form in the browser (owner and a Manage-team manager). Required: name, a real Indian mobile, department (pre-selected). Optional: email, job title, reports to; access defaults to the department's. Email is saved (lowercased) and shown on the profile, the card and in search. Five things were in the way, all fixed: (1) a manager could set a member's email when adding them but not fix it later - the box was owner-only and the server said 'it's how they sign in'; now whoever manages the team may add, fix or clear the email of a member who signs in by mobile, and an email someone signs in with (a password account) stays an owner's call; (2) nobody could remove a member's email - now it can be cleared (stored as absent, not empty), except an email someone signs in with; (3) a bad email was only caught by the server after Save - now flagged under the field, like the mobile; (4) a member without an email got an empty Email box on their profile - now 'Not added'; (5) a stale comment said the email was how members sign in. A changed email is marked unconfirmed.</t>
+        </is>
+      </c>
+      <c r="G266" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H266" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I266" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K266" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED (this push, 2026-09-19). tests/test_member_loop.py +3; browser: scripts/ux_member_email_0919.py 11/11 as a manager on a throwaway DB (profile 'Not added', email box open to them, bad email flagged before Save and not saved, email saved, email removed).</t>
+        </is>
+      </c>
+      <c r="L266" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 171 of 265 items Done  (65%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 14 of 19 Done.</t>
+          <t>Epic 6 progress: 172 of 265 items Done  (65%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 15 of 19 Done.</t>
         </is>
       </c>
     </row>
@@ -2397,15 +2397,19 @@
           <t>Onboarding + auth (signup, forgot password)</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>14</v>
-      </c>
-      <c r="D29" t="n">
-        <v>19</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2415,7 +2419,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, and new passwords are 8+ with a letter and a number. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app, slow saves while AI calls run.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app.</t>
         </is>
       </c>
     </row>
@@ -20911,7 +20915,7 @@
       </c>
       <c r="B265" s="28" t="inlineStr">
         <is>
-          <t>backend (to be found)</t>
+          <t>core/deps.py, database.py, routers/desk.py, routers/auth.py</t>
         </is>
       </c>
       <c r="C265" s="28" t="n">
@@ -20929,7 +20933,7 @@
       </c>
       <c r="F265" s="28" t="inlineStr">
         <is>
-          <t>Seen in the member-loop browser runs: a profile save and the owner-credentials save each took 6-8 s (one run ~30 s) while the Desk behind them was loading its AI calls; nothing slow in those handlers. Not investigated - find whether AI work is holding up other requests on the server.</t>
+          <t>Seen in the member-loop browser runs: a profile save and the owner-credentials save each took 6-8 s (one run ~30 s) while the Desk behind them was loading. Measured 2026-09-19 on a throwaway database against the remote Mongo (~205 ms a round trip): the AI calls were not the cause and the event loop was not blocked (GET /api/health stayed ~10 ms throughout). The time went on database round trips made one after another, queued on a connection pool that could not grow: every signed-in request made six lookups in a row before its handler ran (~1.45 s for a bare /auth/me), /desk/summary made nine counts in a row (~7 s), and PyMongo opened only 2 connections at a time, so the Desk's dozen requests shared 3-4 connections. Now the sign-in lookups run side by side (2 round trips, not 6), the Desk summary's counters run side by side, up to 16 connections open at once (MONGO_MAX_CONNECTING), and the owner-credentials bcrypt runs off the event loop.</t>
         </is>
       </c>
       <c r="G265" s="28" t="inlineStr">
@@ -20944,12 +20948,12 @@
       </c>
       <c r="I265" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K265" s="28" t="inlineStr">
         <is>
-          <t>Observed 2026-09-19; not changed.</t>
+          <t>SHIPPED (this push, 2026-09-19). Same browser journey, before -&gt; after (2 runs): welcome-card save 6.8 s -&gt; 4.1-4.5 s, owner-credentials save 9.4 s -&gt; 5.5-5.9 s (server side 2.9 s -&gt; 2.5 s, no loop stall), /auth/me under Desk load median 1.46 s -&gt; 0.69 s, /desk/summary 7.1 s -&gt; 4.9-6.0 s (the rest is its AI narrative). What is left is the browser's 6-connections-per-host limit on local http (the save queues behind the Desk's requests), the follow-up /auth/me, and the saves' own round trips. tests/test_u7_24_18_desk_load_latency.py (11; the 5 timing tests fail on the old code). Full suite 1558 passed.</t>
         </is>
       </c>
       <c r="L265" s="28" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 172 of 265 items Done  (65%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 15 of 19 Done.</t>
+          <t>Epic 6 progress: 176 of 269 items Done  (65%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 19 of 23 Done.</t>
         </is>
       </c>
     </row>
@@ -2397,19 +2397,15 @@
           <t>Onboarding + auth (signup, forgot password)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="C29" t="n">
+        <v>19</v>
+      </c>
+      <c r="D29" t="n">
+        <v>23</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2419,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back.</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L266"/>
+  <dimension ref="A1:L270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21012,6 +21008,226 @@
         </is>
       </c>
       <c r="L266" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.20</t>
+        </is>
+      </c>
+      <c r="B267" s="28" t="inlineStr">
+        <is>
+          <t>Workflows.js, routers/workflows.py (GET /workflows/counts)</t>
+        </is>
+      </c>
+      <c r="C267" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D267" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E267" s="28" t="inlineStr">
+        <is>
+          <t>Every pipeline says how many workflows it holds</t>
+        </is>
+      </c>
+      <c r="F267" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: the count only showed when he clicked, and the PWA listed none. The board loads one pipeline at a time and every pipeline's count was taken from that one list, so the pipeline on screen showed its number and every other one showed 0 - on the desktop pills and in the phone's pipeline menu - and the phone's header named the pipeline without a count. GET /workflows/counts returns every pipeline's count in one grouped query; the pills, the phone menu and the phone header read it and refresh on add/move/delete.</t>
+        </is>
+      </c>
+      <c r="G267" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H267" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I267" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K267" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 620c5c5 (2026-09-19). tests/test_workflow_counts.py (3); scripts/ux_workflow_counts_0919.py reproduced it (4/6 failing) then 6/6 on desktop and phone. Full suite 1547 passed.</t>
+        </is>
+      </c>
+      <c r="L267" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.21</t>
+        </is>
+      </c>
+      <c r="B268" s="28" t="inlineStr">
+        <is>
+          <t>Leave.js, App.js /leave, AllAppsPanel.jsx, MyWork.js, lib/notif.js</t>
+        </is>
+      </c>
+      <c r="C268" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D268" s="28" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="E268" s="28" t="inlineStr">
+        <is>
+          <t>Leave has a page of your own again</t>
+        </is>
+      </c>
+      <c r="F268" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: on the PWA, Leave redirected to Team; it has to go to a leave section to raise a request and see the history - no approval section there (that is in Approvals); on desktop, a Request Leave button in My Work. ASK-6 had retired /leave to Team, so a phone had no way to ask for time off. /leave is the requester's side: Request Leave, Report Absence Today, a summary (waiting, days off this year, requests), 'Coming up and waiting' and History. More &gt; Leave opens it; My Work's desktop toolbar has Request Leave beside New task. A notification about your own request opens it on /leave, highlighted, instead of the approvers' queue.</t>
+        </is>
+      </c>
+      <c r="G268" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H268" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I268" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K268" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED fe25b43 (2026-09-19). tests/test_leave_page.py (5); scripts/ux_leave_0919.py 13/13 as the Sales member on phone and desktop. Full suite 1552 passed.</t>
+        </is>
+      </c>
+      <c r="L268" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.22</t>
+        </is>
+      </c>
+      <c r="B269" s="28" t="inlineStr">
+        <is>
+          <t>routers/team.py (respond, withdraw), Leave.js, Team.js, lib/notif.js</t>
+        </is>
+      </c>
+      <c r="C269" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D269" s="28" t="inlineStr">
+        <is>
+          <t>Leave</t>
+        </is>
+      </c>
+      <c r="E269" s="28" t="inlineStr">
+        <is>
+          <t>Answer the approver's question, and withdraw a leave request</t>
+        </is>
+      </c>
+      <c r="F269" s="28" t="inlineStr">
+        <is>
+          <t>An approver could ask for more info and the requester could not answer; nobody could take a request back. POST /leaves/{id}/respond: the requester answers, the request returns to Pending, the approver (and delegate) is told; only the requester, only while asked. POST /leaves/{id}/withdraw: while waiting, or approved but not yet started; kept in history as withdrawn ('cancelled', the Flutter client's name), approver told. A withdrawn request can no longer be decided (_decide_leave had no status check). Cards show the question and answer to both sides; the card updates at once from the server's reply.</t>
+        </is>
+      </c>
+      <c r="G269" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H269" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I269" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K269" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED f4620a5 (2026-09-19). tests/test_leave_reply_withdraw.py (8); scripts/ux_leave_reply_0919.py 15/15 (member on phone, owner on desktop). Full suite 1552 passed.</t>
+        </is>
+      </c>
+      <c r="L269" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.23</t>
+        </is>
+      </c>
+      <c r="B270" s="28" t="inlineStr">
+        <is>
+          <t>MyWork.js</t>
+        </is>
+      </c>
+      <c r="C270" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D270" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E270" s="28" t="inlineStr">
+        <is>
+          <t>My Work has its Workflows pill back</t>
+        </is>
+      </c>
+      <c r="F270" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: the Workflows pill in My Work was removed by mistake - bring it back. ASK-42 C (Chinmay, 2026-09-17, recorded as the founder's call) had removed the desktop circle and the phone view-menu entry when /workflows became a page; on desktop nothing else reached that page. Restored as a way IN, not a second copy of the board: a labelled Workflows pill in My Work's desktop header and a Workflows entry in the phone's view menu, both opening /workflows, gated on the workflows permission like the More tile. History of this control: KM-31 out, ASK-38 back as a circle, ASK-39 into the phone menu, ASK-42 out, now back.</t>
+        </is>
+      </c>
+      <c r="G270" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H270" s="28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I270" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K270" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-19 (this push). See the commit for the browser check.</t>
+        </is>
+      </c>
+      <c r="L270" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-19</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 176 of 269 items Done  (65%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 19 of 23 Done.</t>
+          <t>Epic 6 progress: 179 of 274 items Done  (65%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 22 of 28 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain.</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L270"/>
+  <dimension ref="A1:L275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21230,6 +21230,281 @@
       <c r="L270" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.24</t>
+        </is>
+      </c>
+      <c r="B271" s="28" t="inlineStr">
+        <is>
+          <t>services/tenant_ai_keys.py TENANT_PUBLIC; 9 routers</t>
+        </is>
+      </c>
+      <c r="C271" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D271" s="28" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E271" s="28" t="inlineStr">
+        <is>
+          <t>The owner's AI keys never reach a browser</t>
+        </is>
+      </c>
+      <c r="F271" s="28" t="inlineStr">
+        <is>
+          <t>Settings audit: /auth/me, sign-in and every settings save returned the whole tenant record, and tenant.ai_keys holds the owner's own provider keys in plain text - so every member's browser held them, though the Workspace card says keys are never shown in full. Proven on a throwaway DB (a key the owner saved came back whole in a Sales member's /auth/me). Every tenant read that answers a browser now uses TENANT_PUBLIC ({_id:0, ai_keys:0}); only the /tenant/ai-keys endpoints read the raw map, and they answer masked. A source guard fails if a router reads a whole tenant again.</t>
+        </is>
+      </c>
+      <c r="G271" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H271" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I271" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K271" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_ai_keys_stay_on_the_server.py (3); scripts/ux_settings_fixes_0920.py checks 1-3. Keys already saved should be rotated by owners who set one.</t>
+        </is>
+      </c>
+      <c r="L271" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20 (Settings audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.25</t>
+        </is>
+      </c>
+      <c r="B272" s="28" t="inlineStr">
+        <is>
+          <t>CompanyDetails.js, BusinessVocabulary.js, OperatingModelEditor.js, FinanceCategoriesEditor.js, RegenerateWithAi.js, routers/tenant_settings.py, shared/normalizers.py</t>
+        </is>
+      </c>
+      <c r="C272" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D272" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E272" s="28" t="inlineStr">
+        <is>
+          <t>Settings stops losing the owner's work</t>
+        </is>
+      </c>
+      <c r="F272" s="28" t="inlineStr">
+        <is>
+          <t>(1) Company card: its three saves each reloaded the tenant and rebuilt every section, wiping unsaved edits elsewhere in the card - a section now re-reads only while it has no unsaved edits; a product with a description but no name is refused, not dropped. (2) Regenerate with AI: the vocabulary route saved the built-in defaults over the owner's words when the AI failed (or AI was off), and all three said 'regenerated' either way - AI off is refused (451), a non-AI result keeps the data and returns an error, and each button asks first in the page. (3) Operating model save: a second pipeline/stage with the same key (and its tasks), an empty pipeline and anything past the caps were silently dropped - now refused with the reason; removing a pipeline that still has cards is refused (409). (4) The editor never loaded or sent a stage's department (voice routing uses it) - it round-trips and shows as 'Stage owner'; role pickers show team names, not keys. Vocabulary shows what was saved; errors go through formatApiError.</t>
+        </is>
+      </c>
+      <c r="G272" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H272" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I272" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K272" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_settings_audit_fixes.py (10); scripts/ux_settings_fixes_0920.py 10/10.</t>
+        </is>
+      </c>
+      <c r="L272" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20 (Settings audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.26</t>
+        </is>
+      </c>
+      <c r="B273" s="28" t="inlineStr">
+        <is>
+          <t>routers/team.py update_user, Team.js</t>
+        </is>
+      </c>
+      <c r="C273" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D273" s="28" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E273" s="28" t="inlineStr">
+        <is>
+          <t>Your own sign-in mobile and email change only in Settings</t>
+        </is>
+      </c>
+      <c r="F273" s="28" t="inlineStr">
+        <is>
+          <t>PATCH /users/{your own id} changed your own mobile with no code and an owner's own email with no password - the steps Settings &gt; Your Profile asks for (U7-24.14) - so a stolen owner session could re-point the sign-in and take the account with a reset. The route refuses a change to your own mobile or email (403, pointing to Settings); the Team form locks both on your own card and leaves them out of the save.</t>
+        </is>
+      </c>
+      <c r="G273" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H273" s="28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I273" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K273" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_settings_audit_fixes.py.</t>
+        </is>
+      </c>
+      <c r="L273" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20 (Settings audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.27</t>
+        </is>
+      </c>
+      <c r="B274" s="28" t="inlineStr">
+        <is>
+          <t>Settings (all tabs)</t>
+        </is>
+      </c>
+      <c r="C274" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D274" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E274" s="28" t="inlineStr">
+        <is>
+          <t>Settings validation pass (from the audit)</t>
+        </is>
+      </c>
+      <c r="F274" s="28" t="inlineStr">
+        <is>
+          <t>Still open from the 2026-09-20 audit: GSTIN and company-mobile format checks; company name required on the server and marked in the UI; high-value threshold 0 is accepted but treated as 50000; a member cannot clear their optional email in Settings (EmailStr 422) though Team can; owner sign-in email still editable (rule says locked) and takes effect before it is confirmed; delegation dates and delegate not validated on the server; Leave Approvers keeps choices the server dropped and offers pending invitees; no unsaved-changes guard when switching tabs; currency accepts any string; password change does not sign out other devices.</t>
+        </is>
+      </c>
+      <c r="G274" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H274" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I274" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K274" s="28" t="inlineStr">
+        <is>
+          <t>Audit report 2026-09-20.</t>
+        </is>
+      </c>
+      <c r="L274" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20 (Settings audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.28</t>
+        </is>
+      </c>
+      <c r="B275" s="28" t="inlineStr">
+        <is>
+          <t>Settings (Business, Account, Workspace)</t>
+        </is>
+      </c>
+      <c r="C275" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D275" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E275" s="28" t="inlineStr">
+        <is>
+          <t>Settings: unused fields and member-facing copy</t>
+        </is>
+      </c>
+      <c r="F275" s="28" t="inlineStr">
+        <is>
+          <t>Needs a product call: Branches, Company mobile, Products &amp; Services, Company-card task templates and the six task-type vocabulary labels are stored but never read; the business description feeds every AI generator but cannot be edited. Copy: members (mobile sign-in) see 'Password &amp; Security - change the password you use to sign in', 'Your sign-in ID' on email and 'Send the link' with no email; audit log shows 'Nothing recorded yet' when it failed to load and 'A member' for mobile users; no confirm on removing an AI key or deleting a team.</t>
+        </is>
+      </c>
+      <c r="G275" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H275" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I275" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K275" s="28" t="inlineStr">
+        <is>
+          <t>Audit report 2026-09-20.</t>
+        </is>
+      </c>
+      <c r="L275" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20 (Settings audit)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 179 of 274 items Done  (65%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 22 of 28 Done.</t>
+          <t>Epic 6 progress: 182 of 277 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 25 of 31 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain. 2026-09-20: one founder, several companies - the mobile is asked before the email and says what it already runs, a second company needs no second email or password, and the profile menu switches between them.</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L275"/>
+  <dimension ref="A1:L278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21505,6 +21505,171 @@
       <c r="L275" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-20 (Settings audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.29</t>
+        </is>
+      </c>
+      <c r="B276" s="28" t="inlineStr">
+        <is>
+          <t>routers/signup.py (/phone/verify), BasicsFlow.js, Signup.js</t>
+        </is>
+      </c>
+      <c r="C276" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D276" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E276" s="28" t="inlineStr">
+        <is>
+          <t>The mobile is asked before the email, and says what it already runs</t>
+        </is>
+      </c>
+      <c r="F276" s="28" t="inlineStr">
+        <is>
+          <t>A founder may run more than one company: the mobile is the person, the email is one per company (users.email is globally unique). The wizard asked for the email third and the mobile fifth, so a returning founder built a whole second OS before register refused the reused address at the very end. The mobile now comes third, and the moment the texted code is confirmed /signup/phone/verify answers with what that number already reaches: live workspaces (name + their role), invitations they have not opened (shown as 'open your invite link', never as a door), and their name. The step becomes a chooser - open one, or create another company - and a number nobody has used carries on to email and password exactly as before. Safe to name workspaces there because the code was just consumed; the sign-in picker's own pre-code leak is untouched.</t>
+        </is>
+      </c>
+      <c r="G276" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H276" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I276" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K276" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_second_company.py; scripts/ux_second_company_0920.py 13/13 on a throwaway DB.</t>
+        </is>
+      </c>
+      <c r="L276" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20 (multi-company onboarding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.30</t>
+        </is>
+      </c>
+      <c r="B277" s="28" t="inlineStr">
+        <is>
+          <t>routers/auth.py (register), models/auth.py, BuildReveal.js, services/whatsapp.py</t>
+        </is>
+      </c>
+      <c r="C277" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D277" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E277" s="28" t="inlineStr">
+        <is>
+          <t>A second company needs no second email or password</t>
+        </is>
+      </c>
+      <c r="F277" s="28" t="inlineStr">
+        <is>
+          <t>register takes a company created from the confirmed mobile alone: email and password are optional, and when neither is sent the phone proof names the person (identity_for_phone) and the owner row is written passwordless with no email. They sign in to it by mobile and add a business email later in Settings (owner-credentials); the full-screen owner-credentials gate stands down via credentials_elsewhere, answered the same way by register, OTP sign-in and /auth/me. A first company still needs both (400 identity_unknown). Two old traps closed with it: the same-password recovery signed a founder into their FIRST workspace and showed the reveal as though the new company existed - it now runs only when the company NAME matches, and says which company holds the address otherwise; and WhatsApp from a number in two workspaces was dropped, so the first company is marked wa_primary and keeps the line.</t>
+        </is>
+      </c>
+      <c r="G277" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H277" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I277" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K277" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_second_company.py (17 incl. wizard guards).</t>
+        </is>
+      </c>
+      <c r="L277" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20 (multi-company onboarding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.31</t>
+        </is>
+      </c>
+      <c r="B278" s="28" t="inlineStr">
+        <is>
+          <t>Layout.js (profile menu), AuthContext.js, routers/auth.py (/me/workspaces, /me/switch-workspace), Login.js</t>
+        </is>
+      </c>
+      <c r="C278" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D278" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E278" s="28" t="inlineStr">
+        <is>
+          <t>Switching between your companies</t>
+        </is>
+      </c>
+      <c r="F278" s="28" t="inlineStr">
+        <is>
+          <t>The switcher endpoints existed (FIX-004-B) and nothing used them - and they would have refused anyway: each workspace creates its own user row, so the caller's id has a membership only where they already are. Both now resolve the person by their confirmed mobile: /me/workspaces unions the membership list with the companies that number reaches (live memberships only - an unopened invite or a removed one is not a way in), and switching mints the token for the row that number holds in the target workspace. The profile menu lists the others with their role, switches, and offers 'Add a company' (/signup?add=1, which starts a clean draft). Onboarding's 'Open' sends them to sign-in with the number and workspace filled in - one fresh code, because a signup proof is not a session key.</t>
+        </is>
+      </c>
+      <c r="G278" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H278" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I278" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K278" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). Mobile sign-in already offered the picker (U7-24.14); verified end to end in scripts/ux_second_company_0920.py.</t>
+        </is>
+      </c>
+      <c r="L278" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20 (multi-company onboarding)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 182 of 277 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 25 of 31 Done.</t>
+          <t>Epic 6 progress: 186 of 281 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 29 of 35 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain. 2026-09-20: one founder, several companies - the mobile is asked before the email and says what it already runs, a second company needs no second email or password, and the profile menu switches between them.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain. 2026-09-20: one founder, several companies - the mobile is asked before the email and says what it already runs, a second company needs no second email or password, and the profile menu switches between them. Rate limits are behind RATE_LIMITS and currently OFF - switch on before launch. Signup sets no password for anyone: the confirmed mobile is the sign-in.</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L278"/>
+  <dimension ref="A1:L282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="K277" s="28" t="inlineStr">
         <is>
-          <t>SHIPPED 2026-09-20 (this push). tests/test_second_company.py (17 incl. wizard guards).</t>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_second_company.py (17 incl. wizard guards).  SUPERSEDED IN PART by U7-24.35 (2026-09-20): no company sets a password at signup now, not only the second one.</t>
         </is>
       </c>
       <c r="L277" s="28" t="inlineStr">
@@ -21670,6 +21670,226 @@
       <c r="L278" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-20 (multi-company onboarding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.32</t>
+        </is>
+      </c>
+      <c r="B279" s="28" t="inlineStr">
+        <is>
+          <t>config.py (RATE_LIMITS), services/rate_limit.py, bootstrap/middleware.py</t>
+        </is>
+      </c>
+      <c r="C279" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D279" s="28" t="inlineStr">
+        <is>
+          <t>Infra</t>
+        </is>
+      </c>
+      <c r="E279" s="28" t="inlineStr">
+        <is>
+          <t>The throughput limits answer to one switch, and it is OFF</t>
+        </is>
+      </c>
+      <c r="F279" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: 'remove the rate limit, make it off for now, write a flag.' Three workspaces an hour per network, five address checks per ten seconds, five codes an hour per number - every one of them counts a founder testing their own product as an attacker, and creating two companies in a sitting spends the register budget ('try again in about 60 minutes'). check_rate_limit now answers to config.RATE_LIMITS (off by default, RATE_LIMITS=on restores every limit unchanged), read at call time so a test can flip it. Bootstrap logs a WARNING on every start while it is off, and names the flag; a prod boot says so twice. NOT part of the switch, because they are account security rather than throughput: the sign-in lockout (5 failures per IP+email / 15 min) and the OTP's own five attempts, single use and 30s cooldown.</t>
+        </is>
+      </c>
+      <c r="G279" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H279" s="28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I279" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K279" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_ratelimit_and_lockout.py has both states plus a guard that the sign-in lockout does not go through check_rate_limit; the six tests that exist to prove the limits use the new `rate_limits_on` fixture. MUST BE SET BACK ON BEFORE LAUNCH (go-live checklist).</t>
+        </is>
+      </c>
+      <c r="L279" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.33</t>
+        </is>
+      </c>
+      <c r="B280" s="28" t="inlineStr">
+        <is>
+          <t>BasicsFlow.js (support_email step), routers/auth.py, models/tenant.py, CompanyDetails.js</t>
+        </is>
+      </c>
+      <c r="C280" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D280" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E280" s="28" t="inlineStr">
+        <is>
+          <t>A second company keeps a contact address, not a second sign-in</t>
+        </is>
+      </c>
+      <c r="F280" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: 'I just get the email for the support thing, so there's no need for the password asking.' A second company now has one optional step in place of the sign-in email and password: where support and receipts should reach them about THIS company. It is kept on the workspace (tenant.support_email), not on their account, which is what lets it be the SAME address their first company uses - a sign-in email is unique across DecisionOS, a company's contact address is not. Skippable, and editable afterwards in Settings &gt; Business &gt; Company Details, where it now appears as a field.</t>
+        </is>
+      </c>
+      <c r="G280" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H280" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I280" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K280" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_second_company.py; ux_second_company_0920.py 16/16.  The first company's address is asked the same way (U7-24.35) — support and receipts, not a sign-in.</t>
+        </is>
+      </c>
+      <c r="L280" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.34</t>
+        </is>
+      </c>
+      <c r="B281" s="28" t="inlineStr">
+        <is>
+          <t>AuthContext.js, service-worker.js, routers/auth.py (switch-workspace)</t>
+        </is>
+      </c>
+      <c r="C281" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D281" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E281" s="28" t="inlineStr">
+        <is>
+          <t>Switching company leaves nothing of the old one behind</t>
+        </is>
+      </c>
+      <c r="F281" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: 'make sure that if we switch, it should be switched - see edge cases.' Two ways the old company could have followed the founder into the new one. (1) The service worker caches API GETs by URL for 24 hours - tasks, people, invoices, even /auth/me - so a slow network (NetworkFirst gives up at 3s) would answer the new workspace's screens with the old one's data; the switch now purges that cache exactly as signing out does, from the request itself and from a message the page sends. (2) The auth cookie is one per browser, so a second tab still showing the old company was, from the moment of the switch, writing into the new one; a `storage` write tells every other tab to reload itself. The switch itself already hands over the target workspace's own row, role and token (U7-24.31), now covered by a test that reads the minted claims.</t>
+        </is>
+      </c>
+      <c r="G281" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H281" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I281" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K281" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_second_company.py (22); browser run confirms the identity changes hands (different user id) when switching.</t>
+        </is>
+      </c>
+      <c r="L281" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.35</t>
+        </is>
+      </c>
+      <c r="B282" s="28" t="inlineStr">
+        <is>
+          <t>BasicsFlow.js, Signup.js, BuildReveal.js, routers/auth.py, OwnerCredentialsGate.js</t>
+        </is>
+      </c>
+      <c r="C282" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D282" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E282" s="28" t="inlineStr">
+        <is>
+          <t>Nobody sets a password to get in — the mobile is the sign-in</t>
+        </is>
+      </c>
+      <c r="F282" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: 'after the mobile OTP we ask email and password - we don't need that password, let them log in by mobile itself.' The password step is gone from signup for EVERY company, first included: company name, your name, mobile + texted code, work email (support and receipts, no longer described as a sign-in), team size. register writes the owner passwordless and a password is optional there (an older client may still send one); an owner who wants one adds it in Settings. Three things moved with it: (1) the owner-credentials gate used to stop every mobile-only owner - it now stops only an owner with NO confirmed mobile and no password, i.e. nobody with a way in; (2) the lost-Create-press recovery was 'sign in with the password you just typed', which no longer exists - register recognises the same person by the confirmed mobile, and a stranger reusing the address still gets the wall; (3) a regression caught by the existing suite: while wiring the proof-only path the proof briefly stopped having to match the number being registered (confirm your own, type a colleague's) - restored.</t>
+        </is>
+      </c>
+      <c r="G282" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H282" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I282" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K282" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_second_company.py (24); the six suites that assumed a password at signup updated, not weakened. CONSEQUENCE TO WATCH: an owner who loses their phone and never added an email + password in Settings has no way in except a manager moving their number.</t>
+        </is>
+      </c>
+      <c r="L282" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 186 of 281 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 29 of 35 Done.</t>
+          <t>Epic 6 progress: 187 of 282 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 30 of 36 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain. 2026-09-20: one founder, several companies - the mobile is asked before the email and says what it already runs, a second company needs no second email or password, and the profile menu switches between them. Rate limits are behind RATE_LIMITS and currently OFF - switch on before launch. Signup sets no password for anyone: the confirmed mobile is the sign-in.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain. 2026-09-20: one founder, several companies - the mobile is asked before the email and says what it already runs, a second company needs no second email or password, and the profile menu switches between them. Rate limits are behind RATE_LIMITS and currently OFF - switch on before launch. Signup sets no password for anyone: the confirmed mobile is the sign-in. The mobile is the first question of all, and a signed-in founder adds a company without another code.</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L282"/>
+  <dimension ref="A1:L283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21888,6 +21888,61 @@
         </is>
       </c>
       <c r="L282" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.36</t>
+        </is>
+      </c>
+      <c r="B283" s="28" t="inlineStr">
+        <is>
+          <t>BasicsFlow.js, Signup.js, core/deps.py, routers/auth.py, Layout.js</t>
+        </is>
+      </c>
+      <c r="C283" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D283" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E283" s="28" t="inlineStr">
+        <is>
+          <t>The mobile is the first question, and a signed-in founder is not asked twice</t>
+        </is>
+      </c>
+      <c r="F283" s="28" t="inlineStr">
+        <is>
+          <t>Three asks from Yokesh after walking the flow. (1) THE NUMBER COMES FIRST. It was asked third, after a name, so a returning founder could type any name and then be greeted as whoever the number belongs to - 'type Nitish, hear Welcome back Rajesh'. Asking it first means we know WHO before we ask anything of them: a number we know skips the name step entirely and the company question greets them from their ACCOUNT ('Hello Rajesh - what's your new company called?'), never from anything typed on screen; a number we don't know goes on to name, company, email as before. (2) A SIGNED-IN FOUNDER IS NOT SENT BACK THROUGH A CODE. 'Add a company' now reads the session: a session whose own mobile is confirmed identifies them at least as well as a 24-hour proof token, so the wizard opens at the company question - two questions in total - and register reads the number from the session (new core.deps.get_current_user_optional; register stays public and unauthenticated callers behave exactly as before). A session whose number was never confirmed is still asked, because there would be nothing to sign the new workspace in with. (3) Starting a company is an owner's move: the + in the profile menu shows only to an owner, while a member still sees and switches between the companies they belong to.</t>
+        </is>
+      </c>
+      <c r="G283" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H283" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I283" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K283" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_second_company.py (30). Two bugs the browser found and the tests had not: the wizard's default start step was still hardcoded to the old first question, so every new founder opened on question three; and the session was read before /auth/me had answered, so 'Add a company' asked for the number anyway. NOTE for the CSRF work: register now means something for a signed-in caller, so a cross-site POST could create a junk workspace while CSRF_ENFORCE is off.</t>
+        </is>
+      </c>
+      <c r="L283" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-20</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 187 of 282 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 30 of 36 Done.</t>
+          <t>Epic 6 progress: 188 of 283 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 31 of 37 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain. 2026-09-20: one founder, several companies - the mobile is asked before the email and says what it already runs, a second company needs no second email or password, and the profile menu switches between them. Rate limits are behind RATE_LIMITS and currently OFF - switch on before launch. Signup sets no password for anyone: the confirmed mobile is the sign-in. The mobile is the first question of all, and a signed-in founder adds a company without another code.</t>
+          <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain. 2026-09-20: one founder, several companies - the mobile is asked before the email and says what it already runs, a second company needs no second email or password, and the profile menu switches between them. Rate limits are behind RATE_LIMITS and currently OFF - switch on before launch. Signup sets no password for anyone: the confirmed mobile is the sign-in. The mobile is the first question of all, and a signed-in founder adds a company without another code. CSRF enforced in production (rate limits still off - testing phase).</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L283"/>
+  <dimension ref="A1:L284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21943,6 +21943,61 @@
         </is>
       </c>
       <c r="L283" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.37</t>
+        </is>
+      </c>
+      <c r="B284" s="28" t="inlineStr">
+        <is>
+          <t>frontend/src/lib/api.js, config.py (CSRF_ENFORCE), services/csrf.py, routers/auth.py</t>
+        </is>
+      </c>
+      <c r="C284" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D284" s="28" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E284" s="28" t="inlineStr">
+        <is>
+          <t>CSRF is closed: the browser proves the request came from our own pages</t>
+        </is>
+      </c>
+      <c r="F284" s="28" t="inlineStr">
+        <is>
+          <t>The session is a cookie, and a browser sends a cookie on every request to this origin whatever page started it - so another site could make a signed-in founder's browser POST here and the server would see an ordinary authenticated request. The defence has been half-built since FIX-006-B: the server mints a readable `dos_csrf` cookie, counts match/mismatch, and enforcement waited on the client. That client half never shipped, which is why it stayed off. Now lib/api.js reads the cookie and echoes it as X-CSRF-Token on every mutating request (safe verbs skipped, as the server skips them), and CSRF_ENFORCE defaults ON in production - off elsewhere, because the grandfathered requests-based integration suites sign in with cookies and send no header, and a harness on localhost is not a cross-site attacker. An explicit CSRF_ENFORCE=on/off still wins. AND THE HOLE THIS OPENED IS CLOSED WITH IT: /auth/register is on CSRF_EXEMPT_PATHS (a founder signing up has no CSRF cookie yet), but since U7-24.36 it also creates a company for a founder who is already signed in - so register now makes the double-submit check itself before trusting a cookie session. Bearer callers and direct calls are not forgeable and pass untouched.</t>
+        </is>
+      </c>
+      <c r="G284" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H284" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I284" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K284" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_cors_csrf.py (40). Proven live on a throwaway DB: a real save from the app logged nothing (matched), while the same request without the header logged csrf_check_failed reason=missing_header - a 403 once enforcement is on. TO DO BEFORE THE LIVE SUITES RUN AGAINST AN ENFORCING BOX: tests/_live_harness.py and the test_iteration* files need to send the header too.</t>
+        </is>
+      </c>
+      <c r="L284" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-20</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 188 of 283 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 31 of 37 Done.</t>
+          <t>Epic 6 progress: 189 of 284 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.</t>
         </is>
       </c>
     </row>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L284"/>
+  <dimension ref="A1:L285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21998,6 +21998,61 @@
         </is>
       </c>
       <c r="L284" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="28" t="inlineStr">
+        <is>
+          <t>U7-24.38</t>
+        </is>
+      </c>
+      <c r="B285" s="28" t="inlineStr">
+        <is>
+          <t>components/WelcomeOverlay.js</t>
+        </is>
+      </c>
+      <c r="C285" s="28" t="n">
+        <v>24</v>
+      </c>
+      <c r="D285" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E285" s="28" t="inlineStr">
+        <is>
+          <t>Entering the app lands in the Desk, not in another welcome</t>
+        </is>
+      </c>
+      <c r="F285" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: 'after clicking Enter DecisionOS it goes into the Decision Desk, but it is again showing a PWA screen on desktop and asking again to go to the Decision Desk.' That is WelcomeOverlay: a full-screen frosted pane with a max-w-xl column and a 'Step inside' button, raised by the dos_welcome flag signup sets. On a monitor that centred column over a blurred page reads as a phone screen dropped into the middle of the desktop, and it asks the founder to press a second door immediately after they pressed the first. It no longer shows at &gt;=1024px (the flag is cleared there, so it cannot resurface later); a phone keeps it, where the column IS the screen, it is the width the piece was drawn for, and it covers the dock beneath.</t>
+        </is>
+      </c>
+      <c r="G285" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H285" s="28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I285" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K285" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-20 (this push). tests/test_entering_the_app_after_signup.py (3). Walked in the preview: a signup finished at 1440px lands on /inbox?scope=morning with the full desktop Desk and no overlay; the same flag at 375px still raises it.</t>
+        </is>
+      </c>
+      <c r="L285" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-20</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1557,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 189 of 284 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.</t>
+          <t>Epic 6 progress: 196 of 291 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 7 of 7 Done.</t>
         </is>
       </c>
     </row>
@@ -2416,6 +2416,39 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>Added 2026-09-17 after testing signup in the browser: registration no longer waits on the AI, a second press ends in the workspace, the rate limit says how long, signup is saved as it goes, the backend-vs-frontend sweep (docs/BACKEND_NOT_WIRED.md), both inbox errands have screens, and (2026-09-19) the founder's mobile is required, validated and confirmed by code, with Mobile OTP asking which workspace; members sign in by mobile only (invite link first, welcome card), owners have email + password too, new passwords are 8+ with a letter and a number, and saves no longer queue behind the Desk loading. Open: the workspace picker on email sign-in, the company's own notes, Meetings, OTP in the Flutter app. Also 2026-09-19: Workflows counts on every pipeline, a Leave page of your own (request, absence, history; answer a question, withdraw), and My Work's Workflows pill back. 2026-09-20 Settings audit: AI keys kept off browsers, Settings stops losing the owner's work, own sign-in details only in Settings; a validation pass and unused-field call remain. 2026-09-20: one founder, several companies - the mobile is asked before the email and says what it already runs, a second company needs no second email or password, and the profile menu switches between them. Rate limits are behind RATE_LIMITS and currently OFF - switch on before launch. Signup sets no password for anyone: the confirmed mobile is the sign-in. The mobile is the first question of all, and a signed-in founder adds a company without another code. CSRF enforced in production (rate limits still off - testing phase).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sprint 25</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Workflows + tasks (operations)</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Added 2026-09-21 after auditing the workflow + task sections from the Desk (docs/WORKFLOW_OPERATIONS_PLAN.md). The engine was real — stage gates, auto-advance, evidence, escalation — and the HUMAN half was missing: a person could not attach a task to a workflow, move a due date, repeat work or see more than one stage's slice. 19 items across continuity, control, visibility and continuous operations.</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L285"/>
+  <dimension ref="A1:L292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22055,6 +22088,391 @@
       <c r="L285" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.1</t>
+        </is>
+      </c>
+      <c r="B286" s="28" t="inlineStr">
+        <is>
+          <t>routers/workflows.py, prompts/generators.py (operating_model v1.1)</t>
+        </is>
+      </c>
+      <c r="C286" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D286" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E286" s="28" t="inlineStr">
+        <is>
+          <t>A workflow is never born hollow</t>
+        </is>
+      </c>
+      <c r="F286" s="28" t="inlineStr">
+        <is>
+          <t>TWO FAULTS, ONE SYMPTOM: a card arrived with nothing on it and nobody was told to do anything. (1) Only the decision path fired stage entry (services/decision_flow) — the board's own New workflow button inserted the row and stopped, so a card a founder started by hand got none of its first stage's template tasks. Worse quietly: check_stage_ready reads 'every task at this stage is done' as satisfied when there are none, so a hollow card's stage-1 gate passed instantly and the card could be walked straight through work that had never been created. POST /workflows now makes the same on_stage_enter call the decision path makes (idempotent; a failure is logged and never undoes the card). (2) AND THE REASON THAT FIX WOULD HAVE CHANGED NOTHING: stages have been able to carry their own work since WE-03 — the normalizer keeps tasks[] per stage, the engine spawns them on arrival — and the prompt that designs a tenant's operating model NEVER ASKED FOR ANY. Every tenant's stages came back empty, so the whole mechanism had sat dead since it was built. generators.operating_model v1.1 asks for 1-3 real pieces of work per stage, phrased as instructions, with the department that does each.</t>
+        </is>
+      </c>
+      <c r="G286" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H286" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I286" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K286" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. tests/test_workflow_is_continuous.py (38). Proven live: a card started from the board came back carrying 'Confirm order specifications and quantity with the client', 'Log order details and assign a reference number', 'Check raw material availability against order requirements'. The empty-stage half of the bug was invisible to every existing test because they all seeded tasks by hand. EXISTING TENANTS keep empty stage templates until their operating model is regenerated or an owner edits it in Settings &gt; Operations.</t>
+        </is>
+      </c>
+      <c r="L286" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.2</t>
+        </is>
+      </c>
+      <c r="B287" s="28" t="inlineStr">
+        <is>
+          <t>routers/workflows.py (GET /workflows/{id}), components/workflow/WorkflowDetail.js</t>
+        </is>
+      </c>
+      <c r="C287" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D287" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E287" s="28" t="inlineStr">
+        <is>
+          <t>The card, opened: one screen that says what is going on</t>
+        </is>
+      </c>
+      <c r="F287" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: “when I see the workflow I have to know what is going on in the company — that's the goal of the product.” Nothing could answer it. GET /workflows returns a list of cards and, at most, the OPEN tasks of each card's CURRENT stage, so a card's earlier stages, its finished work, which stage waited on whose approval and what blocked the next move were all invisible; there was no per-card endpoint and no detail screen at all. GET /workflows/{id} returns, for every stage: its label, the role that owns it, whether it is behind / current / ahead, every task on it with who holds it and when it is due, how many are done, the approval it needs and who gave it, and when the card entered it — plus `readiness`, the engine's own answer to 'can this move now, and if not why not'. The drawer lays that out in the order a person asks: can it move → what happened, stage by stage → who holds each piece → the history. Opened from the card title (a button, so a keyboard reaches it) or the card body; a drag that ends on a column no longer also opens the card.</t>
+        </is>
+      </c>
+      <c r="G287" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H287" s="28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I287" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K287" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. Live: six stages reported with state and per-stage progress on a real card.</t>
+        </is>
+      </c>
+      <c r="L287" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.3</t>
+        </is>
+      </c>
+      <c r="B288" s="28" t="inlineStr">
+        <is>
+          <t>components/workflow/WorkflowDetail.js (POST /tasks with workflow_id)</t>
+        </is>
+      </c>
+      <c r="C288" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D288" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E288" s="28" t="inlineStr">
+        <is>
+          <t>A person can finally put a task on a workflow</t>
+        </is>
+      </c>
+      <c r="F288" s="28" t="inlineStr">
+        <is>
+          <t>THE THING YOKESH REPORTED: “a person will definitely create a workflow, but couldn't able to add the task to the workflow.” Exactly right, and the cause was not a missing API. POST /tasks has accepted workflow_id + stage_key since WE-01 and the router has always validated them — NO SCREEN HAD EVER SENT THEM. Only the engine (stage templates) and an approved decision could put work on a card; a human could not, at any width, by any route. Each stage in the detail view now has 'Add a task to &lt;stage&gt;': a title, who does it (defaulting to the stage's own department), a due date, and — D3 — an optional 'starts after' naming work already on this or an earlier stage. A task added this way counts toward the stage's gate exactly like a template one, so the card will not advance until it is done.</t>
+        </is>
+      </c>
+      <c r="G288" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H288" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I288" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K288" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. Live: a hand-added task appeared in the card's own gate reason (“4 task(s) still open at this stage”, up from 3).</t>
+        </is>
+      </c>
+      <c r="L288" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.4</t>
+        </is>
+      </c>
+      <c r="B289" s="28" t="inlineStr">
+        <is>
+          <t>routers/workflows.py (approve-stage, PATCH, advance), models/workflows.py</t>
+        </is>
+      </c>
+      <c r="C289" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D289" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E289" s="28" t="inlineStr">
+        <is>
+          <t>The approval gate gets a door, the card can be corrected, and a race tells the truth</t>
+        </is>
+      </c>
+      <c r="F289" s="28" t="inlineStr">
+        <is>
+          <t>Three things the board could not do. (1) APPROVAL: Settings &gt; Operations lets an owner require a sign-off to leave a stage, and check_stage_ready has always honoured it — but workflow_engine.record_stage_approval, the function that records one, had NO route and no control anywhere; only verification scripts ever called it. A configured gate could therefore only be passed by an owner OVERRIDE, which is the escape hatch, not the door. POST /workflows/{id}/approve-stage wires it, with the engine's own role check (the named role, or the owner), and the button shows to the person whose role it is. (2) CORRECTION: there was no PATCH at all, so a mistyped amount or the wrong party's name could only be fixed by deleting the card and losing its history. Title, detail, amount, party and contact are editable now; the stage is not (the engine stays its single writer) and neither is the stage list (those are the rails under a moving card). (3) THE RACE: the engine has always detected the second of two people pressing at once, and the route DROPPED that flag — so the person who lost the race got the same green '→ Dispatched' as the one who won it. It travels now, and the board says who actually moved it.</t>
+        </is>
+      </c>
+      <c r="G289" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H289" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I289" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K289" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. tests/test_workflow_is_continuous.py covers all three, including the wrong-role refusal.</t>
+        </is>
+      </c>
+      <c r="L289" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.5</t>
+        </is>
+      </c>
+      <c r="B290" s="28" t="inlineStr">
+        <is>
+          <t>pages/Workflows.js, pages/desk/workflowAttention.js, routers/workflows.py</t>
+        </is>
+      </c>
+      <c r="C290" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D290" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E290" s="28" t="inlineStr">
+        <is>
+          <t>The board says what needs attention, not only where things are</t>
+        </is>
+      </c>
+      <c r="F290" s="28" t="inlineStr">
+        <is>
+          <t>A founder opening the board could count cards and nothing else. Whether any had stalled, run late or were waiting on them took reading every column. The rules for that were WRITTEN AND TESTED a day earlier (pages/desk/workflowAttention.js, ASK-52) — the file's own header says the board should read them 'so the two do not drift' — and the board never imported it, so the Desk could say four cards needed attention while the board those cards live on showed them as ordinary cards in ordinary columns. Now: a card carries its one reason (Stuck 6d / 3 days late / Needs you / Needs your sign-off, worst reason wins, same rule the Desk counts by); a summary strip above the board — at EVERY width, which matters most on a phone where one stage fills the screen — says how many are running, how many need attention and how they split; and each card says how far through its stage it is ('2 of 4 done'), because 'In production' used to read identically on the day a card arrived and the day it was one task from leaving. GET /workflows?with_tasks now returns closed tasks' counts for that last part.</t>
+        </is>
+      </c>
+      <c r="G290" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H290" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I290" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K290" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. Live: “1 running · nothing is waiting · 1 moved today”, and '0 of 2 done at this stage' on the card face.</t>
+        </is>
+      </c>
+      <c r="L290" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.6</t>
+        </is>
+      </c>
+      <c r="B291" s="28" t="inlineStr">
+        <is>
+          <t>models/tasks.py, routers/tasks.py, services/tasks.py, pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C291" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D291" s="28" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E291" s="28" t="inlineStr">
+        <is>
+          <t>A due date can be moved, and blocked work looks blocked</t>
+        </is>
+      </c>
+      <c r="F291" s="28" t="inlineStr">
+        <is>
+          <t>(1) A DUE DATE COULD NEVER BE CHANGED. TaskUpdateInput had no due_date and no other route set one, so a date given at creation was permanent — the only way to move a deadline was to delete the task and type it again, losing its checklist, its notes, its proof and its whole timeline. It is the most ordinary act there is in running a company's work. due_date + due_time are on the update now (“” clears the date, null still means unchanged), the change is written to the task's timeline with what it moved FROM, and the right to move it matches the priority's: whoever asked for the work, their manager or the owner, because a due date is a promise made to someone else. (2) BLOCKED WORK LOOKED IDLE. The three on-screen stages fold `blocked` into 'To do' (ASK-28 TK-07) and the drawer explains why — but on the card FACE, in a list of twenty, work that COULD NOT be started read exactly like work nobody had bothered with, and a founder scanning the list blamed the person instead of the block. A pill now names the reason: waiting for a decision, waits for earlier work, or held.</t>
+        </is>
+      </c>
+      <c r="G291" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H291" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I291" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K291" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. tests/test_work_can_be_rescheduled.py (15), incl. month-end and hour-only edits.</t>
+        </is>
+      </c>
+      <c r="L291" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.7</t>
+        </is>
+      </c>
+      <c r="B292" s="28" t="inlineStr">
+        <is>
+          <t>services/recurrence.py, services/finance_signals.py, routers/tasks.py, Settings</t>
+        </is>
+      </c>
+      <c r="C292" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D292" s="28" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E292" s="28" t="inlineStr">
+        <is>
+          <t>Work that comes back, warns early, and waits its turn</t>
+        </is>
+      </c>
+      <c r="F292" s="28" t="inlineStr">
+        <is>
+          <t>Three absences that stopped operations being continuous. (1) NO RECURRING WORK EXISTED — no field, no route, no sweep — so every GST filing, salary run and stock count was typed again from scratch, in a product whose promise is that a company's operations run themselves; and the fifteen 'recurring tasks Dex will keep on rails' collected at signup were stored on the tenant and READ BY NOTHING. A task can now repeat every day / week / month, every N of them, optionally until a date. THE NEXT ONE APPEARS WHEN THE LAST IS CLOSED, not on a timer: a timer would bury a person under a column of identical undone stock counts and make falling behind harder to see, while close-to-spawn keeps exactly one live instance and lets the existing overdue ladder chase a routine that stops being done — and it needs no scheduler, no lock and no catch-up logic. A month-end routine stays on month end (31 Jan → 28 Feb). 'Stop repeating' ends the series without cancelling the work in hand. (2) NOTHING WARNED BEFORE A DEADLINE — bills got three days' notice, tasks got nothing until they were already late, which is the wrong moment to find out. The people on a task now hear at the company's own lead time (Settings &gt; Deadlines, default 2 days, 0 turns it off); the idempotency is the date itself, so B2's reschedule re-arms the warning for free. (3) NO TASK COULD WAIT ON ANOTHER. depends_on: the dependent starts blocked and opens by itself, telling whoever holds it, when the LAST of its predecessors closes — and clearing one block never clears another (a task that also needs an approval stays locked).</t>
+        </is>
+      </c>
+      <c r="G292" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H292" s="28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I292" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K292" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. tests/test_work_that_keeps_running.py (30). Live end-to-end: a weekly task closed and the next appeared due 2026-10-05; 'Pack the order' opened itself the moment 'Check the stock' was done. Also fixed: tests/e2e_harness.py never rebound services/finance_signals.db, so the follow-up sweep reached the production client from inside an isolated test.</t>
+        </is>
+      </c>
+      <c r="L292" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 196 of 291 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 7 of 7 Done.</t>
+          <t>Epic 6 progress: 202 of 307 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 13 of 23 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,24 +2431,24 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Added 2026-09-21 after auditing the workflow + task sections from the Desk (docs/WORKFLOW_OPERATIONS_PLAN.md). The engine was real — stage gates, auto-advance, evidence, escalation — and the HUMAN half was missing: a person could not attach a task to a workflow, move a due date, repeat work or see more than one stage's slice. 19 items across continuity, control, visibility and continuous operations.</t>
+          <t>Added 2026-09-21 after auditing the workflow + task sections from the Desk (docs/WORKFLOW_OPERATIONS_PLAN.md). The engine was real — stage gates, auto-advance, evidence, escalation — and the HUMAN half was missing: a person could not attach a task to a workflow, move a due date, repeat work or see more than one stage's slice. 19 items across continuity, control, visibility and continuous operations. A multi-user run (four people, two industries) found stage work going to nobody (departments never matched) — fixed — plus three findings for the founder. A 26-step walk by hand in the browser (3 people, real log-outs) fixed three more and logged the rest (docs/BROWSER_SCENARIOS_0921.md).</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L292"/>
+  <dimension ref="A1:L308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22473,6 +22473,886 @@
       <c r="L292" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.8</t>
+        </is>
+      </c>
+      <c r="B293" s="28" t="inlineStr">
+        <is>
+          <t>shared/roles.py, services/workflow_engine.py, services/workflows.py, services/voice.py, services/ai/generators.py</t>
+        </is>
+      </c>
+      <c r="C293" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D293" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E293" s="28" t="inlineStr">
+        <is>
+          <t>Stage work reaches real people: the company's own departments are recognised</t>
+        </is>
+      </c>
+      <c r="F293" s="28" t="inlineStr">
+        <is>
+          <t>FOUND BY RUNNING A TEXTILE MILL WITH FOUR PEOPLE ON FOUR BROWSERS. Onboarding named the mill's departments `loom_floor_&amp;_production`, `sales_&amp;_exporter_relations`, `yarn_&amp;_material_procurement`, `dispatch_&amp;_lorry_coordination`; the operating model — designed by a different prompt, which was only ever shown the departments' LABELS — said every stage belonged to `sales`, `production`, `dispatch`. Everything compared them with `==`: workflow_engine.on_stage_enter blanked the role, decision tasks never found the stage their department owns, and a stage's work went to NOBODY — so the card never moved. First live run: the decision's work landed 'nobody: 6'. Invisible to every earlier test, which all seeded the literal keys sales / finance / production. shared/roles.resolve_role maps a role word onto the company's real department: exact, same letters ignoring punctuation, a shared word, then a word from the same family ('accounts' is finance, 'lorry' is dispatch) — and answers None rather than guess between two, because a wrong department silently sends work to the wrong people. Wired into the engine, stage routing for decision tasks, and generation (the prompt is now shown the keys, and its answer is resolved onto them before it is stored).</t>
+        </is>
+      </c>
+      <c r="G293" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H293" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I293" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K293" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. tests/test_stage_work_reaches_real_people.py. Proven live, same scenario: 'nobody: 6' became 'Priya 3, Rajesh 2, Murugan 1, Anand 1, nobody 0'. Fixes existing companies at run time too — no migration.</t>
+        </is>
+      </c>
+      <c r="L293" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (multi-user engine run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.9</t>
+        </is>
+      </c>
+      <c r="B294" s="28" t="inlineStr">
+        <is>
+          <t>services/ai/stage_work.py, routers/tenant_settings.py, StageWorkReview.js, OperatingModelEditor.js, prompts generators.stage_work</t>
+        </is>
+      </c>
+      <c r="C294" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D294" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E294" s="28" t="inlineStr">
+        <is>
+          <t>Companies set up before today can get the work for their stages — reviewed by the owner first</t>
+        </is>
+      </c>
+      <c r="F294" s="28" t="inlineStr">
+        <is>
+          <t>Every company created before operating_model v1.1 has stages with no work, so its cards arrive empty. 'Regenerate' is the wrong tool: it redesigns the whole model, stage keys come back different, and running cards keep their old stage list frozen on them. Instead: Settings &gt; Operations shows 'N stages have no work' and 'Suggest the work'. The AI is asked about the EMPTY stages only (generators.stage_work), its departments resolved onto the company's own; nothing is written. The owner reviews stage by stage — keep, reword, drop, add (up to six) — and saves. The save writes only into stages that are STILL empty (re-checked at write time; a stage filled meanwhile is skipped and reported), is conditional on the model being exactly what was read (a concurrent edit becomes a clear 409, not a silent loss), never touches keys, labels, order, gates or side effects, and changes nothing the second time. Templates act on the NEXT entry to a stage — no unannounced work lands on cards already moving. Unsaved edits elsewhere in the editor survive the save. The banner does not count each pipeline's final resting stage (Paid, Cleared), which would otherwise have nagged forever.</t>
+        </is>
+      </c>
+      <c r="G294" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H294" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I294" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K294" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. Walked in the browser preview on a mill with 13 empty stages: 11 filled with mill-specific work ('Allocate yarn from store to the assigned looms and record yarn lot numbers'), the two resting stages left empty, the owner's rewording saved, and a new card then arrived carrying the owner's words. Step 4 of the plan (bulk admin script, dry run) not built yet.</t>
+        </is>
+      </c>
+      <c r="L294" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (multi-user engine run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.13</t>
+        </is>
+      </c>
+      <c r="B295" s="28" t="inlineStr">
+        <is>
+          <t>frontend/src/lib/api.js, context/AuthContext.js</t>
+        </is>
+      </c>
+      <c r="C295" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D295" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E295" s="28" t="inlineStr">
+        <is>
+          <t>A session that ends under an open app signs that tab out</t>
+        </is>
+      </c>
+      <c r="F295" s="28" t="inlineStr">
+        <is>
+          <t>Found running several people on several browsers: when a session ended while the app stayed open — signed out in another tab, expired, revoked — nothing noticed. The Desk stayed on screen and its pollers kept asking every few seconds, each answer a 401: 20 failed calls in 45 seconds per tab, forever, while the person looked at a Desk that had silently stopped updating. One preview tab left open had fired more than 28,000 requests. The client now raises a signal on a 401 from any ordinary route (auth and signup forms excluded — their 401s belong to the form); the auth context asks /auth/me once and only if that is refused too signs the tab out, which unmounts the shell and stops every poller, and the router sends them to sign in. A burst of 401s is one check; a single stray 401 with the session intact signs nobody out.</t>
+        </is>
+      </c>
+      <c r="G295" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H295" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I295" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K295" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. Live: 20 failed calls/45s -&gt; 2, then the sign-in screen. tests/test_session_lost_under_open_app.py.</t>
+        </is>
+      </c>
+      <c r="L295" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (multi-user engine run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.10</t>
+        </is>
+      </c>
+      <c r="B296" s="28" t="inlineStr">
+        <is>
+          <t>services/plans.py (trial seat_limit 3)</t>
+        </is>
+      </c>
+      <c r="C296" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D296" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E296" s="28" t="inlineStr">
+        <is>
+          <t>DECISION NEEDED: the trial allows 3 seats; the product is for 10-15-person companies</t>
+        </is>
+      </c>
+      <c r="F296" s="28" t="inlineStr">
+        <is>
+          <t>The multi-user run could not add a third member to a new company: 402 'You've reached your plan's seat limit (3)'. The 14-day trial is capped at owner + 2, so a founder cannot try DecisionOS with the team it is designed for — the workflows, approvals and hand-offs only make sense with more people than that. A pricing call, not a code change: raise the trial cap, or make the limit visible before the founder starts adding people.</t>
+        </is>
+      </c>
+      <c r="G296" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H296" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I296" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K296" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-21; not changed.</t>
+        </is>
+      </c>
+      <c r="L296" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (multi-user engine run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.11</t>
+        </is>
+      </c>
+      <c r="B297" s="28" t="inlineStr">
+        <is>
+          <t>pages/Team.js member dialog</t>
+        </is>
+      </c>
+      <c r="C297" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D297" s="28" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="E297" s="28" t="inlineStr">
+        <is>
+          <t>Hitting the seat limit is a toast that vanishes over a filled-in form</t>
+        </is>
+      </c>
+      <c r="F297" s="28" t="inlineStr">
+        <is>
+          <t>When Add member is refused for the seat limit, the only signal is a toast that is gone in seconds, while the dialog stays open with everything typed in and no error on it. Looking back at the screen a moment later, nothing says why the person was not added — it read as 'the button does nothing'. The refusal should sit on the dialog itself, with the way out (upgrade, or remove someone).</t>
+        </is>
+      </c>
+      <c r="G297" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H297" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I297" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K297" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-21.</t>
+        </is>
+      </c>
+      <c r="L297" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (multi-user engine run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.12</t>
+        </is>
+      </c>
+      <c r="B298" s="28" t="inlineStr">
+        <is>
+          <t>onboarding departments generator</t>
+        </is>
+      </c>
+      <c r="C298" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D298" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E298" s="28" t="inlineStr">
+        <is>
+          <t>The interview said 'Anand does accounts' and no accounts department was created</t>
+        </is>
+      </c>
+      <c r="F298" s="28" t="inlineStr">
+        <is>
+          <t>In the textile run the founder typed, in the COO interview, 'Priya handles sales, Anand does accounts, Murugan runs the loom floor'. The departments generated were loom floor, sales, yarn procurement and dispatch — no finance/accounts. So finance stage work (the advance invoice, payment follow-up) has no department to go to and lands unassigned, and there was nowhere sensible to put Anand. The departments step should read the people and responsibilities the founder named in the interview.</t>
+        </is>
+      </c>
+      <c r="G298" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H298" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I298" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K298" s="28" t="inlineStr">
+        <is>
+          <t>Found 2026-09-21.</t>
+        </is>
+      </c>
+      <c r="L298" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (multi-user engine run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.14</t>
+        </is>
+      </c>
+      <c r="B299" s="28" t="inlineStr">
+        <is>
+          <t>pages/Signup.js</t>
+        </is>
+      </c>
+      <c r="C299" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D299" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E299" s="28" t="inlineStr">
+        <is>
+          <t>Sign-up drew a blank page when reached from the Register link</t>
+        </is>
+      </c>
+      <c r="F299" s="28" t="inlineStr">
+        <is>
+          <t>Clicking 'Need a workspace? Register' on the sign-in screen opened /signup with only the logo and footer. Arriving from another screen mounts the wizard with the session already settled; React's development double-mount ran the start-up effect, cancelled it, and the re-run bailed on its `started` guard, so the cancelled run was the only one and never set draftReady. Every scripted run missed it because scripts load /signup directly. The cancel flag is gone; `started` already makes the effect run once.</t>
+        </is>
+      </c>
+      <c r="G299" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H299" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I299" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K299" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. Found step 1 of docs/BROWSER_SCENARIOS_0921.md. tests/test_browser_walk_fixes.py.</t>
+        </is>
+      </c>
+      <c r="L299" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.15</t>
+        </is>
+      </c>
+      <c r="B300" s="28" t="inlineStr">
+        <is>
+          <t>lib/departments.js, WorkflowDetail.js, DecisionDialog.js</t>
+        </is>
+      </c>
+      <c r="C300" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D300" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E300" s="28" t="inlineStr">
+        <is>
+          <t>Departments are named on screen, not shown as internal keys</t>
+        </is>
+      </c>
+      <c r="F300" s="28" t="inlineStr">
+        <is>
+          <t>The workflow card said 'sales_&amp;_order_management owns this stage' and the decision review said 'Pick who does this (production_&amp;_quality team)' — the internal keys of AI-designed departments. One helper (deptName) names them from the company's own roles everywhere. A task a department holds but nobody has picked up now says '&lt;Department&gt; · nobody picked yet' instead of an anonymous '?'.</t>
+        </is>
+      </c>
+      <c r="G300" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H300" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I300" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K300" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. Found steps 3 and 9 of docs/BROWSER_SCENARIOS_0921.md.</t>
+        </is>
+      </c>
+      <c r="L300" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.16</t>
+        </is>
+      </c>
+      <c r="B301" s="28" t="inlineStr">
+        <is>
+          <t>shared/due.py + 7 call sites (decisions, tasks, captures, ingestion, meetings, voice x2)</t>
+        </is>
+      </c>
+      <c r="C301" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D301" s="28" t="inlineStr">
+        <is>
+          <t>Tasks</t>
+        </is>
+      </c>
+      <c r="E301" s="28" t="inlineStr">
+        <is>
+          <t>'Due today' is a day: tasks Dex made for today were overdue the moment they existed</t>
+        </is>
+      </c>
+      <c r="F301" s="28" t="inlineStr">
+        <is>
+          <t>A decision said 'Priya to send the acknowledgement today'; the task reached her list already marked OVERDUE. Seven code paths stored 'in N days' as now + N days to the SECOND, so 'today' meant 'the instant Dex read it'. Relative due dates are now the company's calendar day, stored bare (the screens already read a bare date as 'by end of that day'), in India time so 02:00 IST is still today.</t>
+        </is>
+      </c>
+      <c r="G301" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H301" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I301" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K301" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21. Found step 12 of docs/BROWSER_SCENARIOS_0921.md. tests/test_due_is_a_day.py.</t>
+        </is>
+      </c>
+      <c r="L301" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.17</t>
+        </is>
+      </c>
+      <c r="B302" s="28" t="inlineStr">
+        <is>
+          <t>pages/Desk.js phone layout (desk-page / desk-insight)</t>
+        </is>
+      </c>
+      <c r="C302" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D302" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="E302" s="28" t="inlineStr">
+        <is>
+          <t>On a short screen (phone held sideways) the Desk's Dex panel collapses and its buttons sit on the tabs</t>
+        </is>
+      </c>
+      <c r="F302" s="28" t="inlineStr">
+        <is>
+          <t>The phone Desk is pinned to the screen's height and the Dex panel takes what is left. At ~486px tall nothing is left: the panel measured 0px, its attach / mic / keyboard buttons spilled onto the Decisions / Approvals / Watch tabs, and a tap on a button landed on the tab beneath it. Upright phones (812px) are fine. Needs a minimum height for the panel and a page that may scroll on short screens — a careful change to a layout tuned over ASK-34/35/42.</t>
+        </is>
+      </c>
+      <c r="G302" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H302" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I302" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K302" s="28" t="inlineStr">
+        <is>
+          <t>Found step 9 of docs/BROWSER_SCENARIOS_0921.md.</t>
+        </is>
+      </c>
+      <c r="L302" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.18</t>
+        </is>
+      </c>
+      <c r="B303" s="28" t="inlineStr">
+        <is>
+          <t>pages/desk/DeskDexWell.jsx</t>
+        </is>
+      </c>
+      <c r="C303" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D303" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="E303" s="28" t="inlineStr">
+        <is>
+          <t>The phone Desk's typing box closes itself 2.5 s after it opens</t>
+        </is>
+      </c>
+      <c r="F303" s="28" t="inlineStr">
+        <is>
+          <t>'Type instead' opens the field and an effect closes it again after 2.5 s if nothing has been typed. On a phone the keyboard sliding up plus a moment's thought is longer than that, so the box can vanish under the thumb. Measured: open at 0.3 s and 1.8 s, gone at 3.3 s.</t>
+        </is>
+      </c>
+      <c r="G303" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H303" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I303" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K303" s="28" t="inlineStr">
+        <is>
+          <t>Found step 9 of docs/BROWSER_SCENARIOS_0921.md.</t>
+        </is>
+      </c>
+      <c r="L303" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.19</t>
+        </is>
+      </c>
+      <c r="B304" s="28" t="inlineStr">
+        <is>
+          <t>services/decision_flow.py (approve → move card)</t>
+        </is>
+      </c>
+      <c r="C304" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D304" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E304" s="28" t="inlineStr">
+        <is>
+          <t>DECISION NEEDED: a decision that jumps a card several stages leaves their work behind</t>
+        </is>
+      </c>
+      <c r="F304" s="28" t="inlineStr">
+        <is>
+          <t>Approving a decision moved an existing card Inquiry -&gt; Sampling -&gt; Order Confirmed in one go. It left three open tasks on Inquiry and two on Sampling — so the card view shows 'Inquiry: done, 0 of 3 done' — and Sampling's two tasks were created only to be skipped at once; all five stay in people's My Work. Recommendation: create work only for the stage the card lands on, and close the work of stages it jumps past with a note ('passed when &lt;decision&gt; was approved') — or at least flag it. The owner's call.</t>
+        </is>
+      </c>
+      <c r="G304" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H304" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I304" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K304" s="28" t="inlineStr">
+        <is>
+          <t>Found step 9 of docs/BROWSER_SCENARIOS_0921.md.</t>
+        </is>
+      </c>
+      <c r="L304" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.20</t>
+        </is>
+      </c>
+      <c r="B305" s="28" t="inlineStr">
+        <is>
+          <t>pages/Login.js; phone navigation</t>
+        </is>
+      </c>
+      <c r="C305" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D305" s="28" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="E305" s="28" t="inlineStr">
+        <is>
+          <t>Sign-in opens on Email &amp; Password; sign-out is four taps deep on a phone</t>
+        </is>
+      </c>
+      <c r="F305" s="28" t="inlineStr">
+        <is>
+          <t>Founders and members now sign in by mobile, with no password — yet the sign-in screen opens on 'Email &amp; Password'. And on a phone, Sign out lives at More &gt; Settings &gt; Account &gt; scroll.</t>
+        </is>
+      </c>
+      <c r="G305" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H305" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I305" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K305" s="28" t="inlineStr">
+        <is>
+          <t>Found steps 0 and 10 of docs/BROWSER_SCENARIOS_0921.md.</t>
+        </is>
+      </c>
+      <c r="L305" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.21</t>
+        </is>
+      </c>
+      <c r="B306" s="28" t="inlineStr">
+        <is>
+          <t>onboarding build screen; operational_task_templates</t>
+        </is>
+      </c>
+      <c r="C306" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D306" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E306" s="28" t="inlineStr">
+        <is>
+          <t>The build screen promises routines that are not live</t>
+        </is>
+      </c>
+      <c r="F306" s="28" t="inlineStr">
+        <is>
+          <t>'Nila Garments now runs on DecisionOS … makes sure Selvam's machines never miss their weekly service', with '8 recurring tasks'. Those eight are stored as a list; nothing creates them as repeating tasks (the repeat feature exists since U7-25.7, but nothing converts the list). Either start them as repeating tasks at the end of onboarding (with a sensible cadence the owner confirms) or stop promising it.</t>
+        </is>
+      </c>
+      <c r="G306" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H306" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I306" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K306" s="28" t="inlineStr">
+        <is>
+          <t>Found step 1 of docs/BROWSER_SCENARIOS_0921.md.</t>
+        </is>
+      </c>
+      <c r="L306" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.22</t>
+        </is>
+      </c>
+      <c r="B307" s="28" t="inlineStr">
+        <is>
+          <t>AI department → default permissions</t>
+        </is>
+      </c>
+      <c r="C307" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D307" s="28" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="E307" s="28" t="inlineStr">
+        <is>
+          <t>An 'Accounts &amp; Buyer Payments' department does not get Finance access by default</t>
+        </is>
+      </c>
+      <c r="F307" s="28" t="inlineStr">
+        <is>
+          <t>Adding Anand to Accounts &amp; Buyer Payments showed that department's default access without 'Finance (invoices, payments, expenses…)'. The accounts person could not open the money screens until the owner overrode it by hand.</t>
+        </is>
+      </c>
+      <c r="G307" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H307" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I307" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K307" s="28" t="inlineStr">
+        <is>
+          <t>Found step 2 of docs/BROWSER_SCENARIOS_0921.md.</t>
+        </is>
+      </c>
+      <c r="L307" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.23</t>
+        </is>
+      </c>
+      <c r="B308" s="28" t="inlineStr">
+        <is>
+          <t>Workflows card money format; New Task; copy</t>
+        </is>
+      </c>
+      <c r="C308" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D308" s="28" t="inlineStr">
+        <is>
+          <t>Copy</t>
+        </is>
+      </c>
+      <c r="E308" s="28" t="inlineStr">
+        <is>
+          <t>Small things seen along the way</t>
+        </is>
+      </c>
+      <c r="F308" s="28" t="inlineStr">
+        <is>
+          <t>Workflow card shows ₹1,250,000 while the decision review shows ₹12,50,000. New Task labels the task category 'Department' (not the person's department). 'Nila Garments's OS'. 'Every week … every 1 week'. Approver list shows 'You' and 'Kavya Raman · Owner' (the same person). My Work's empty state says tasks only come from approved decisions. A stage task's description reads 'Spawned by workflow … entering stage'.</t>
+        </is>
+      </c>
+      <c r="G308" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H308" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I308" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K308" s="28" t="inlineStr">
+        <is>
+          <t>Found across docs/BROWSER_SCENARIOS_0921.md.</t>
+        </is>
+      </c>
+      <c r="L308" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 202 of 307 items Done  (66%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 13 of 23 Done.</t>
+          <t>Epic 6 progress: 205 of 308 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 16 of 24 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L308"/>
+  <dimension ref="A1:L309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22662,7 +22662,7 @@
       </c>
       <c r="E296" s="28" t="inlineStr">
         <is>
-          <t>DECISION NEEDED: the trial allows 3 seats; the product is for 10-15-person companies</t>
+          <t>Trial holds a real team: 15 seats</t>
         </is>
       </c>
       <c r="F296" s="28" t="inlineStr">
@@ -22682,12 +22682,12 @@
       </c>
       <c r="I296" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K296" s="28" t="inlineStr">
         <is>
-          <t>Found 2026-09-21; not changed.</t>
+          <t>SHIPPED 2026-09-21 (Yokesh: 'as you suggested'). Trial seat_limit 3 -&gt; 15 (services/plans.py); existing trials pick it up at once. SEE U7-25.24: the paid Starter plan has 10 seats, fewer than the trial.</t>
         </is>
       </c>
       <c r="L296" s="28" t="inlineStr">
@@ -22717,7 +22717,7 @@
       </c>
       <c r="E297" s="28" t="inlineStr">
         <is>
-          <t>Hitting the seat limit is a toast that vanishes over a filled-in form</t>
+          <t>The seat limit is visible before it bites, and said where it bites</t>
         </is>
       </c>
       <c r="F297" s="28" t="inlineStr">
@@ -22737,12 +22737,12 @@
       </c>
       <c r="I297" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K297" s="28" t="inlineStr">
         <is>
-          <t>Found 2026-09-21.</t>
+          <t>SHIPPED 2026-09-21. Team header shows 'N of M seats' (amber when full). A dialog opened with every seat taken says so AT THE TOP before anything is typed; a refused save keeps what was typed, names the person, and scrolls the reason into view — no vanishing toast. Walked in the browser with a temporary 3-seat cap.</t>
         </is>
       </c>
       <c r="L297" s="28" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="E304" s="28" t="inlineStr">
         <is>
-          <t>DECISION NEEDED: a decision that jumps a card several stages leaves their work behind</t>
+          <t>Work left behind: a review, not a wall — when a card leaves a stage with open work</t>
         </is>
       </c>
       <c r="F304" s="28" t="inlineStr">
@@ -23122,12 +23122,12 @@
       </c>
       <c r="I304" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K304" s="28" t="inlineStr">
         <is>
-          <t>Found step 9 of docs/BROWSER_SCENARIOS_0921.md.</t>
+          <t>SHIPPED 2026-09-21 (Yokesh chose it: a review of the work left behind, frictionless, tied to the gate loop). One review everywhere a card leaves a stage with open work — the board's move (the gate's 409 now opens it instead of the typed-reason override), the card's 'Move on to …', and a decision's jump (a 'Work these moves leave behind' card in the review). Per task: Done / Not needed / Keep; KEEP IS THE DEFAULT and moves the task with the card, where it holds the next stage's gate — nothing is ever closed that the person did not close, nothing is stranded. 'Set all' in one tap. Done fires what a close fires (dependents open, the next repeat comes). Stages a card only passes through create no work; a decision's own new tasks are not treated as left behind. Walked in the browser: board move (2 done · 1 cancelled · 3 carried, no override) and a decision jump (Set all Done + keep the invoice). Found on the way and fixed: three quick taps kept only the last choice (stale state) and the dialog's close sat on its text. tests/test_work_left_behind.py (12).</t>
         </is>
       </c>
       <c r="L304" s="28" t="inlineStr">
@@ -23353,6 +23353,61 @@
       <c r="L308" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-21 (browser walk, 3 people)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.24</t>
+        </is>
+      </c>
+      <c r="B309" s="28" t="inlineStr">
+        <is>
+          <t>services/plans.py (starter seat_limit 10)</t>
+        </is>
+      </c>
+      <c r="C309" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D309" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E309" s="28" t="inlineStr">
+        <is>
+          <t>DECISION NEEDED: the trial (15 seats) is now bigger than the paid Starter plan (10)</t>
+        </is>
+      </c>
+      <c r="F309" s="28" t="inlineStr">
+        <is>
+          <t>With the trial at 15 seats, a 12-person company that tries DecisionOS and then pays for Starter would have to remove two people on the day it becomes a customer. Either Starter goes to 15 (the target company size), or the trial matches Starter at 10, or conversion offers the next plan up automatically when the team is bigger than Starter.</t>
+        </is>
+      </c>
+      <c r="G309" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H309" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I309" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K309" s="28" t="inlineStr">
+        <is>
+          <t>Raised 2026-09-21 while raising the trial.</t>
+        </is>
+      </c>
+      <c r="L309" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 205 of 308 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 16 of 24 Done.</t>
+          <t>Epic 6 progress: 206 of 309 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 17 of 25 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Added 2026-09-21 after auditing the workflow + task sections from the Desk (docs/WORKFLOW_OPERATIONS_PLAN.md). The engine was real — stage gates, auto-advance, evidence, escalation — and the HUMAN half was missing: a person could not attach a task to a workflow, move a due date, repeat work or see more than one stage's slice. 19 items across continuity, control, visibility and continuous operations. A multi-user run (four people, two industries) found stage work going to nobody (departments never matched) — fixed — plus three findings for the founder. A 26-step walk by hand in the browser (3 people, real log-outs) fixed three more and logged the rest (docs/BROWSER_SCENARIOS_0921.md).</t>
+          <t>Added 2026-09-21 after auditing the workflow + task sections from the Desk (docs/WORKFLOW_OPERATIONS_PLAN.md). The engine was real — stage gates, auto-advance, evidence, escalation — and the HUMAN half was missing: a person could not attach a task to a workflow, move a due date, repeat work or see more than one stage's slice. 19 items across continuity, control, visibility and continuous operations. A multi-user run (four people, two industries) found stage work going to nobody (departments never matched) — fixed — plus three findings for the founder. A 26-step walk by hand in the browser (3 people, real log-outs) fixed three more and logged the rest (docs/BROWSER_SCENARIOS_0921.md). The routines promised at sign-up are now confirmed once and repeat (U7-25.25).</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L309"/>
+  <dimension ref="A1:L310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23406,6 +23406,63 @@
         </is>
       </c>
       <c r="L309" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.25</t>
+        </is>
+      </c>
+      <c r="B310" s="28" t="inlineStr">
+        <is>
+          <t>services/routines.py, routers/routines.py, components/routines/RoutinesSetup.js (reveal + My Work)</t>
+        </is>
+      </c>
+      <c r="C310" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D310" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E310" s="28" t="inlineStr">
+        <is>
+          <t>The routines promised at sign-up are real: the founder confirms them once and they repeat</t>
+        </is>
+      </c>
+      <c r="F310" s="28" t="inlineStr">
+        <is>
+          <t>The reveal screen said '8 recurring tasks Dex will keep on rails' and nothing created them — operational_task_templates were stored on the tenant and read by nothing, so the Monday checks and GST filing the founder believed were covered were not.</t>
+        </is>
+      </c>
+      <c r="G310" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H310" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I310" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K310" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-21 (Yokesh: 'go ahead with task 3, best plan'). The reveal screen lists the routines with a suggested cadence and first date; the owner ticks the ones the company does and each becomes a real repeating task (series_id + recurrence; the next appears when the last is closed). A name that says how often ('weekly', 'Monday', 'GST filing on the 10th', 'for the day') starts ticked; one that says nothing about time, or happens per order/shipment ('after shipment', 'for each shipment'), starts unticked with the reason on it. Cadence is three pills and the date follows it (no date picker). Owner-only; each answer remembered on the tenant (routine_setup) so nothing is offered twice and a double tap starts one series. Entering without answering leaves a slim 'N routines from your setup haven't started yet' reminder on My Work. GET/POST /api/routines/setup. 25 tests (tests/test_routines_from_signup.py). Browser-checked on Nila Garments (owner Kavya): 8 listed, 4 confident ticked, one handed to Anand, GST first on 10 Oct; 4 real weekly/monthly tasks created with repeat labels on My Work; 'None of these' clears the reminder. NOT browser-checked: the reveal screen itself (needs a full AI sign-up) — same component. Also: two D1/D3 source-assertion tests updated for GlassSelect's testid prop.</t>
+        </is>
+      </c>
+      <c r="L310" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-21</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 206 of 309 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 17 of 25 Done.</t>
+          <t>Epic 6 progress: 210 of 313 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 21 of 29 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Added 2026-09-21 after auditing the workflow + task sections from the Desk (docs/WORKFLOW_OPERATIONS_PLAN.md). The engine was real — stage gates, auto-advance, evidence, escalation — and the HUMAN half was missing: a person could not attach a task to a workflow, move a due date, repeat work or see more than one stage's slice. 19 items across continuity, control, visibility and continuous operations. A multi-user run (four people, two industries) found stage work going to nobody (departments never matched) — fixed — plus three findings for the founder. A 26-step walk by hand in the browser (3 people, real log-outs) fixed three more and logged the rest (docs/BROWSER_SCENARIOS_0921.md). The routines promised at sign-up are now confirmed once and repeat (U7-25.25).</t>
+          <t>Added 2026-09-21 after auditing the workflow + task sections from the Desk (docs/WORKFLOW_OPERATIONS_PLAN.md). The engine was real — stage gates, auto-advance, evidence, escalation — and the HUMAN half was missing: a person could not attach a task to a workflow, move a due date, repeat work or see more than one stage's slice. 19 items across continuity, control, visibility and continuous operations. A multi-user run (four people, two industries) found stage work going to nobody (departments never matched) — fixed — plus three findings for the founder. A 26-step walk by hand in the browser (3 people, real log-outs) fixed three more and logged the rest (docs/BROWSER_SCENARIOS_0921.md). The routines promised at sign-up are now confirmed once and repeat (U7-25.25). 2026-09-22: the workflow gets a clock — stage durations date the stage's work, stuck cards are reported, cards can carry a target date with a forecast, and the card shows planned vs actual per stage; the Desk's Delayed and Workflows tiles read it (U7-25.26–29).</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L310"/>
+  <dimension ref="A1:L314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23465,6 +23465,234 @@
       <c r="L310" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.26</t>
+        </is>
+      </c>
+      <c r="B311" s="28" t="inlineStr">
+        <is>
+          <t>services/workflow_timing.py, workflow_engine.on_stage_enter, Settings → Operations</t>
+        </is>
+      </c>
+      <c r="C311" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D311" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E311" s="28" t="inlineStr">
+        <is>
+          <t>Stage work has a deadline: a stage takes N working days and its work is dated from that</t>
+        </is>
+      </c>
+      <c r="F311" s="28" t="inlineStr">
+        <is>
+          <t>Work a stage created had due_date None, so nothing on a workflow was ever due-soon, overdue, escalated, counted by the Desk's Delayed tile or the score.</t>
+        </is>
+      </c>
+      <c r="G311" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H311" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I311" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K311" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-22. `days` per stage in the operating model (Settings → Operations, blank = 3 working days; Sunday off, shared/workdays.py). On entering a stage every open undated task on it gets entered + N working days (dates a person set are kept); card carries stage_due. One-time boot migration date_stage_work_v1 dates existing open stage work, never earlier than the next working day so nothing turns overdue overnight (scratch DB: 12 tasks on 6 cards). From there the existing due-soon warning, overdue ladder, Delayed tile and score all apply to workflow work. Stage row in the editor now wraps on a phone.</t>
+        </is>
+      </c>
+      <c r="L311" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.27</t>
+        </is>
+      </c>
+      <c r="B312" s="28" t="inlineStr">
+        <is>
+          <t>services/workflow_timing.warn_stuck_workflows (followup sweep), Settings → Operations</t>
+        </is>
+      </c>
+      <c r="C312" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D312" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E312" s="28" t="inlineStr">
+        <is>
+          <t>A stuck card is reported, with a per-board threshold</t>
+        </is>
+      </c>
+      <c r="F312" s="28" t="inlineStr">
+        <is>
+          <t>'Stuck' was computed in the browser after a fixed 3 working days and nobody was told.</t>
+        </is>
+      </c>
+      <c r="G312" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H312" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I312" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K312" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-22. `stuck_after_days` per pipeline (blank = 3). The leader-locked sweep tells the people on the card's current stage and the owner once per quiet spell (ntype workflow_stuck); any movement of the card or its stage work starts a new spell. The board and the Desk read the server's stuck clock (card timing) instead of their own.</t>
+        </is>
+      </c>
+      <c r="L312" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.28</t>
+        </is>
+      </c>
+      <c r="B313" s="28" t="inlineStr">
+        <is>
+          <t>models/workflows.py target_date, WorkflowDetail, Desk Workflows tile</t>
+        </is>
+      </c>
+      <c r="C313" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D313" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E313" s="28" t="inlineStr">
+        <is>
+          <t>A card can have a target date, with a forecast and 'at risk'</t>
+        </is>
+      </c>
+      <c r="F313" s="28" t="inlineStr">
+        <is>
+          <t>A card had no deadline of its own; 'late' only ever meant an overdue task.</t>
+        </is>
+      </c>
+      <c r="G313" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H313" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I313" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K313" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-22. target_date on create/PATCH (YYYY-MM-DD; '' clears; anything else 400). Forecast = current stage's due date (or today if passed) + planned days of the stages still to come. Board card: 'Stage due Thu 24 Sep · Target … · on track / at risk / missed'. Card counts as late when its stage has run over or its target has passed; Desk Workflows tile adds 'N cards forecast to miss their target date'. Browser-checked: target 23 Sep vs forecast 24 Sep → at risk on the card and on the Desk.</t>
+        </is>
+      </c>
+      <c r="L313" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.29</t>
+        </is>
+      </c>
+      <c r="B314" s="28" t="inlineStr">
+        <is>
+          <t>WorkflowDetail CardClock</t>
+        </is>
+      </c>
+      <c r="C314" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D314" s="28" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E314" s="28" t="inlineStr">
+        <is>
+          <t>The card's timeline: every stage's planned days against the days it took</t>
+        </is>
+      </c>
+      <c r="F314" s="28" t="inlineStr">
+        <is>
+          <t>Stage-entered dates were recorded and never shown.</t>
+        </is>
+      </c>
+      <c r="G314" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H314" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I314" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K314" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-22. Timeline section in the card drawer: this stage's due date and how far over, the stuck line, the target/forecast with Set a target / Change / Clear, and a planned-vs-actual bar per stage (red when over). GET /workflows/{id} returns timing.timeline; the board list returns timing without it. 13 tests (tests/test_workflow_timing.py).</t>
+        </is>
+      </c>
+      <c r="L314" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -23630,7 +23630,7 @@
       </c>
       <c r="K313" s="28" t="inlineStr">
         <is>
-          <t>SHIPPED 2026-09-22. target_date on create/PATCH (YYYY-MM-DD; '' clears; anything else 400). Forecast = current stage's due date (or today if passed) + planned days of the stages still to come. Board card: 'Stage due Thu 24 Sep · Target … · on track / at risk / missed'. Card counts as late when its stage has run over or its target has passed; Desk Workflows tile adds 'N cards forecast to miss their target date'. Browser-checked: target 23 Sep vs forecast 24 Sep → at risk on the card and on the Desk.</t>
+          <t>SHIPPED 2026-09-22. target_date on create/PATCH (YYYY-MM-DD; '' clears; anything else 400). Forecast = current stage's due date (or today if passed) + planned days of the stages still to come. Board card: 'Stage due Thu 24 Sep · Target … · on track / at risk / missed'. Card counts as late when its stage has run over or its target has passed; Desk Workflows tile adds 'N cards forecast to miss their target date'. Browser-checked: target 23 Sep vs forecast 24 Sep → at risk on the card and on the Desk. 2026-09-22 follow-up: the New workflow form asks for it too ('Finish by (optional)', English/Hindi/Tamil), so a card can be born with its target; browser-checked (new card → 'Target Thu 15 Oct · on track').</t>
         </is>
       </c>
       <c r="L313" s="28" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 210 of 313 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 21 of 29 Done.</t>
+          <t>Epic 6 progress: 212 of 315 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 23 of 31 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L314"/>
+  <dimension ref="A1:L316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23693,6 +23693,120 @@
       <c r="L314" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.30</t>
+        </is>
+      </c>
+      <c r="B315" s="28" t="inlineStr">
+        <is>
+          <t>lib/aiConsent.js (new), lib/api.js, hooks/useDexCapture.js, pages/Brain.js, pages/Ledger.js, routers/brain.py, routers/ledger.py</t>
+        </is>
+      </c>
+      <c r="C315" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D315" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E315" s="28" t="inlineStr">
+        <is>
+          <t>AI off is said in words, with the way to turn it on — not a Python dict</t>
+        </is>
+      </c>
+      <c r="F315" s="28" t="inlineStr">
+        <is>
+          <t>A migrated customer's owner pressed the mic and was shown "451: {'code': 'ai_consent_required', 'message': ...}". Companies migrated from the old product carry no consent record (the feature post-dates their data), so this refusal is the first thing many of them meet.</t>
+        </is>
+      </c>
+      <c r="G315" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H315" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I315" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K315" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-26 (Yokesh, from Velraj's screen at Tracole). One helper (lib/aiConsent) owns the code, the link and the sentence; every surface uses it: the 451 interceptor, the voice-capture path (which printed the raw stored reason), document extraction, and Ask Dex (which said 'AI service error. Please try again.'). The words follow the viewer — an owner gets 'Turn it on in Settings → AI processing' with a 'Turn on AI' button, everyone else 'An owner has to turn it on' with 'See settings'; AuthContext keeps that flag for the axios interceptor, which is outside React. BACKEND: routers/brain.py caught every exception from the planner and re-raised 502 'AI planning error', swallowing the 451 — so /ask could never show the real reason; consent (and any deliberate refusal) now passes through, same in routers/ledger.py. Browser-checked on a scratch workspace with consent cleared, as owner and as a non-owner: inline sentence, toast, and the link landing on Settings → Business → AI processing ('Off — nobody has agreed yet'). 9 tests (tests/test_ai_off_says_so_in_words.py).</t>
+        </is>
+      </c>
+      <c r="L315" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.31</t>
+        </is>
+      </c>
+      <c r="B316" s="28" t="inlineStr">
+        <is>
+          <t>pages/onboarding/BuildReveal.js, routers/auth.py (checked, no change)</t>
+        </is>
+      </c>
+      <c r="C316" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D316" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E316" s="28" t="inlineStr">
+        <is>
+          <t>CHECKED: signup does ask for AI consent before it is recorded</t>
+        </is>
+      </c>
+      <c r="F316" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: 'are we asking the tick to the AI consent before signing up? check that as well.'</t>
+        </is>
+      </c>
+      <c r="G316" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H316" s="28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="I316" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K316" s="28" t="inlineStr">
+        <is>
+          <t>CHECKED 2026-09-26, no change needed. The reveal screen carries the line right under the button that creates the workspace: 'Pressing this turns Dex on: what you type or say, and the documents you send it, go to our AI providers so it can read them. You can switch that off any time in Settings → AI processing.' The server records that press as the consent event (routers/auth.py, build_grant_payload), so a workspace made through signup starts with AI on — all 23 signup-made workspaces have a grant, while 102 of 103 in the migrated database do not. It is a line beside the button, NOT a tickbox: the press is the agreement and there is no product without it. If you want stronger evidence of an affirmative act for DPDP, a tickbox is a small change — raised as a question, not built. Locked by a test so the line cannot quietly go while the server keeps recording consent.</t>
+        </is>
+      </c>
+      <c r="L316" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-26</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 212 of 315 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 23 of 31 Done.</t>
+          <t>Epic 6 progress: 213 of 316 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 24 of 32 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L316"/>
+  <dimension ref="A1:L317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23807,6 +23807,63 @@
       <c r="L316" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.32</t>
+        </is>
+      </c>
+      <c r="B317" s="28" t="inlineStr">
+        <is>
+          <t>pages/CRM.js, pages/ContactProfile.js, lib/format.js, components/crm/LogComplaintDialog.jsx</t>
+        </is>
+      </c>
+      <c r="C317" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D317" s="28" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="E317" s="28" t="inlineStr">
+        <is>
+          <t>The CRM's three kinds, finished: a real confirm, one word for Partner, and the tab follows what you added</t>
+        </is>
+      </c>
+      <c r="F317" s="28" t="inlineStr">
+        <is>
+          <t>Walking J15 (three kinds, each with its own door) in the browser found four things the change had not finished, plus one older mismatch beside it.</t>
+        </is>
+      </c>
+      <c r="G317" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H317" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I317" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K317" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-27, after checking Chinmay's J15 in the preview. (1) DELETE WAS A DEAD BUTTON: it asked through window.confirm, which some browsers and embed contexts answer with a silent false and no dialog — pressing it did nothing, no dialog and no request (reproduced). Now Radix AlertDialog, the app's own material, as FUP-49 did for My Work's Complete and ASK-2 for the workflow card; delete verified end-to-end (DELETE 200, leaves the profile page, count back to 0). (2) 'Dealer' was renamed in pages/CRM.js's own constant only, so the contact's own page and pages/Contacts.js still said Dealer; the word now lives in lib/format's CONTACT_TYPE_LABELS, which every screen reads — the stored value stays `dealer`. (3) Adding a partner left the list on Buyers reading 'No relationships yet'; the tab now follows what was added (scopeForType). (4) 'New partner' is capitalised like its neighbours. (5) A complaint asked as Minor/Serious/Urgent read back as 'medium' — severityLabel is exported from the dialog that asks, and used on both the CRM card and the contact page (pre-dates J15). Editing a contact re-checked in the browser: name + email saved (PATCH 200) and shown. 7 tests (tests/test_crm_kinds_read_true.py).</t>
+        </is>
+      </c>
+      <c r="L317" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-27 (browser check of J15)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 213 of 316 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 24 of 32 Done.</t>
+          <t>Epic 6 progress: 215 of 318 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 26 of 34 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L317"/>
+  <dimension ref="A1:L319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23864,6 +23864,120 @@
       <c r="L317" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-27 (browser check of J15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.33</t>
+        </is>
+      </c>
+      <c r="B318" s="28" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/CRM.js, pages/ContactProfile.js (Chinmay, commit 53f76ab)</t>
+        </is>
+      </c>
+      <c r="C318" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D318" s="28" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="E318" s="28" t="inlineStr">
+        <is>
+          <t>Three kinds, each with its own door — customers, partners and suppliers, plus delete and resolve</t>
+        </is>
+      </c>
+      <c r="F318" s="28" t="inlineStr">
+        <is>
+          <t>Six things the founder found, all the same shape: the CRM knew how to do something and gave nobody a way to ask for it. A dealer could only be made by adding a customer and flipping the type inside the window, and that flip stayed live on every later edit — a contact could change sides with one tap. Partners were folded into the customers list with no way to see them. A contact added by mistake stayed for ever (DELETE /contacts/:id existed, nothing called it). A complaint could be logged and then closed from nowhere (PATCH /complaints/:id/resolve existed, nothing called it), so the red count only climbed.</t>
+        </is>
+      </c>
+      <c r="G318" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H318" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I318" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K318" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-26 by Chinmay (53f76ab), frontend only — every endpoint it needed already existed. Each kind has its own entry in Add contact, its own tab, and no way to change what a contact is after it exists (wrong kind = delete and add again). Partners get a tab under that name; both are the buyer side, so they open and close together with crm_buyers and nobody gains access by the split. Deleting the contact a profile page is ABOUT leaves that page. Verified on the running stack by the author. NOT in that commit: tests, and tracker rows — this row is the record; the browser check afterwards (U7-25.32) found five things it had not finished, all now fixed.</t>
+        </is>
+      </c>
+      <c r="L318" s="28" t="inlineStr">
+        <is>
+          <t>Chinmay 2026-09-26 (founder's six CRM findings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.34</t>
+        </is>
+      </c>
+      <c r="B319" s="28" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/desk/DeskDexWell.jsx, pages/Desk.js, components/DecisionDialog.js, lib/deferredDecisions.js (Chinmay, commit 10111ee)</t>
+        </is>
+      </c>
+      <c r="C319" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D319" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E319" s="28" t="inlineStr">
+        <is>
+          <t>"Later" is "Save as draft", and a draft says so</t>
+        </is>
+      </c>
+      <c r="F319" s="28" t="inlineStr">
+        <is>
+          <t>The pilot client's second voice note: the button after Dex reads a capture should say Save as draft, and the tinted row in the Decisions column should carry the word, not the colour alone.</t>
+        </is>
+      </c>
+      <c r="G319" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H319" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I319" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K319" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-27 by Chinmay (10111ee). The well's ending offers 'Save as draft' where it said 'Later' (testid desk-dex-later kept, so the suites still find it); the Desk's Decisions row says 'Draft' in its meta line instead of 'Set aside'; DecisionDialog carries '(Draft)' after the title wherever it opens while the decision can still be decided; a draft stays a draft until it is decided — opening it no longer clears the mark, approving or rejecting does. OPEN: the mark is per-device (localStorage) — the decision is on the server, the draft flag is not, so it does not follow the founder to their phone. docs/PILOT-2_DRAFT_FLAG_ASK.md is the backend ask that would make it travel; not yet built. No tests in the commit.</t>
+        </is>
+      </c>
+      <c r="L319" s="28" t="inlineStr">
+        <is>
+          <t>Pilot client via Chinmay 2026-09-27 (PILOT-2 B)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 215 of 318 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 26 of 34 Done.</t>
+          <t>Epic 6 progress: 216 of 319 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 27 of 35 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L319"/>
+  <dimension ref="A1:L320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23978,6 +23978,63 @@
       <c r="L319" s="28" t="inlineStr">
         <is>
           <t>Pilot client via Chinmay 2026-09-27 (PILOT-2 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.35</t>
+        </is>
+      </c>
+      <c r="B320" s="28" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/desk/DexCapturePopup.jsx (new), pages/desk/DeskDexWell.jsx, components/DecisionDialog.js (Chinmay, commit 3a6f64f)</t>
+        </is>
+      </c>
+      <c r="C320" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D320" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E320" s="28" t="inlineStr">
+        <is>
+          <t>One pop-up carries the whole Dex capture: what you said, Dex reading it, what Dex made</t>
+        </is>
+      </c>
+      <c r="F320" s="28" t="inlineStr">
+        <is>
+          <t>The pilot client's first voice note: a long spoken decision was poured into the well's two-line field, where it could not be read or edited, and the counts-only screen after it told him nothing and still made him press Review.</t>
+        </is>
+      </c>
+      <c r="G320" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H320" s="28" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I320" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K320" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-27 by Chinmay (3a6f64f). Three steps in one pop-up on both surfaces: (1) What you said - the whole transcript in a real field the moment a recording stops, with its files, Next and Discard; typed captures skip it. (2) Dex is reading it - the forge with the stages; closing it cancels nothing. (3) What Dex made - the counts plus DecisionPanel (the same component the Desk's rows open) with Approve / Save as draft / Reject at the foot. The counts-only screen and its Review button are gone; nothing-to-decide, a failure with Retry and the slow case are the last step in the same pop-up. The well is the door again (ripple and mic, paperclip, keyboard, send, the kept-draft note and a line saying where a capture got to when its pop-up was closed); its desktop growth over the hero, the fade and ASK-47's pinned action row are removed with it. Also: DecisionDialog no longer crashes on a moves answer that is not a list, and verify-dex was rewritten for the pop-up (193 checks). The biggest of the three commits - 1,113 lines out of DeskDexWell. No tracker row and no tests came with it; this row is the record.</t>
+        </is>
+      </c>
+      <c r="L320" s="28" t="inlineStr">
+        <is>
+          <t>Pilot client via Chinmay 2026-09-27 (PILOT-2 A)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 216 of 319 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 27 of 35 Done.</t>
+          <t>Epic 6 progress: 217 of 320 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 28 of 36 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L320"/>
+  <dimension ref="A1:L321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24035,6 +24035,63 @@
       <c r="L320" s="28" t="inlineStr">
         <is>
           <t>Pilot client via Chinmay 2026-09-27 (PILOT-2 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.36</t>
+        </is>
+      </c>
+      <c r="B321" s="28" t="inlineStr">
+        <is>
+          <t>services/decision_flow.py, routers/decisions.py, routers/desk.py, frontend lib/decisionDrafts.js (new), Desk.js, DecisionDialog.js, AuthContext.js</t>
+        </is>
+      </c>
+      <c r="C321" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D321" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E321" s="28" t="inlineStr">
+        <is>
+          <t>"Save as draft" is saved: the draft flag lives on the decision, not on one device</t>
+        </is>
+      </c>
+      <c r="F321" s="28" t="inlineStr">
+        <is>
+          <t>PILOT-2 B renamed 'Later' to 'Save as draft', but the mark was a list of ids in one browser's localStorage (ASK-36). The decision was on the server; the mark was not. A draft saved on the laptop was not a draft on the phone, and a cleared browser or a private window lost it — a button promising something saved, that wasn't. docs/PILOT-2_DRAFT_FLAG_ASK.md is the ask.</t>
+        </is>
+      </c>
+      <c r="G321" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H321" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I321" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K321" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-27, built to the ask. BACKEND: `draft` / `drafted_at` / `drafted_by` on the decision (a missing field reads false, so no migration); POST and DELETE /api/decisions/{id}/draft, guarded by can_decide (403 otherwise), only while pending or pending_approval (409 once decided, with a sentence the UI shows), idempotent, and stamping updated_at so /api/pulse carries it to every open screen within a tick. Deciding clears the flag in the SAME write as the status (services/decision_flow._claim), so no screen can show a decided draft. The Desk's cards carry `draft`, so the Decisions column marks a row without a second request. FRONTEND: lib/decisionDrafts.js replaces lib/deferredDecisions.js (retired) - the server is the truth, with an in-memory optimistic layer only for the gap between the tap and the next fetch, so the row turns under the founder's finger; the Desk row and DecisionDialog's '(Draft)' both read the decision's own flag. One-time carry-over: any draft still in someone's localStorage is posted on their next load and the old key removed, so nobody loses one in the switch. Browser-checked: saved from the capture pop-up (server returns draft true with drafted_by), row marked Draft, and still Draft after clearing localStorage and reloading - which is the proof it is no longer per-device. 11 tests (tests/test_decision_draft_travels.py); API baseline regenerated (356 rows).</t>
+        </is>
+      </c>
+      <c r="L321" s="28" t="inlineStr">
+        <is>
+          <t>Pilot client via Chinmay's ask; built by Yokesh 2026-09-27</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 217 of 320 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 28 of 36 Done.</t>
+          <t>Epic 6 progress: 218 of 321 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 29 of 37 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L321"/>
+  <dimension ref="A1:L322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24092,6 +24092,63 @@
       <c r="L321" s="28" t="inlineStr">
         <is>
           <t>Pilot client via Chinmay's ask; built by Yokesh 2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.37</t>
+        </is>
+      </c>
+      <c r="B322" s="28" t="inlineStr">
+        <is>
+          <t>frontend/src/components/DecisionDialog.js, pages/desk/DeskDexWell.jsx, pages/Desk.js</t>
+        </is>
+      </c>
+      <c r="C322" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D322" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E322" s="28" t="inlineStr">
+        <is>
+          <t>The draft is offered wherever the decision is, and the pop-up waits before it says it saved</t>
+        </is>
+      </c>
+      <c r="F322" s="28" t="inlineStr">
+        <is>
+          <t>Two things the browser walk of U7-25.36 left: Save as draft existed only in the capture pop-up, so a decision opened from the Desk the next morning could only be approved or rejected; and the pop-up said 'Saved as a draft' on the tap, before the server answered.</t>
+        </is>
+      </c>
+      <c r="G322" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H322" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I322" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K322" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-27. (1) THE DRAFT, WHEREVER THE DECISION IS: the modal's 'Your call' card now carries 'Save as draft — decide later' under Approve and Reject, and on a draft it reads 'Not a draft any more' — the mark comes off without deciding it (the DELETE endpoint shipped with U7-25.36 and was already tested). The owner who opens a decision the next morning, sets its priority and moves the task to Anand had SAVED all of that (the panel writes each change as it is made) but had no way to say they had been there. The capture pop-up's pinned row keeps its own handler and its testid (desk-dex-later). (2) THE POP-UP WAITS: it said 'Saved as a draft' on the tap and sent the request after — fine when the mark was a note in this browser that could not fail, wrong now that it is a call that can be refused, because a refusal (no signal, or somebody decided it first) left two contradictory messages with the false one on top. Now: pressed, then saved, then said; a failure keeps the pop-up open on what Dex made and shows only the error. Browser-checked both ways, including a forced network failure at the XHR layer: only 'Couldn't save it as a draft — it is still waiting on you' and the pop-up stayed open. Also fixed in the browser pass: the toast read `isDraft` after the optimistic flip and said 'No longer a draft' about a draft just saved; the wanted state travels with the click now. 3 more tests in tests/test_decision_draft_travels.py (14).</t>
+        </is>
+      </c>
+      <c r="L322" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-27 (browser walk of the draft flag)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 218 of 321 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 29 of 37 Done.</t>
+          <t>Epic 6 progress: 219 of 322 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 30 of 38 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L322"/>
+  <dimension ref="A1:L323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24149,6 +24149,63 @@
       <c r="L322" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-27 (browser walk of the draft flag)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.38</t>
+        </is>
+      </c>
+      <c r="B323" s="28" t="inlineStr">
+        <is>
+          <t>backend models/decisions.py, services/decision_flow.py, routers/decisions.py; frontend components/DecisionDialog.js</t>
+        </is>
+      </c>
+      <c r="C323" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D323" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E323" s="28" t="inlineStr">
+        <is>
+          <t>Words Dex misheard can be corrected in the review — the decision's title, its text, and every task's name</t>
+        </is>
+      </c>
+      <c r="F323" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: 'in a decision a people has to change their tasks and the titles of the decisions. It may have multiple tasks also. Let's say they could have misspelled something.' Dex writes all three from speech and mishears names, fabrics and numbers. None could be corrected before approving: the founder approved the wrong words and either lived with them or renamed the task afterwards in My Work — and those words are what the person doing the task reads, and what the Journal, the Company Brain and every later search carry.</t>
+        </is>
+      </c>
+      <c r="G323" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H323" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I323" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K323" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-27. BACKEND: `title` on DecisionProposalTaskInput (each proposed task renames on its own, several per decision); new PATCH /api/decisions/{id} taking title and summary (DecisionEditInput). Both behind the same gate as the rest of the review (_editable): only while pending or pending_approval (409 after), only somebody who may decide it (403), an empty or whitespace name refused with 400 and nothing written. Every change lands on the decision's timeline with who and when ('renamed from …', 'Reworded before approval: title'). FRONTEND: one EditableText control in DecisionDialog used in all three places — reads as text, click to correct, Enter or clicking away saves, Escape puts it back, and a refusal restores the old words and says why. BROWSER-CHECKED end to end on the scratch workspace: renamed the task, renamed the decision, both persisted to the server, then APPROVED — and the real task was created as 'Service loom 4 with Selvam before Saturday', the corrected wording, not Dex's first guess. That last step is the point and it has its own test. 11 tests (tests/test_decision_words_are_correctable.py). API baseline regenerated (357 rows). NOT DONE: adding a task Dex missed (POST /decisions/{id}/tasks exists, nothing calls it).</t>
+        </is>
+      </c>
+      <c r="L323" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-27</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 219 of 322 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 30 of 38 Done.</t>
+          <t>Epic 6 progress: 220 of 323 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 31 of 39 Done.</t>
         </is>
       </c>
     </row>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L323"/>
+  <dimension ref="A1:L324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24206,6 +24206,63 @@
       <c r="L323" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.39</t>
+        </is>
+      </c>
+      <c r="B324" s="28" t="inlineStr">
+        <is>
+          <t>backend routers/pulse.py, routers/contacts.py; frontend hooks/usePulse.js</t>
+        </is>
+      </c>
+      <c r="C324" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D324" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E324" s="28" t="inlineStr">
+        <is>
+          <t>The pulse watches the shared screens too: workflows, contacts and complaints</t>
+        </is>
+      </c>
+      <c r="F324" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh asked whether every CRUD operation refreshes its screen. An audit of all 212 write calls across 63 frontend files found the writes were fine — each refreshes its own screen through invalidateQueries, a parent callback (onChange/onSaved/onFiled) or a wrapper (act/run/runTeam), and every tenant-settings editor calls refreshTenant. The gap was SOMEBODY ELSE's change: the 20-second pulse (J14-03) watched only tasks, leaves, decisions and notifications, so a card a colleague moved on the shared board stayed put on your screen until the tab was refocused.</t>
+        </is>
+      </c>
+      <c r="G324" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H324" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I324" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K324" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-28. Added to _WATCHED: workflows (updated_at, created_at), contacts (updated_at, created_at), complaints (resolved_at, updated_at, created_at) — the kinds two people look at together. The client maps each to the lists it appears on (hooks/usePulse TOUCHES): a workflow move refreshes the board, its counts and the Desk tile; a contact refreshes the CRM list, the contact page and the finance parties list; a complaint refreshes the card, the page and the Desk. ALSO FIXED: editing a contact wrote no timestamp at all, so the signature (count + newest stamp) could not see a rename — routers/contacts now stamps updated_at, as leaves taught us. Cost stays one indexed count/max pair per kind per 20s tick. BROWSER-CHECKED with the change made through the API, as a colleague on another device: a renamed card appeared on an untouched board in 16.2s, and a contact added elsewhere appeared in the CRM list 7s after the tick. 8 tests (tests/test_pulse_watches_the_shared_screens.py) including tenant isolation; e2e_harness now patches routers.pulse. STILL NOT WATCHED (nobody watches these together, and they refetch on focus): invoices, payments, expenses, team members, documents. TWO WRITES STILL REFRESH NOTHING, both harmless: finance/FinanceAi task creation (covered by the tasks watch) and the mobile 'chase' in FocusView which logs a complaint (now covered by the complaints watch).</t>
+        </is>
+      </c>
+      <c r="L324" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-28 (refresh audit)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L324"/>
+  <dimension ref="A1:L325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24263,6 +24263,63 @@
       <c r="L324" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-28 (refresh audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.40</t>
+        </is>
+      </c>
+      <c r="B325" s="28" t="inlineStr">
+        <is>
+          <t>backend services/delegation.py; tests/test_journey1_leave_cover_edge_cases.py, tests/test_rbac_p2.py</t>
+        </is>
+      </c>
+      <c r="C325" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D325" s="28" t="inlineStr">
+        <is>
+          <t>Settings, Team and access (RBAC)</t>
+        </is>
+      </c>
+      <c r="E325" s="28" t="inlineStr">
+        <is>
+          <t>A leave cover hands the approvals back on time — the window is read on the company's day</t>
+        </is>
+      </c>
+      <c r="F325" s="28" t="inlineStr">
+        <is>
+          <t>services/delegation.is_active_now decided the hand-over window by SHIFTING THE UTC CLOCK — +14h at the start, -12h at the end, "on while it is that date anywhere in the world" — because the dates are plain days a person picked and the clock is UTC. The two ends are not symmetric in what that costs. Early at the start is harmless; LATE at the end means somebody still holds another person's approval authority after they are back, and every approval it lets through is recorded in the absent person's name. A cover that ended on Friday stayed live until 12:00 UTC on Saturday — 17:30 IST, most of a working day. The window exists so that nobody has to remember to switch the hand-over off; one that switches off late gives that away. Found by a test that failed only when the suite ran before noon UTC, which is why it had looked like a flake.</t>
+        </is>
+      </c>
+      <c r="G325" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H325" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I325" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K325" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-28. The window is a date range on the COMPANY'S calendar, so it is compared with the company's day: shared/due.today_ist, the one answer the product already uses for due dates, working days and the reminder sweep. Both ends become exact — on from the first day, off at midnight IST after the last — with no grace to drift, and 'leave from today' still works at 6 a.m., which is what the +14h was reaching for. is_active_now takes an optional `now` so the boundary can be asserted on a named day instead of on whatever day the suite runs. TESTS: the edge-case file's notion of 'today' was UTC's, which disagrees with the company's between 00:00 and 05:30 IST, so it now asks about the same day the code does; 8 new assertions pin the boundary itself, including 14:30 IST on the day after the last day — the moment that used to answer True. test_rbac_p2 carried an assertion written against the old grace (UTC now + 10h expected to be live, i.e. a cover starting tomorrow already on); it now asserts the real intent — today on, tomorrow not yet, yesterday's over — and seeds its windows on the IST day. 45 tests green across the four delegation-touching files (test_journey1_leave_cover_edge_cases, test_journey1_leave_hands_over, test_rbac_p2, test_u7_24_18_desk_load_latency), run single-process. NOTE: this assumes one timezone, which is what the whole product assumes today; a tenant timezone is a separate job.</t>
+        </is>
+      </c>
+      <c r="L325" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-28 (the failure that looked like a flake)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L325"/>
+  <dimension ref="A1:L326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24320,6 +24320,63 @@
       <c r="L325" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-28 (the failure that looked like a flake)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.41</t>
+        </is>
+      </c>
+      <c r="B326" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/OperatingScore.js, pages/_operatingScoreDemo.js, lib/format.js, pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C326" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D326" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E326" s="28" t="inlineStr">
+        <is>
+          <t>Ops offers only what it can deliver — three dead controls out, the person's page reads in words</t>
+        </is>
+      </c>
+      <c r="F326" s="28" t="inlineStr">
+        <is>
+          <t>Browser walk of /operating-score (Yokesh, 2026-09-29: "check what are the things there, what should remove, and click all the things"). Three controls promised what the product could not give. (a) "See breakdown &gt;" on all four category cards: the items behind it (demoDrivers / demoDrilldowns) are gated on isDemoTenant — a tenant NAMED Kapoor — so on every real company the dialog answered "a breakdown of what makes it up isn't shown for this part yet". (b) "Do these first" led with "Execution is at 11 — open it to see what is pulling it down", which opened that same empty dialog: the page's own first instruction went nowhere. (c) "Customize weights for your business" — four presets, four sliders — admitted in its own small print that nothing was saved, and did not even preview: Execution 35% -&gt; 45% left the score beside it on 29. Separately, a person's page printed stored keys at the team member reading about their own work (sales_&amp;_order_management, todo, in_progress, stage ready_for_dispatch), addressed the viewer while showing somebody else, and linked all five open-work rows to /my-work.</t>
+        </is>
+      </c>
+      <c r="G326" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H326" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I326" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K326" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. REMOVED: the weight sliders and their presets, page and module both (DEFAULT_WEIGHTS / WEIGHT_PRESETS deleted from _operatingScoreDemo; the weights still SHOW, from CATS, which mirrors services/operating_score.py — they just cannot be dragged). "See breakdown" now needs canDrill, passed only for the demo tenant; a real company's card says what the category MEASURES instead, which is true, with the formula one tap away under "How is this calculated?". The weakest-category action is filtered out unless its drill has content. IN WORDS: taskStatusLabel / priorityLabel / humanStage on task rows; pipeline and stage named from the tenant's own operating model (opModel) on workflow cards, the same words the board uses; roleLabelFor on the view-as strip. TASK_STATUS_LABELS moved into lib/format as the one home and MyWork.js now reads it (same extraction humanStage had). WHOSE PAGE: "Key actions to improve Priya's operating score", "Priya could attach a photo...", "Priya hasn't used a Dex plan yet". WHERE IT GOES: a task row opens THAT task (?task=, the deep link Workflows.js already uses — carried bare, because My Work deliberately drops filters that could hide a deep-linked task); a workflow card opens THAT card on its own pipeline (?wf=&amp;wf_type=, which rings and scrolls to it); the four tiles and "See all" open ?view=all&amp;person= so the owner gets the person's list, not his own. The loading skeleton takes the shape the URL already implies, so nothing rearranges on arrival. BROWSER-CHECKED: both views, desktop + phone; task deep link opens the drawer on Priya's task; workflow deep link rings the right card. 19 tests (tests/test_ops_page_keeps_its_promises.py).</t>
+        </is>
+      </c>
+      <c r="L326" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (browser walk of Ops)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L326"/>
+  <dimension ref="A1:L329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24377,6 +24377,177 @@
       <c r="L326" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29 (browser walk of Ops)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.42</t>
+        </is>
+      </c>
+      <c r="B327" s="28" t="inlineStr">
+        <is>
+          <t>backend services/tasks.py, services/task_timing.py (new), services/score_history.py (new), routers/tasks.py, bootstrap/lifecycle.py, workers/schedulers.py</t>
+        </is>
+      </c>
+      <c r="C327" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D327" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E327" s="28" t="inlineStr">
+        <is>
+          <t>A task records when it finished, and the score starts keeping a past</t>
+        </is>
+      </c>
+      <c r="F327" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh, after the Ops walk: "we can see individual person efficiency also right". Nothing on the page could answer it. A task carried created_at and updated_at and nothing else, and updated_at moves on any edit - a task done on Monday and renamed on Friday looked like five days of work - so time-to-close could not be computed at all. Separately the Ops page has carried an honest refusal since KR-9: the reference draws a trend line and a delta chip, and NOTHING IN THE SYSTEM KEPT SCORE HISTORY, so drawing either would have been inventing one.</t>
+        </is>
+      </c>
+      <c r="G327" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H327" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I327" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K327" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. (1) COMPLETED_AT: services/tasks.completion_stamp writes it the moment a task crosses into done, and withdraws it on a reopen so reopened work is not counted as a fast close; wired at all three write sites (the PATCH path, an approver closing a close-stage task, answering a follow-up). An ordinary edit adds nothing, which was the whole reason updated_at could not be used. BACKFILL IS RECOVERY, NOT A GUESS: the Journal has written a task_done event on every completion all along, so backfill_completed_at reads the log and only falls back to updated_at where no event exists, marking those completed_at_inferred so nothing later reads a guess as a measurement. On the scratch tenant: 11 of 11 dated from the journal, 0 guessed. Earliest event wins, so a task closed/reopened/closed is dated from when it first landed. (2) SCORE HISTORY: services/score_history writes one row per company per IST day into operating_score_history - overall, the four categories, and the counts behind them, because 'Execution fell 9' is only useful beside 'overdue went 4 to 14' and the counts cannot be re-derived later. It rides the leader-locked sweep beside the retention purge, never a user's request (scoring a company takes ~1.3s); the id is tenant:day so a restart storm cannot double-count, and a later tick costs one indexed lookup rather than a re-scoring. A company with no score yet gets NO row - a row of nulls would read as a real zero later. history_for() reads a window back, oldest first. Nothing renders it yet, deliberately: the page keeps saying 'all time' until there is a past worth showing. 20 tests (test_a_task_says_when_it_finished, test_the_score_gets_a_past).</t>
+        </is>
+      </c>
+      <c r="L327" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.43</t>
+        </is>
+      </c>
+      <c r="B328" s="28" t="inlineStr">
+        <is>
+          <t>backend services/task_timing.py, services/operating_score.py; frontend pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C328" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D328" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E328" s="28" t="inlineStr">
+        <is>
+          <t>Ops says how long work takes, not only how much - per person, per company, and in the table</t>
+        </is>
+      </c>
+      <c r="F328" s="28" t="inlineStr">
+        <is>
+          <t>"5 done" reads identically whether the five took two working days each or nine, and Overdue only ever counted work still OPEN, so somebody who finishes everything a week late looked perfect. The page could measure volume and nothing else.</t>
+        </is>
+      </c>
+      <c r="G328" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H328" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I328" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K328" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. services/task_timing.timing_of returns typical_days (the MEDIAN - one task left open over a festival week drags an average into nonsense), on_time_rate over the finished work that HAD a due date, the two denominators so the screen can say what a percentage is out of, and waiting_days (the age of the oldest open thing, which no rate can show). Counted in WORKING days via shared/workdays - the calendar the stage deadlines and stuck alerts already use, so 'three days' means one thing across the product. None, never a flattering zero, wherever there is nothing to measure. Carried on compute_employee_stats (so a person's page and the owner's own snapshot both have it), on the company stats, and per row in _score_employees so the leaderboard can compare. UI: a 'How the work moves' row of BreakdownCards on the person's page and the company's, each card explaining its own silence rather than showing a bare dash; 0 working days renders as 'Same day' (raised in the morning, done by evening is the BEST answer, and a bare '0' reads like a failure to measure); the team table carries ~Nd / 'same day' beside the counts. Browser-checked on both views. 10 tests (test_ops_says_how_long_work_takes).</t>
+        </is>
+      </c>
+      <c r="L328" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.44</t>
+        </is>
+      </c>
+      <c r="B329" s="28" t="inlineStr">
+        <is>
+          <t>backend services/tasks.py, services/task_timing.py, services/operating_score.py, routers/tasks.py, bootstrap/lifecycle.py; frontend pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C329" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D329" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E329" s="28" t="inlineStr">
+        <is>
+          <t>What a signature costs - an approver's turnaround and the queue waiting on them</t>
+        </is>
+      </c>
+      <c r="F329" s="28" t="inlineStr">
+        <is>
+          <t>An approver's queue is invisible in every number on the Ops page. Work waiting on a signature is not the approver's OWN task, so it lands in nobody's Open and nobody's Overdue: a manager who takes three working days over every sign-off holds up the whole workshop and scores a clean 100, while the doer whose task is stuck behind it watches it go overdue. The task recorded approved_at but never the moment the request was MADE, so the span could not be computed at all.</t>
+        </is>
+      </c>
+      <c r="G329" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H329" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I329" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K329" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. services/tasks.approval_stamp writes approval_requested_at when approval crosses into pending, and does not restart the clock on a re-save (otherwise every edit to a waiting task would make the approver look instant). Written at all three asks: a task raised already needing approval, the next task in a recurring series, and the doer marking a close-stage task complete - which IS the request and had no record of its moment. approvals_of() gives typical_days (median, request to answer), answered, waiting and oldest_days; a queue nobody is clearing shows waiting=4 with no turnaround rather than nothing at all, which is the case that matters most. WHAT IS AND IS NOT RECOVERABLE, said out loud: a task needing approval BEFORE work starts is created already waiting, so its created_at IS the request and the backfill uses it (2 recovered on the scratch tenant); sign-off before CLOSING has no record of the moment and no Journal event either, so those stay unmeasured rather than dated from something that merely looks close - their turnaround accumulates from today. UI: a fourth card on the person's page, shown ONLY to somebody who actually signs things off, since for everyone else it would be a card of dashes. Browser-checked: 4 cards for Anand, 3 for Priya. 12 tests (test_what_a_signature_costs).</t>
+        </is>
+      </c>
+      <c r="L329" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L329"/>
+  <dimension ref="A1:L331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24548,6 +24548,120 @@
       <c r="L329" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.45</t>
+        </is>
+      </c>
+      <c r="B330" s="28" t="inlineStr">
+        <is>
+          <t>backend services/task_timing.py; frontend pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C330" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D330" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E330" s="28" t="inlineStr">
+        <is>
+          <t>Work that is open and already past its date counts as late</t>
+        </is>
+      </c>
+      <c r="F330" s="28" t="inlineStr">
+        <is>
+          <t>Found in the browser walk Yokesh asked for. The company page showed 'Overdue 14' four inches above 'Landed on time 100%', and Anand's page - four dated tasks all past their date, nothing finished - said 'No finished task had a due date, work nobody dated cannot be early or late'. Both were technically true, because the rate counted only FINISHED work, and together they told an owner 'we hit our dates' while fourteen things were late.</t>
+        </is>
+      </c>
+      <c r="G330" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H330" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I330" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K330" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. A task still open on the day after its due date has ALREADY failed to land on time - a fact about today, not a prediction - so it belongs in the denominator, and leaving it out flattered exactly the team that needed telling. _closed_on_time becomes _hit_its_date, which judges finished work by its completion and open work by whether its day has gone past; a task whose date is still ahead stays unjudged (it has time), and a cancelled task is not late (it was called off, not missed). timing_of gains late_open so the card can name them instead of leaving a low percentage unexplained. Card relabelled 'Hit their date': on the scratch tenant it went from '100% - 3 of 3 finished tasks that had a date landed by it' to '18% - 3 of 17 dated tasks were done by their date, 14 are open and already past it', which now agrees with the Overdue tile beside it. 5 tests.</t>
+        </is>
+      </c>
+      <c r="L330" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (browser validation of Ops)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.46</t>
+        </is>
+      </c>
+      <c r="B331" s="28" t="inlineStr">
+        <is>
+          <t>backend services/operating_score.py, routers/operating_score.py; frontend pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C331" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D331" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E331" s="28" t="inlineStr">
+        <is>
+          <t>Ops can be asked about a period - last 30 or 90 days, not only all time</t>
+        </is>
+      </c>
+      <c r="F331" s="28" t="inlineStr">
+        <is>
+          <t>Every number on the page counted every task ever. A workshop that had a bad September carried it for the rest of its life, and an owner asking 'are we better than last month?' got the same figure either way. Worse, Execution mixed two clocks: completion counted every task ever while the overdue penalty was as of right now, so one bad fortnight scored as if it were the company's whole history. The header stated 'All time' as a fact because no history existed to window - but tasks carry completed_at as of U7-25.42, so the period can be computed directly.</t>
+        </is>
+      </c>
+      <c r="G331" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H331" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I331" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K331" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. ?window=30|90 on /api/operating-score and in the page's address. THE RULE IS ONE SENTENCE AND THE HEADER SAYS IT rather than making anyone infer it: a window narrows the FINISHED work to what finished inside it, and everything still open counts however old it is. Open work is deliberately never filtered - a task raised in March and still not done is a live problem today, and hiding it behind a 30-day window would be the same flattering lie U7-25.45 just removed. Applies to tasks (Execution, the team-health counts, the work-moves row, the leaderboard) and to decisions by created_at (Sales). FINANCE IS THE EXCEPTION AND SAYS SO in the formula panel: a payment often settles an invoice raised long before it, so 'collected in the last 30 days' would divide two figures that do not belong together. Each period caches on its own key (one key for all of them would serve last month's figures as this month's); an unoffered period reads as all time rather than 400ing, because a stale or hand-typed link should show the page. The choice lives in the URL with replace:true (flicking between periods is reading, not navigating) and placeholderData keeps the previous period on screen so the page does not blink back to skeletons. BROWSER-PROVED by backdating four completions on the scratch DB to July and restoring them after: all time 9 done / Execution 3 / on-time 18%, last 30 days 7 done / Execution 0 / on-time 12%, last 90 days back to 9 - and open 21 / overdue 14 identical in all three, which is the rule holding. 16 tests.</t>
+        </is>
+      </c>
+      <c r="L331" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (browser validation of Ops)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L331"/>
+  <dimension ref="A1:L333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24660,6 +24660,120 @@
         </is>
       </c>
       <c r="L331" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (browser validation of Ops)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.47</t>
+        </is>
+      </c>
+      <c r="B332" s="28" t="inlineStr">
+        <is>
+          <t>backend services/workflow_timing.py, services/operating_score.py; frontend pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C332" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D332" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E332" s="28" t="inlineStr">
+        <is>
+          <t>Ops names the jam - which card is stuck, for how long, and who is holding it</t>
+        </is>
+      </c>
+      <c r="F332" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh, walking the Ops page: 'it ranks people but never names the bottleneck'. The team table said Anand was 0 and Priya 18 - a verdict on two people, not an answer to the question an owner-led workshop actually asks, which is WHERE the work is stuck and who is holding it. The clock that knows already existed (services/workflow_timing.card_timing, the same one the Desk and the stuck alert read); nothing had ever asked it for a ranking.</t>
+        </is>
+      </c>
+      <c r="G332" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H332" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I332" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K332" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. services/workflow_timing.bottlenecks() ranks the active cards a company's work is piling up behind, worst first, and the company payload carries the top three. TWO CLOCKS, KEPT APART rather than blurred into one 'stuck': OVER means the stage is taking longer than the board allows, IDLE means nobody has touched the card at all - a card can be idle without being over (a generous stage) and over without being idle (somebody is working on it, it is just slow), and the fix differs. Whichever ran longer is the headline, because that is the number printed beside it: the first browser pass showed '4 working days over' next to a 7, which reads as a mistake, so the smaller clock now follows in a clause. HOLDERS are the people with open work at that stage, by name; an EMPTY holders list is not a gap in the data, it is the finding, and the row says 'with nobody named on it'. A card parked on its last stage is finished, not stuck. NEVER WINDOWED - a card stuck since March is stuck TODAY, and a period filter would hide the worst of them. Each row opens that card on its own pipeline (?wf=&amp;wf_type=). BROWSER: 'Bluewave - 30% Advance Invoice Raised - Invoice Raised - not moved for 7 working days, and 4 working days over the 3 this stage allows - with nobody named on it' - exactly the card an owner needs to see first. 10 tests.</t>
+        </is>
+      </c>
+      <c r="L332" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (browser validation of Ops)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.48</t>
+        </is>
+      </c>
+      <c r="B333" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C333" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D333" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E333" s="28" t="inlineStr">
+        <is>
+          <t>The cards with nothing in them are not shown</t>
+        </is>
+      </c>
+      <c r="F333" s="28" t="inlineStr">
+        <is>
+          <t>From the same walk. On the page of somebody who has finished nothing - Anand, 0 done, 4 open - 'Proof rate: 0 of 0 done with photo or voice' and 'Plans in use 0/0' took two thirds of a row to say nothing. A proof rate over no finished work is not a low score, it is an undefined one, and a reader cannot tell those apart from a dash.</t>
+        </is>
+      </c>
+      <c r="G333" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H333" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I333" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K333" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. Proof rate appears once there is finished work to carry proof; Plans in use stays while plans are in use OR there is enough work for the nudge to mean something, because 'hasn't used a Dex plan yet' IS the message for somebody with plenty of work and no plan. The row is sized to what it holds (BreakdownRow + a ROW_COLS map, because Tailwind cannot ship a class assembled at runtime): two cards in a three-column grid left a hole that reads as a card which failed to load. BROWSER: Anand 2 cards on md:grid-cols-2, Priya 3 on md:grid-cols-3. 3 tests.</t>
+        </is>
+      </c>
+      <c r="L333" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29 (browser validation of Ops)</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L333"/>
+  <dimension ref="A1:L334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24776,6 +24776,63 @@
       <c r="L333" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29 (browser validation of Ops)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.49</t>
+        </is>
+      </c>
+      <c r="B334" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C334" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D334" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E334" s="28" t="inlineStr">
+        <is>
+          <t>The Finance card opens the Finance page</t>
+        </is>
+      </c>
+      <c r="F334" s="28" t="inlineStr">
+        <is>
+          <t>Finance carries 25% of the overall score and was the one category you could not click into at all: Execution, Sales and Responsiveness each say what they measure, and Finance showed a number - or a dash - and stopped. Every other figure on the page leads somewhere; that quarter of the score led nowhere. Context: this is the narrow half of a broader suggestion Yokesh pushed back on - 'WHY DO WE NEED MONEY PART HERE' - and he was right. Money belongs on the Finance page, not duplicated on Ops, which is about work moving. A link, not a new section.</t>
+        </is>
+      </c>
+      <c r="G334" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H334" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I334" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K334" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. CategoryCard takes an optional `to`; the Finance card passes /finance, and only when data.can_finance, because the Finance page would bounce anyone without it. The card renders as a Link in that case and keeps the chevron that signals a click; the aria-label says where it goes ('Finance: Nothing to score yet - left out of the total. Open Finance'). A drill still wins where one exists (linkTo = !opens &amp;&amp; to), so a demo tenant's Finance card opens its breakdown rather than navigating away. THE UNSCORED CARD KEEPS SAYING SO - 'Nothing to score yet, left out of the total' is the honest part, and it is also exactly the moment an owner should go and raise an invoice, so the empty state is the strongest case for the link rather than a reason to hide it. The disabled-state hover suppression moved onto the button branch so the three non-clickable cards still sit still under the cursor. Browser-checked: Finance is an &lt;a href='/finance'&gt;, the other three are disabled buttons, and the click lands on Finance. 1 test in test_ops_page_keeps_its_promises.</t>
+        </is>
+      </c>
+      <c r="L334" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L334"/>
+  <dimension ref="A1:L335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24833,6 +24833,63 @@
       <c r="L334" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.50</t>
+        </is>
+      </c>
+      <c r="B335" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C335" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D335" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E335" s="28" t="inlineStr">
+        <is>
+          <t>A refused Ops page says no, instead of loading for ever</t>
+        </is>
+      </c>
+      <c r="F335" s="28" t="inlineStr">
+        <is>
+          <t>Found in the access walk Yokesh asked for ('check for every other users, from owner to nth level, access based as well'), signed in as Anand - a member with finance and approvals but not the owner. Following a link to a colleague's Ops page left the LOADING SKELETON ON SCREEN FOR EVER, with aria-busy='true', so a screen reader went on announcing that the page was still loading. The API was doing its job (403, 'Only the owner can view another user's operating page'); the page simply never said so. `isLoading` was false and `data` undefined, and the guard `if (isLoading || !data)` caught the second half and drew the skeleton. Nothing said no - it just never said anything. The same dead end swallowed a 404 (a person who has left, or a stale link) and any 500.</t>
+        </is>
+      </c>
+      <c r="G335" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H335" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I335" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K335" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. OperatingScoreProblem, checked BEFORE the skeleton because an error is not a slow load. Three sentences rather than one, since 'something went wrong' would be true of all of them and useful for none: 403 'That page isn't yours to open - only the owner can open a colleague's operating page, yours is right here'; 404 'That person isn't in this company - they may have left, or the link may be out of date'; anything else 'The operating score didn't load'. A 'Go to my operating page' button on the two that came from a ?user= link. Also stopped react-query retrying a refusal: no number of retries turns a 403 into a 200, and the three extra round trips only delayed the page saying so (retry skips 401/403/404). BROWSER-VERIFIED across all three real users: Anand hand-typing Priya's URL now gets the 403 card, the owner with a made-up id gets the 404 card, and the button returns to a working page. 3 tests.</t>
+        </is>
+      </c>
+      <c r="L335" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (access walk, owner to nth level)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D30" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L335"/>
+  <dimension ref="A1:L336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24888,6 +24888,63 @@
         </is>
       </c>
       <c r="L335" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (access walk, owner to nth level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.51</t>
+        </is>
+      </c>
+      <c r="B336" s="28" t="inlineStr">
+        <is>
+          <t>frontend lib/perms.js, components/Layout.js, pages/OperatingScore.js</t>
+        </is>
+      </c>
+      <c r="C336" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D336" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E336" s="28" t="inlineStr">
+        <is>
+          <t>A role has one set of words, and the header reads them</t>
+        </is>
+      </c>
+      <c r="F336" s="28" t="inlineStr">
+        <is>
+          <t>From the access walk: the header printed the stored key. Every non-owner saw 'Accounts_&amp;_buyer_payments' under their own name, on every screen, because {user.role} under CSS capitalize only touches the first letter of each word and leaves the underscores exactly where they are.</t>
+        </is>
+      </c>
+      <c r="G336" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H336" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I336" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K336" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. lib/perms.roleLabel(role, tenantRoles, fallback) takes the company's own words first - the owner names their roles in Settings - with the humanised key as the fallback for a role this tenant does not list. That fallback is the normal case one line up in the same menu: the workspace switcher shows the role held in ANOTHER company, whose role list this one has never seen, so humanising the key is the best that is honest there. Third field to reach a shared home after the same bug (humanStage, then TASK_STATUS_LABELS) - a stored value on a founder's screen is a bug, not a style. The Ops page had grown its own copy of the logic and now reads the shared one, so the two cannot drift. Browser-verified signed in as Anand. 1 test.</t>
+        </is>
+      </c>
+      <c r="L336" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29 (access walk, owner to nth level)</t>
         </is>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L336"/>
+  <dimension ref="A1:L337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24947,6 +24947,63 @@
       <c r="L336" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29 (access walk, owner to nth level)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.52</t>
+        </is>
+      </c>
+      <c r="B337" s="28" t="inlineStr">
+        <is>
+          <t>frontend lib/departments.js, lib/perms.js, components/Layout.js, components/StageWorkReview.js, pages/MyWork.js, pages/Team.js, pages/Leave.js, pages/Contacts.js, pages/OperatingScore.js, pages/admin/AdminSections.js, pages/admin/Tenant360Section.js</t>
+        </is>
+      </c>
+      <c r="C337" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D337" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E337" s="28" t="inlineStr">
+        <is>
+          <t>A role reads the same on every screen - six implementations become one</t>
+        </is>
+      </c>
+      <c r="F337" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: 'sweep the rest of the role labels .. COMPLETE APPLICATION'. The sweep found why the key kept leaking onto screens, and it was not carelessness at any one call site: the codebase held SIX implementations of 'name this role' - lib/departments.deptName (whose own docstring from 2026-09-21 already said 'one helper, so every screen that names a department says the same words'), lib/perms.roleLabel (added that same morning without noticing the first one existed), MyWork.teamLabel, Team.roleName, Team.roleNameFor with its own humanize, and OperatingScore.roleLabelFor. Six copies is how a screen ends up printing sales_&amp;_order_management: not because anyone chose to, but because the copy within reach did not have the fix.</t>
+        </is>
+      </c>
+      <c r="G337" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H337" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I337" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K337" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. One function in lib/departments - the oldest and best of the six, since it already handled _&amp;_ - now with roleWords (the key as words, title-cased per word, which Team's humanize did and this file's own fallback did not) and roleLabel(key, roles, fallback); deptName delegates. The other five are gone or reduced to a call. TEN RENDER SITES FIXED: the people pickers in My Work (who does a task, who helps, who is waited on, the New Task assignee), Leave (who covers your approvals, and the team approver list), Contacts (who owns a contact), the stage-work review, both lines in the header, 'Among the &lt;role&gt; peers' on a person's Ops page, and three in the platform admin console, which looks at other people's companies. The fallback is safe in the two places that cannot know the labels - the workspace switcher (a role held in ANOTHER company) and the admin console - because the keys are slugs of the labels. Each caller keeps its own word for nobody: 'Member' in the header, 'Unassigned' on Team, blank in a picker. BROWSER-VERIFIED as owner and as two members: no underscored key anywhere on Team, My Work or Ops, and the New Task picker reads 'Anand Rao - Accounts &amp; Buyer Payments'. Caught on the way: the import-insertion landed inside a multi-line import in two files and broke the build - fixed, and the tests now assert each import is a top-level statement. 29 tests (tests/test_a_role_reads_the_same_everywhere.py).</t>
+        </is>
+      </c>
+      <c r="L337" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D30" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L337"/>
+  <dimension ref="A1:L338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25004,6 +25004,63 @@
       <c r="L337" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.53</t>
+        </is>
+      </c>
+      <c r="B338" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/Tasks.js, pages/Captures.js, pages/ContactProfile.js, pages/MyWork.js, pages/admin/ImpersonationSection.js, hooks/useDexConversation.js</t>
+        </is>
+      </c>
+      <c r="C338" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D338" s="28" t="inlineStr">
+        <is>
+          <t>People + Growth</t>
+        </is>
+      </c>
+      <c r="E338" s="28" t="inlineStr">
+        <is>
+          <t>The role sweep finishes - the phone included, and a seventh copy that was shadowing the shared one</t>
+        </is>
+      </c>
+      <c r="F338" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh: 'CHECK .. DO WE IMPLEMENTED IN THE MOBILE PERSPECTIVE'. The phone has no role text of its own - the avatar line that carried it is desktop-only (hidden xl:block) - so the question is really whether the screens a phone DOES show were all covered. Re-grepping for the answer turned up eight more render sites the first sweep's pattern had missed, and a seventh implementation of the helper.</t>
+        </is>
+      </c>
+      <c r="G338" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H338" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I338" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K338" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. THE SEVENTH COPY: Tasks.js had `const roleLabel = (key) =&gt; ...` INSIDE NewTaskDialog, so for that whole component - the live New Task form, reached from My Work - the import resolved to the local copy instead. Invisible, and exactly the drift this sweep exists to end. EIGHT MORE SITES: the WhatsApp capture card in the Finance inbox (the reviewer's team, the sender's role, and 'routed to the X team'), a contact's open work, what Dex reads back about a decision it just captured ('3 tasks for X team'), the platform admin's impersonation list, the one inside MyWork that had the logic but not the helper, and three in Tasks.js's TaskBoard - which is unreachable since WE-14 retired its import, fixed anyway because a stored key left in dead code comes back the day somebody revives it. CaptureCard and ContactProfile's Table have no tenant in scope, so they take the humanised fallback; reaching for tenant?.roles there would have been a ReferenceError, not a label. MOBILE-VERIFIED at 375px as the owner and as a member: no underscored key on Ops, Team or My Work, no sideways scroll, and the New Task picker reads 'Anand Rao - Accounts &amp; Buyer Payments'. A test walks components/mobile and fails if a role key is ever rendered there. 10 more tests (39 in the file).</t>
+        </is>
+      </c>
+      <c r="L338" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (mobile check of the role sweep)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D30" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L338"/>
+  <dimension ref="A1:L340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25061,6 +25061,120 @@
       <c r="L338" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29 (mobile check of the role sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.54</t>
+        </is>
+      </c>
+      <c r="B339" s="28" t="inlineStr">
+        <is>
+          <t>backend routers/ledger.py; frontend pages/finance/FinanceAi.jsx</t>
+        </is>
+      </c>
+      <c r="C339" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D339" s="28" t="inlineStr">
+        <is>
+          <t>Finance cluster</t>
+        </is>
+      </c>
+      <c r="E339" s="28" t="inlineStr">
+        <is>
+          <t>The finance AI panel notices when the figures move</t>
+        </is>
+      </c>
+      <c r="F339" s="28" t="inlineStr">
+        <is>
+          <t>Found walking Finance at phone width. The AI Analysis panel on Revenue read 'No income data found - revenue picture is completely blank / Zero revenue records: Rs 0 billed' directly above cards reading Billed Rs 13,58,500 - 3 invoices. On Expenses it went further: 'Zero records found: data pipeline may be broken' over a list of three real expenses - telling a founder their books are broken when they are not, on the one page whose whole job is to be trusted about money. db.ledger_ai was cleared ONLY by a full finance re-sync, never when an invoice, expense or payment was written, and the client held its first answer for the whole session (staleTime: Infinity). The generator was never at fault - pressing Refresh produced a good, true analysis. Nothing ever asked it again.</t>
+        </is>
+      </c>
+      <c r="G339" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H339" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I339" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K339" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. The analysis records WHAT IT WAS WRITTEN FROM (`basis`, a hash of the finance context minus the wall clock, so an overnight view does not regenerate for nothing) and GET /ledger/ai/{scope} regenerates when that no longer matches. WHY THE FIGURES AND NOT A TIMESTAMP: the cheap check used everywhere else here is /api/pulse's count-and-newest-stamp, and it does not work on this data - NONE of the thirteen finance update sites in ledger.py writes updated_at, so marking an invoice paid (amount_paid + status, nothing else) would sail straight past it, and that is the single change a receivables analysis most needs to notice. A row written before this ships carries no basis and is rewritten once. Client: staleTime Infinity -&gt; 60s, so returning to Finance asks again; the server hands back the cached analysis unchanged when nothing has moved, so that ask is a read, not an AI call. A 60-SECOND GRACE WINDOW WAS TRIED AND REVERTED: it collapses a burst of tab-flicks to one lookup and reintroduces this very bug on the likeliest path there is - raise the first invoice, open Finance, read that you have none. The check costs a read of the rows the page is already showing (~2s against the remote dev database); correctness on that path is worth more. BROWSER-PROVED end to end on a phone: analysed empty, seeded three invoices and three expenses on the scratch DB, reloaded WITHOUT pressing Refresh, and got 'Rs 9.66L receivables at risk - chase Bluewave before Oct 7 / Rs 48,500 Target Sourcing due TOMORROW'. Probe data removed after. 9 tests.</t>
+        </is>
+      </c>
+      <c r="L339" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (mobile check of CRM and Finance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.55</t>
+        </is>
+      </c>
+      <c r="B340" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/CRM.js</t>
+        </is>
+      </c>
+      <c r="C340" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D340" s="28" t="inlineStr">
+        <is>
+          <t>Finance cluster</t>
+        </is>
+      </c>
+      <c r="E340" s="28" t="inlineStr">
+        <is>
+          <t>The CRM's empty card speaks for the tab, not the company</t>
+        </is>
+      </c>
+      <c r="F340" s="28" t="inlineStr">
+        <is>
+          <t>From the same walk, and unavoidable on a phone because the two sit in one glance: the tab chips read 'Buyers 0 - Partners 0 - Suppliers 1' and three centimetres below, 'No relationships yet - Add your first one from the Add contact button'. One supplier is on record; the card says nobody is. The button underneath had it right all along ('Add your first buyer') - only the heading and the line above it were speaking for everybody, because the card fires whenever the CURRENT list is empty and its words were written for a brand-new workspace.</t>
+        </is>
+      </c>
+      <c r="G340" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H340" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I340" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K340" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. anyContacts, off the tab counts already in scope. An empty tab in a company that has contacts now reads 'No buyers yet - Your other lists have people in them, this one is empty'; a genuinely new workspace still gets 'No relationships yet' and the welcome, which is right exactly once - when it is true; and a filter that matches nothing keeps its own words, which it already had. Browser-verified at 375px. 5 tests.</t>
+        </is>
+      </c>
+      <c r="L340" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (mobile check of CRM and Finance)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -2431,14 +2431,14 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D30" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L340"/>
+  <dimension ref="A1:L341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25175,6 +25175,63 @@
       <c r="L340" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29 (mobile check of CRM and Finance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.56</t>
+        </is>
+      </c>
+      <c r="B341" s="28" t="inlineStr">
+        <is>
+          <t>frontend components/OperatingModelEditor.js, components/StageWorkReview.js</t>
+        </is>
+      </c>
+      <c r="C341" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D341" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E341" s="28" t="inlineStr">
+        <is>
+          <t>The operating model editor fits a phone, and stops opening OS wheels</t>
+        </is>
+      </c>
+      <c r="F341" s="28" t="inlineStr">
+        <is>
+          <t>Found walking Settings at 375px. Settings &gt; Operations is where an owner decides how work moves - pipelines, stages, task templates, approval gates - and on a phone half of it could not be reached: the stage's role picker was cut off by 22px, the evidence tick by 37px and every row's delete button by 122px. The page does not scroll sideways, so those were not awkward, they were gone. The rows were single-line flexes built for a desktop with no way to wrap. The pickers were native &lt;select&gt;, 76 of them, which on a phone opens the OS wheel - against the rule the rest of the app follows with GlassSelect. The same two faults were in StageWorkReview, which is worse: that is an ONBOARDING step, so a new owner meets it on their phone before anything else.</t>
+        </is>
+      </c>
+      <c r="G341" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H341" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I341" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K341" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. EVERY ROW STACKS: the stage name takes a line with its move/delete buttons; days and the stage owner wrap onto the next; a task template's title takes a line with its delete, and the role picker plus the evidence tick wrap under it. Same shape in StageWorkReview. EVERY PICKER IS A GlassSelect (80 of them), wearing smSel - the same border as the inputs beside it - so the row still reads as one form; variant is deliberately NOT 'pill', which is the 48px page-header shape and would tower over these fields. Each one is min-w + flex-1, so it stays readable but gives way rather than pushing the delete off the edge again. The icon buttons went from p-1 (~22px) to a 36px target, Sprint 16's rule applied where it was worst, and the checkboxes to h-4 w-4. MEASURED AFTER, at 375px: 0 clipped controls, 0 native selects, 0 buttons under 32px, no sideways scroll; a picker opened, listed its six departments, changed the value, and its menu fitted the viewport. Desktop at 1440px re-checked: 0 clipped, and the editor column is narrow at any width so the stacked layout serves both. 12 tests (tests/test_the_operating_model_fits_a_phone.py); the native-select assertion strips comments first, because the comment explaining the fix mentions the thing it forbids.</t>
+        </is>
+      </c>
+      <c r="L341" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (mobile check of Settings and Team)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 220 of 323 items Done  (67%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 31 of 39 Done.</t>
+          <t>Epic 6 progress: 238 of 341 items Done  (70%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 49 of 57 Done.</t>
         </is>
       </c>
     </row>
@@ -2430,11 +2430,15 @@
           <t>Workflows + tasks (operations)</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>48</v>
-      </c>
-      <c r="D30" t="n">
-        <v>56</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6035,7 +6039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L341"/>
+  <dimension ref="A1:L342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25232,6 +25236,63 @@
       <c r="L341" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29 (mobile check of Settings and Team)</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.57</t>
+        </is>
+      </c>
+      <c r="B342" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/Signup.js, pages/onboarding/BuildReveal.js, lib/onboardingDraft.js; backend routers/auth.py, models/auth.py, services/auth/onboarding_drafts.py</t>
+        </is>
+      </c>
+      <c r="C342" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D342" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E342" s="28" t="inlineStr">
+        <is>
+          <t>A signup you can come back to - /signup stops opening blank, and the draft it built from is closed</t>
+        </is>
+      </c>
+      <c r="F342" s="28" t="inlineStr">
+        <is>
+          <t>Found walking the whole signup at 375px with real taps. TWO FAULTS, ONE CAUSE - resuming was never finished. (1) /signup came back BLANK with a saved draft in localStorage: React said phase 'build', draftReady true, while the screen showed the basics slot. AnimatePresence mode='wait' holds the next child until the last has finished leaving, and the basics node changed key in the tick it was created - it never appeared, so it never left, so nothing after it mounted. BuildReveal had the same deadlock between 'building' and 'preview', stopping a resumed signup at 0% with no request in flight. The draft that causes it is in the browser, so it came back on every reload with no way out. (2) The wizard never sent draft_id to /register, so FIX-001-D's merge AND mark_completed have both been dead since they shipped: a workspace was created and its draft still read completed_at null. Proven on the scratch DB.</t>
+        </is>
+      </c>
+      <c r="G342" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H342" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I342" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K342" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. Signup: the waiting card moved OUT of the AnimatePresence (nothing is keyed until the phase is known) and setDraftReady moved into a .finally. BuildReveal: stage/bp/pct/welcome initialise FROM savedBlueprint instead of travelling to it, and a resumed build asks the model for nothing. register now sends draft_id + draft_token; the server verifies the token (GET/PATCH have required it since RBAC-01) and refuses an already-consumed draft. get_draft's docstring corrected - it never filtered completed drafts. Browser-proved: resume lands on the review, CTA enters the app, draft completed_at + tenant_id set. Also checked and fine at 375px: every field's keyboard (tel/email/url), no horizontal scroll, no native selects, no tap target under 32px, the 27-option industry GlassSelect and the 11-language native-script grid. 12 tests. CORRECTION: an earlier report in this session that the final CTA was dead was wrong - that was synthetic event driving.</t>
+        </is>
+      </c>
+      <c r="L342" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (mobile check of onboarding and signup)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 238 of 341 items Done  (70%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 49 of 57 Done.</t>
+          <t>Epic 6 progress: 239 of 342 items Done  (70%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 50 of 58 Done.</t>
         </is>
       </c>
     </row>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6039,7 +6039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L342"/>
+  <dimension ref="A1:L343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25293,6 +25293,63 @@
       <c r="L342" s="28" t="inlineStr">
         <is>
           <t>Yokesh 2026-09-29 (mobile check of onboarding and signup)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.58</t>
+        </is>
+      </c>
+      <c r="B343" s="28" t="inlineStr">
+        <is>
+          <t>frontend lib/api.js (formatApiError - 139 call sites, 35 files)</t>
+        </is>
+      </c>
+      <c r="C343" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D343" s="28" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="E343" s="28" t="inlineStr">
+        <is>
+          <t>A refused call says what to do about it, instead of quoting the parser</t>
+        </is>
+      </c>
+      <c r="F343" s="28" t="inlineStr">
+        <is>
+          <t>Found on the signup reveal, under "Couldn't create your workspace": "email: value is not a valid email address: The part after the @-sign contains invalid characters: '@', SPACE." That is pydantic talking to a developer, printed at a founder - nobody outside this repo knows what an @-sign rule is, and the one thing they needed (go back and fix the address) is the one thing it does not say. FUP-46 was right about the SHAPE of a 422 and wrong about the words.</t>
+        </is>
+      </c>
+      <c r="G343" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H343" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I343" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K343" s="28" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-09-29. formatApiError translates from pydantic's STABLE `type`, never from `msg` (prose that changes between versions and carries the internals), and names the field in the founder's own word: 'That email address does not look right.', 'Your company name is needed.', 'Check the amount.' An unknown rule still gets a sentence rather than the parser's diary. A detail we wrote ourselves is a STRING and passes through untouched; our {code,message} shape speaks through its message. One field is never read out twice. Nothing renders as [object Object] any more. 19 tests, which RUN the real function in node against payloads taken off the wire from the dev server, and the new sentence was confirmed on the reveal screen itself.</t>
+        </is>
+      </c>
+      <c r="L343" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-09-29 (error copy, from the onboarding mobile check)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 239 of 342 items Done  (70%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 50 of 58 Done.</t>
+          <t>Epic 6 progress: 242 of 341 items Done  (71%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 50 of 58 Done.</t>
         </is>
       </c>
     </row>
@@ -1638,15 +1638,19 @@
           <t>Operating Score</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>39</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>51%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -6221,7 +6225,7 @@
       <c r="J3" s="13" t="inlineStr"/>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Score numeral counts up (CountUp, reduced-motion guarded); ArcGauge ring fill doesn't animate from 0 on mount.</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED. No animation on the ring and no prefers-reduced-motion branch. Worth knowing before picking it up: ScoreRing is hidden below lg (OperatingScore.js:286), so this is a desktop-only flourish unless the ring earns a place on the phone first.</t>
         </is>
       </c>
       <c r="L3" s="13" t="inlineStr">
@@ -6781,7 +6785,7 @@
       <c r="J13" s="13" t="inlineStr"/>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: No hover WorkCoach mini-card on leaderboard rows.</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED. No onMouseEnter, HoverCard or tooltip on the leaderboard rows.</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -7279,13 +7283,13 @@
       </c>
       <c r="I22" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: ScoreMeter role=progressbar + values added; per-category descriptive aria-label + overall progressbar still missing.</t>
+          <t>Audited against the code 2026-10-02. DONE. Every category bar carries role=meter with aria-label, aria-valuenow/valuemin/valuemax (OperatingScore.js:225). DEVIATION, deliberate: the overall score is NOT a progressbar. It is read as text -- the number, / 100, the band word, then the caption -- and ScoreRing beside it is aria-hidden, which is the correct pairing: a screen reader gets the number and its meaning rather than a role announcing a bar it cannot see. If U7-16.4's audit disagrees, it is one attribute.</t>
         </is>
       </c>
       <c r="L22" s="13" t="inlineStr">
@@ -7335,13 +7339,13 @@
       </c>
       <c r="I23" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr"/>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: No OperatingScoreMobile / responsive mobile pass (also U7-17.1).</t>
+          <t>Audited against the code 2026-10-02. DONE, WITHOUT THE SEPARATE FILE. There is no OperatingScoreMobile.jsx and there should not be: the page is responsive throughout (sm:/lg: on the hero, the 2-up category grid, the leaderboard) and it was walked at 375px in the Sprint 25 mobile pass, where the real defects were found and fixed. A second file would be a second thing to keep true. DEVIATION: the category drill-down opens as an in-page panel, not a bottom sheet; it was checked on a phone and reads correctly.</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr">
@@ -7394,10 +7398,14 @@
           <t>Backlog</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.38</t>
+        </is>
+      </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: Weekly ops-score email opt-in toggle + template not built (frontend of U7-01.38).</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED. This is the owner-facing half of U7-01.38 -- do them together.</t>
         </is>
       </c>
       <c r="L24" s="13" t="inlineStr">
@@ -7450,10 +7458,14 @@
           <t>Backlog</t>
         </is>
       </c>
-      <c r="J25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>U7-01.39</t>
+        </is>
+      </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: Shareable one-pager token link + generator not built (frontend of U7-01.39).</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED. This is the owner-facing half of U7-01.39 -- do them together.</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
@@ -12281,7 +12293,7 @@
       <c r="J111" s="18" t="inlineStr"/>
       <c r="K111" s="18" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Mostly i18n action-verb labels; 1 literal 'Submit' + widespread uppercase labels remain.</t>
+          <t>Audited against the code 2026-10-02. SWEEP RUN 2026-10-02: ONE violation left in the whole app -- pages/Leave.js:176, a button that still says Submit (data-testid leave-submit). Everything else already uses an action verb. Closing this row is one label and the confirmation that follows it.</t>
         </is>
       </c>
       <c r="L111" s="18" t="inlineStr">
@@ -12337,7 +12349,7 @@
       <c r="J112" s="16" t="inlineStr"/>
       <c r="K112" s="16" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: No systematic top-20 error-message rewrite; raw system strings still leak (audit: 2 violations).</t>
+          <t>Audited against the code 2026-10-02. HALF SHIPPED 2026-09-29 as U7-25.58: formatApiError no longer prints the parser at the reader, which was the worst of it -- a founder was shown pydantic's @-sign rule on the signup reveal. WHAT IS LEFT is the app's OWN strings, roughly 20 of them in catch blocks. Most are already human but stop at what happened and never say what to do; the biggest cluster is 'Could not save' x7. Also mixed register: 'Could not' and 'Couldn't' both appear, which belongs with U7-18.3.</t>
         </is>
       </c>
       <c r="L112" s="16" t="inlineStr">
@@ -12449,7 +12461,7 @@
       <c r="J114" s="16" t="inlineStr"/>
       <c r="K114" s="16" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Confirm/Cancel/Discard vocab partly centralized in i18n but used ad-hoc across 24 files; no enforced pairing.</t>
+          <t>Audited against the code 2026-10-02. AUDITED 2026-10-02 and it is nearly there already: Cancel x8, Save x2, Discard x1, Confirm x1 -- the pairs are consistent. ONE outlier: an OK button in pages/desk/DexCapturePopup.jsx:418, which should say what dismissing it does. Small row; close it with that one button. Re-checked after the mobile-capacitor merge (2026-10-02): both findings still stand, only the line moved.</t>
         </is>
       </c>
       <c r="L114" s="16" t="inlineStr">
@@ -12615,7 +12627,7 @@
       </c>
       <c r="I117" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="J117" s="13" t="inlineStr">
@@ -12625,8 +12637,7 @@
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no operating_score_history collection, no daily cron, no history endpoint.
-Wire target: HeroCard sparkline (U7-01.3 shipped as demo).</t>
+          <t>Audited against the code 2026-10-02. MOST OF IT SHIPPED 2026-09-29. services/score_history.py writes operating_score_history, one row per company per IST day, _id = tenant:day so a retry cannot double-write, and no row at all when the score is still None. The sweep in workers/schedulers.py calls record_all under the existing leader lock. history_for(db, tenant, days) reads them back. STILL MISSING, and this is what keeps the row open: (1) nothing CALLS history_for -- there is no GET /api/operating-score-history; (2) the row stores overall, categories and counts but NOT employees[{id, score}], which U7-01.33 needs; (3) it rides the sweep tick rather than a 03:00 IST cron, which is a fair trade for not adding a scheduler but is not what this row says.</t>
         </is>
       </c>
       <c r="L117" s="13" t="inlineStr">
@@ -12686,8 +12697,7 @@
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no week-over-week company.delta (needs history).
-Wire target: HeroCard DeltaChip (U7-01.1 shipped as demo). Also enables per-employee deltas (U7-01.33).</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED, and it cannot be until U7-01.27 is finished and a month of rows exists. The frontend slot is already there and already honest: OperatingScore.js:651 renders a delta for the DEMO tenant only, so a real company is shown nothing rather than a guess.</t>
         </is>
       </c>
       <c r="L118" s="13" t="inlineStr">
@@ -12747,8 +12757,7 @@
       </c>
       <c r="K119" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no per-category drivers in payload; real tenants see blank driver rows.
-Wire target: CategoryCard drivers (U7-01.4 shipped as demo).</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED. OperatingScore.js:691 passes drivers={demo ? demoDrivers[cat] : []} -- a real tenant opens a category and gets an empty list. The drawer already has the slot and the label.</t>
         </is>
       </c>
       <c r="L119" s="13" t="inlineStr">
@@ -12808,8 +12817,7 @@
       </c>
       <c r="K120" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no /operating-score/drill/{category} endpoint; real tenants get 'not wired' fallback.
-Wire target: CategoryDrillModal (U7-01.5..8 shipped as demo).</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED. OperatingScore.js:692 passes drill={demo ? demoDrilldowns[cat] : null}. No /operating-score/drill route exists; the router has only GET /operating-score and the two work-coach routes.</t>
         </is>
       </c>
       <c r="L120" s="13" t="inlineStr">
@@ -12869,8 +12877,7 @@
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no /ai/operating-score-explain endpoint; Dex narrative demo-only.
-Wire targets: HeroCard narrative (U7-01.1) + DexExplainerCard (U7-01.9). Both shipped with hardcoded demo text.</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED. No POST /api/ai/operating-score-explain anywhere in routers/. demoDex is the placeholder standing in for it.</t>
         </is>
       </c>
       <c r="L121" s="13" t="inlineStr">
@@ -12920,7 +12927,7 @@
       </c>
       <c r="I122" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J122" s="13" t="inlineStr">
@@ -12930,8 +12937,7 @@
       </c>
       <c r="K122" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] PARTIAL: Suggested-action chips now derive from real stats client-side (karmaScore.js:40); not a backend field; 'lift' estimate dropped as dishonest.
-Wire target: SuggestedActions chip row (U7-01.10 shipped as demo).</t>
+          <t>Audited against the code 2026-10-02. DONE as lib/karmaScore.scoreActions(stats, categories), rendered by DoTheseFirst -- overdue tasks, open complaints, the weakest category (only when it is actually weak), and a first-close prompt, all from real stats with a route for each. TWO DEVIATIONS, both deliberate: derived in the frontend from the payload rather than returned by it, since every input is already on the wire; and it claims NO lift figure -- clear 3 overdue and your score rises 9 is a number nobody can honour. No waiting-decisions rule yet; add it when decisions carry a waiting state.</t>
         </is>
       </c>
       <c r="L122" s="13" t="inlineStr">
@@ -12986,13 +12992,12 @@
       </c>
       <c r="J123" s="13" t="inlineStr">
         <is>
-          <t>U7-01.11, U7-01.27</t>
+          <t>U7-01.27</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no per-employee week-over-week delta; leaderboard shows no delta chip.
-Wire target: Leaderboard per-row delta (U7-01.11 shipped as demo).</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED, and blocked: record_today stores overall, categories and counts but no employees[], so there is nothing to diff against. Finish U7-01.27 first.</t>
         </is>
       </c>
       <c r="L123" s="13" t="inlineStr">
@@ -13042,7 +13047,7 @@
       </c>
       <c r="I124" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Dropped</t>
         </is>
       </c>
       <c r="J124" s="13" t="inlineStr">
@@ -13052,8 +13057,7 @@
       </c>
       <c r="K124" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: BACKEND: weights hardcoded, not read from tenant; FormulaExplainer editor local-only.
-Wire target: FormulaExplainer weights editor (U7-01.17 shipped as demo). Also unlocks per-tenant score tuning (Manufacturer vs Services vs Distributor presets).</t>
+          <t>Audited against the code 2026-10-02. DROPPED, overtaken by Sprint 25. The weight sliders and FormulaPanel's setWeights were REMOVED from the Ops page: a score an owner can re-weight until it flatters them is not a measurement, and no two companies' scores would mean the same thing. Nothing reads tenant.operating_score_weights and nothing writes it. Reopen only if weights come back as a product decision, not as a control.</t>
         </is>
       </c>
       <c r="L124" s="13" t="inlineStr">
@@ -13093,7 +13097,7 @@
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="H125" s="13" t="inlineStr">
@@ -13113,8 +13117,7 @@
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: InlineCapture fake-sends; not wired to POST /api/voice-notes.
-Wire target: InlineCapture form (U7-01.15 shipped as demo).</t>
+          <t>Audited against the code 2026-10-02. RAISED P2 -&gt; P1, because this is not an absence, it is a LIE. InlineCapture's submit (OperatingScore.js:1291) clears the box, shows 'sent' for 2.4 seconds and makes NO request. It sits in the empty state a brand-new company sees first, so the one decision a founder types to turn their score on is silently discarded, and the page then goes on telling them they have no activity. Wire it to POST /api/voice-notes or take the box out; either is better than today.</t>
         </is>
       </c>
       <c r="L125" s="13" t="inlineStr">
@@ -13174,8 +13177,7 @@
       </c>
       <c r="K126" s="13" t="inlineStr">
         <is>
-          <t>[2026-08-20 karma-validation] KEEP: BACKEND: no 15-min per-tenant cache for explain endpoint (moot until 01.31).
-Companion to U7-01.31 -- ship together to keep cost bounded.</t>
+          <t>Audited against the code 2026-10-02. NOT STARTED, and nothing to cache until U7-01.31 exists.</t>
         </is>
       </c>
       <c r="L126" s="13" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -599,7 +599,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B113"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
@@ -1558,7 +1558,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 242 of 341 items Done  (71%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 50 of 58 Done.</t>
+          <t>Epic 6 progress: 247 of 346 items Done  (71%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 55 of 63 Done.</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2472,7 +2472,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E134"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -6043,8 +6043,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L343"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L348"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -25355,6 +25355,316 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.59</t>
+        </is>
+      </c>
+      <c r="B344" s="28" t="inlineStr">
+        <is>
+          <t>frontend components/common.js (LoadFailed); pages/CRM.js, MyWork.js, Workflows.js</t>
+        </is>
+      </c>
+      <c r="C344" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D344" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E344" s="28" t="inlineStr">
+        <is>
+          <t>A list that could not load stops reading as a list with nothing in it</t>
+        </is>
+      </c>
+      <c r="F344" s="28" t="inlineStr">
+        <is>
+          <t>Found by failing ONE endpoint in the browser. With /api/contacts answering 500 and auth healthy, CRM rendered 'Buyers 0 - Partners 0 - Suppliers 0' and said nothing else; the company has contacts. Pages read `data || []`, so a failed query and an empty one arrive identically, and the no-signal screen does not catch it (that fires only when /auth/me itself fails, so a PARTIAL outage - the common kind - walks past it). Worse than an ugly error: a confident wrong answer on the page about customers.</t>
+        </is>
+      </c>
+      <c r="G344" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H344" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I344" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. One shared LoadFailed in components/common.js: names what did not arrive, says the absence is not an answer, offers react-query's own retry. Asked BEFORE `length === 0` - the order is the fix. CRM, My Work and Workflows wired; My Work's two empty states stand down on isError; CRM's scope chips show en-dash rather than 0. Browser-proved on all three.</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. One shared LoadFailed in components/common.js: names what did not arrive, says the absence is not an answer, offers react-query's own retry. Asked BEFORE `length === 0` - the order is the fix. CRM, My Work and Workflows wired; My Work's two empty states stand down on isError; CRM's scope chips show en-dash rather than 0. Browser-proved on all three.</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (error-presentation walk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.60</t>
+        </is>
+      </c>
+      <c r="B345" s="28" t="inlineStr">
+        <is>
+          <t>frontend lib/api.js (formatApiError)</t>
+        </is>
+      </c>
+      <c r="C345" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D345" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E345" s="28" t="inlineStr">
+        <is>
+          <t>The server's own vocabulary stops being shown to founders</t>
+        </is>
+      </c>
+      <c r="F345" s="28" t="inlineStr">
+        <is>
+          <t>Saving company details against a 500 produced a toast reading, in its entirety, 'Internal Server Error'. Right mechanism, wrong words - no what-failed, no was-anything-saved, no what-now. FastAPI answers an unhandled exception with {detail: 'Internal Server Error'} and a string detail passes straight through, which is correct for the sentences we wrote and wrong for the one phrase we did not. Every 5xx in the app read like this.</t>
+        </is>
+      </c>
+      <c r="G345" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H345" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I345" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. FRAMEWORK_PHRASES maps HTTP's reason phrases to sentences that say what to do; matched WHOLE and case-insensitively, so a message of ours that merely contains 'not found' is untouched. Browser-proved: the same 500 now reads 'Something broke on our side. Nothing you did caused it - try again in a moment.'</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. FRAMEWORK_PHRASES maps HTTP's reason phrases to sentences that say what to do; matched WHOLE and case-insensitively, so a message of ours that merely contains 'not found' is untouched. Browser-proved: the same 500 now reads 'Something broke on our side. Nothing you did caused it - try again in a moment.'</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (error-presentation walk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.61</t>
+        </is>
+      </c>
+      <c r="B346" s="28" t="inlineStr">
+        <is>
+          <t>frontend components/common.js (ConfirmAction); Team.js, BrainDocuments.js, admin/{Announcements,Compliance,AdminSections}</t>
+        </is>
+      </c>
+      <c r="C346" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D346" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E346" s="28" t="inlineStr">
+        <is>
+          <t>Nothing asks an irreversible question through the browser any more</t>
+        </is>
+      </c>
+      <c r="F346" s="28" t="inlineStr">
+        <is>
+          <t>Seven live window.confirm sites. On a phone that is an OS sheet wearing none of this product's clothes; inside the Capacitor WebView it is worse. The real fault is recorded in this repo twice already (ASK-2, FUP-49): some browsers and embed contexts return false from it with NO VISIBLE UI, so the button looks dead and gets pressed again. Two were user-facing (erase a teammate, delete a Brain document); five were admin, including EXPORT-then-PERMANENTLY-DELETE a tenant and a live retention purge.</t>
+        </is>
+      </c>
+      <c r="G346" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H346" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I346" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. ConfirmAction in components/common.js, on the AlertDialog that Workflows already proved - focus-trapped, keyboard-dismissable, renders the same in every context. The confirm button says the DEED ('Erase Priya', 'Export and delete'), never OK, so it reads correctly with the question out of view. The tenant wipe's button now opens the question instead of starting the deletion.</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. ConfirmAction in components/common.js, on the AlertDialog that Workflows already proved - focus-trapped, keyboard-dismissable, renders the same in every context. The confirm button says the DEED ('Erase Priya', 'Export and delete'), never OK, so it reads correctly with the question out of view. The tenant wipe's button now opens the question instead of starting the deletion.</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (error-presentation walk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.62</t>
+        </is>
+      </c>
+      <c r="B347" s="28" t="inlineStr">
+        <is>
+          <t>frontend context/AuthContext.js, pages/Login.js</t>
+        </is>
+      </c>
+      <c r="C347" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D347" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E347" s="28" t="inlineStr">
+        <is>
+          <t>Signing back in puts you back where you were</t>
+        </is>
+      </c>
+      <c r="F347" s="28" t="inlineStr">
+        <is>
+          <t>A 401 mid-session lands you on /login having lost the page you were on. CORRECTION to the first report of this: the expiry TOAST was already there and correct ('You were signed out. Sign in again to carry on.') - the earlier check looked six seconds late, after it had auto-dismissed. What was missing is only the return.</t>
+        </is>
+      </c>
+      <c r="G347" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H347" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I347" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. The path is remembered in sessionStorage at the moment the session is lost (the tab that was thrown out, not every tab), read once by takeReturnTo() and cleared, so a later deliberate sign-in is not sent somewhere nobody asked for. /login is never a place to return to.</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. The path is remembered in sessionStorage at the moment the session is lost (the tab that was thrown out, not every tab), read once by takeReturnTo() and cleared, so a later deliberate sign-in is not sent somewhere nobody asked for. /login is never a place to return to.</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (error-presentation walk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.63</t>
+        </is>
+      </c>
+      <c r="B348" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C348" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D348" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E348" s="28" t="inlineStr">
+        <is>
+          <t>A link to a deleted task says so - the banner existed and was unreachable</t>
+        </is>
+      </c>
+      <c r="F348" s="28" t="inlineStr">
+        <is>
+          <t>Following ?task=&lt;deleted id&gt; dropped you on the list with no word about it. The interesting part is why: ASK-28's 'This task no longer exists' banner was already written, translated and dismissible. The effect that tidies ?task= out of the address ran ON MOUNT, in the same commit as the effect that opens the task, saw `openId` still null, decided the task had been closed and stripped the id. With the id gone `focusTaskId` went empty, `focusDenied` could never become true, and the banner was unreachable code.</t>
+        </is>
+      </c>
+      <c r="G348" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H348" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I348" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. `hadOpen` makes closing mean closing - the address is tidied only after the task has really been open - and a denied or missing task keeps the id the banner is about. The tidy-up also moved onto the close handler itself, where no render order can race it. Both proved in the browser: the banner renders for a dead link, and closing a real task still clears the address.</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. `hadOpen` makes closing mean closing - the address is tidied only after the task has really been open - and a denied or missing task keeps the id the banner is about. The tidy-up also moved onto the close handler itself, where no render order can race it. Both proved in the browser: the banner renders for a dead link, and closing a real task still clears the address.</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (error-presentation walk)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25422,7 +25732,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -599,7 +599,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B113"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
@@ -1558,7 +1558,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 247 of 346 items Done  (71%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 55 of 63 Done.</t>
+          <t>Epic 6 progress: 249 of 348 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 57 of 65 Done.</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2472,7 +2472,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E134"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
@@ -6043,8 +6043,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L348"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:L350"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -25665,6 +25665,120 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.64</t>
+        </is>
+      </c>
+      <c r="B349" s="28" t="inlineStr">
+        <is>
+          <t>frontend lib/api.js (response interceptor)</t>
+        </is>
+      </c>
+      <c r="C349" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D349" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E349" s="28" t="inlineStr">
+        <is>
+          <t>Every surface gets the translated error, not the 141 that asked for it</t>
+        </is>
+      </c>
+      <c r="F349" s="28" t="inlineStr">
+        <is>
+          <t>A census of the whole codebase: 545 raises on the server, and on the client 141 call sites use formatApiError while 88 MORE read e.response.data.detail and render it RAW. So U7-25.60's fix reached two thirds of the app and missed a third: approving a decision against a 500 still put the words 'Internal Server Error' on screen, proved in the browser.</t>
+        </is>
+      </c>
+      <c r="G349" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H349" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I349" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. The detail is rewritten ONCE in the axios response interceptor, so by the time any call site sees it the framework's phrase is already a sentence - including the 88 that never asked, and every one written tomorrow. Whole matches only; a dict detail (our {code,message}) is untouched; wrapped in try so tidying the words can never swallow the error. Verified live on the decision-approve path, which was the proof case.</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (codebase-wide error census)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.65</t>
+        </is>
+      </c>
+      <c r="B350" s="28" t="inlineStr">
+        <is>
+          <t>backend routers/billing.py, services/otp.py, routers/brain.py</t>
+        </is>
+      </c>
+      <c r="C350" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D350" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E350" s="28" t="inlineStr">
+        <is>
+          <t>The server stops naming its own plumbing in front of a founder</t>
+        </is>
+      </c>
+      <c r="F350" s="28" t="inlineStr">
+        <is>
+          <t>From the same census, reading all 279 distinct detail strings. The worst: /billing/checkout is OWNER-FACING and answered 'Billing not configured. Set BILLING_LANDING_URL + RAZORPAY_KEY_ID env vars.' - an SME owner pressing Upgrade was handed our deployment instructions. Also 'Invalid plan_key. Purchasable plans: ...' (a field name), 'Internal error: OTP issued without tenant scope' (a code bug, shown mid sign-in), 'SMS provider returned an unexpected response', and 'Unsupported format'.</t>
+        </is>
+      </c>
+      <c r="G350" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H350" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I350" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. Upgrade now says it is not switched on yet AND that nothing has been charged, which is the thing a founder is actually afraid of. The OTP code-bug keeps its loudness where it belongs - logger.error with the diagnosis, a plain 500 on screen (and services/otp.py gained the module logger it never had, so that line cannot NameError). Bare 'Not found' x many was deliberately NOT rewritten at source: the interceptor already turns it into a sentence.</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (codebase-wide error census)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25732,7 +25846,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 249 of 348 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 57 of 65 Done.</t>
+          <t>Epic 6 progress: 252 of 351 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 60 of 68 Done.</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L350"/>
+  <dimension ref="A1:L353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25776,6 +25776,177 @@
       <c r="L350" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-02 (codebase-wide error census)</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.66</t>
+        </is>
+      </c>
+      <c r="B351" s="28" t="inlineStr">
+        <is>
+          <t>frontend lib/api.js, lib/aiConsent.js, pages/Team.js, pages/onboarding/BuildReveal.js</t>
+        </is>
+      </c>
+      <c r="C351" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D351" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E351" s="28" t="inlineStr">
+        <is>
+          <t>A structured refusal reaches the person instead of throwing inside React</t>
+        </is>
+      </c>
+      <c r="F351" s="28" t="inlineStr">
+        <is>
+          <t>Covering the four status codes the earlier sweep had not forced (402/410/415/451). 402 found a real bug: 17 server raises use our {code, message} shape, and the 88 call sites that pass the detail straight to toast.error handed React an OBJECT. React does not render objects - 'Objects are not valid as a React child (found: object with keys {code, message, seat_limit})', thrown during the commit. Forced on the decision-approve path: the founder saw NOTHING and the tree was left broken; in production that unmounts it. 410 and 415 needed no change, their wording was already human.</t>
+        </is>
+      </c>
+      <c r="G351" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H351" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I351" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. The interceptor flattens a structured detail to its sentence and keeps the object on detail_full; the four places that branch on `code` were rewired - the seat wall (re-verified rendering with its counts), signup's phone/email branches, the consent check, and formatApiError's own dict branch. test_browser_walk_fixes pinned the old seat-wall line and caught the change, which is the test doing its job; its assertion follows the new shape and its promise is unchanged.</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (402/410/415/451 sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.67</t>
+        </is>
+      </c>
+      <c r="B352" s="28" t="inlineStr">
+        <is>
+          <t>frontend lib/aiConsent.js, lib/api.js</t>
+        </is>
+      </c>
+      <c r="C352" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D352" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E352" s="28" t="inlineStr">
+        <is>
+          <t>One refusal, one toast - and the way out lands on the switch</t>
+        </is>
+      </c>
+      <c r="F352" s="28" t="inlineStr">
+        <is>
+          <t>A 451 produced TWO toasts: the rich one carrying the way out, and a plain copy from whichever of the 88 call sites made the request. One fact said twice, and only one of the two had the button on it.</t>
+        </is>
+      </c>
+      <c r="G352" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H352" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I352" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. The file's own quiet period already existed for this; it just could not see the second route. toast.error is wrapped ONCE and drops a message that is EXACTLY the consent sentence while a consent toast is live - sonner's toast is one shared object, so all 88 sites are covered without touching any. The interceptor hands the call site the same sentence so the two routes can recognise each other. FIRST VERSION SHOWED NOTHING: showAiConsentToast sets the timestamp then calls toast.error, so it met its own guard; it uses the unwrapped reference now, and a test pins that. Checked in the browser that a 500 inside the 8s window still shows. The button lands on /settings?tab=business#ai-consent with the card in view at 100px - the destination was tested, not just the href.</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (451 duplicate + destination)</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.68</t>
+        </is>
+      </c>
+      <c r="B353" s="28" t="inlineStr">
+        <is>
+          <t>frontend lib/navigate.js (new), lib/aiConsent.js, hooks/useNativeBack.js, components/Layout.js</t>
+        </is>
+      </c>
+      <c r="C353" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D353" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E353" s="28" t="inlineStr">
+        <is>
+          <t>Code that is not a component can go somewhere without restarting the app</t>
+        </is>
+      </c>
+      <c r="F353" s="28" t="inlineStr">
+        <is>
+          <t>The consent toast's way out was window.location.href - a full document load: the bundle parsed again, every cache dropped, the session re-fetched. A blink in a browser; in the installed PWA and the Capacitor shell it is the app restarting in front of somebody who pressed a button on a toast. The repo had already paid for this lesson once (the note on EmptyState about an &lt;a href&gt; reloading the whole app in the installed PWA), and the Capacitor work makes it live again.</t>
+        </is>
+      </c>
+      <c r="G353" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H353" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I353" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. NOT A NEW MECHANISM: lib/native/links already takes a go(path) and useNativeBack already supplies navigate because it is mounted at the root inside the Router. lib/navigate is that pattern named and reused, registered from the same place for the same stated reason - a second way to navigate would have been the worse outcome. goTo falls back to a real location change when no router is listening (before mount, in a test), so no caller has to ask which happened. It also scrolls the hash itself, over a 2.5s rAF budget, because the browser only jumps to an anchor on a real document load and the target is not on screen yet - the page has to mount, its tab has to switch, its data has to arrive. Layout's workspace switch KEEPS its full load deliberately and now says so: a different workspace is a different everything, and the reload is the feature. Browser-proved: an in-page marker SURVIVED the navigation (so no document load) and the AI card still landed in view at 100px on the Business tab.</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (SPA navigation for the toast action)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 252 of 351 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 60 of 68 Done.</t>
+          <t>Epic 6 progress: 253 of 352 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 61 of 69 Done.</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L353"/>
+  <dimension ref="A1:L354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25947,6 +25947,63 @@
       <c r="L353" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-02 (SPA navigation for the toast action)</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.69</t>
+        </is>
+      </c>
+      <c r="B354" s="28" t="inlineStr">
+        <is>
+          <t>backend tests/conftest.py, tests/_live_harness.py</t>
+        </is>
+      </c>
+      <c r="C354" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D354" s="28" t="inlineStr">
+        <is>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="E354" s="28" t="inlineStr">
+        <is>
+          <t>The suite rides out a slow network instead of going red</t>
+        </is>
+      </c>
+      <c r="F354" s="28" t="inlineStr">
+        <is>
+          <t>Four tests had failed intermittently for three sessions - always under the two parallel workers, always green alone: test_s5_niches::test_textile_baseline_full_flow (pymongo error), test_s2_functional::test_decision_approve_and_reject_lifecycle, test_s8_isolation_scenarios::test_tenant_deletion_removes_A_and_keeps_B, test_s4_onboarding::test_q1_opener_is_industry_aware_and_why_is_localized. 'Flaky test' was the wrong diagnosis: none of them is nondeterministic - the last one builds its opener from a TEMPLATE, not a model, so there was no AI variance to blame. What they share is the only thing they all touch, the with_test_db fixture, which connects to a REMOTE database.</t>
+        </is>
+      </c>
+      <c r="G354" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H354" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I354" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. MEASURED against the live test host: warm connect+ping 1.26/1.28/1.29/1.31s across fresh processes, bursts of 8 and 16 at median 1.3s with no errors - and one transient of 8.16 SECONDS, against a budget of serverSelectionTimeoutMS=8000. The budget sat exactly on the hiccup, so a blip of that size did not make a test slow, it made it FAIL, and the traceback pointed at whichever test was unlucky. That is why it read as four flaky tests in four files. Budget 8s -&gt; 30s in conftest and _live_harness (same remote, same cliff); server selection retries throughout its window so the healthy path is unchanged. maxPoolSize capped at 8 - one database, one coroutine, against a default ceiling of 100 sockets ~400 times a run. NOT DONE, deliberately: a retry wrapper (it would mask a genuinely down database by doubling the wait) and one shared client per worker (it needs a single persistent event loop, and this suite already has loop-affinity scar tissue - trading a known flake for subtler ones is the wrong direction). VALIDATED: three consecutive full suites green, 1911 / 1917 / 1917 passed. 6 tests pin the budget AND the measurement, so the next person finds the numbers before tightening it back.</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (flake hunt)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 253 of 352 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 61 of 69 Done.</t>
+          <t>Epic 6 progress: 255 of 354 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 63 of 71 Done.</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L354"/>
+  <dimension ref="A1:L356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26004,6 +26004,120 @@
       <c r="L354" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-02 (flake hunt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.70</t>
+        </is>
+      </c>
+      <c r="B355" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C355" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D355" s="28" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E355" s="28" t="inlineStr">
+        <is>
+          <t>My Work opens on a band that has work in it</t>
+        </is>
+      </c>
+      <c r="F355" s="28" t="inlineStr">
+        <is>
+          <t>Found walking every route in the browser looking for errors. At 620px My Work read 'PRIORITY High 0 Medium 3 Low 0' directly above 'Nothing here' - three open tasks, assigned to the person reading, one tap away in a column they could not see. Below lg only the SELECTED band's column is on screen and the band started at 'high' whatever the list held. Nothing was broken: the counts were right, the list was right, the filtering was right. The CHOICE of which column to show was wrong, and the result was the same contradiction the CRM empty card used to produce - a count and a list disagreeing in one glance.</t>
+        </is>
+      </c>
+      <c r="G355" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H355" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I355" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. Opens on the first band that HAS work, and only until the person chooses: a deliberate tap on an empty band is an answer ('nothing is high today'), and bouncing them out of it would be the page arguing with them. bandChosen tracks whose choice it is; turning AI priority off hands the choice back. Both halves proved in the browser - default lands on Medium with the three tasks, tapping High sticks on High. Nearly misreported as data loss: it was a saved {scope:'mine'} preference plus a 620px pane, checked against localStorage and each column's computed display before concluding.</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (whole-app browser sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.71</t>
+        </is>
+      </c>
+      <c r="B356" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/desk/useDeskMetrics.js</t>
+        </is>
+      </c>
+      <c r="C356" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D356" s="28" t="inlineStr">
+        <is>
+          <t>Decision Desk</t>
+        </is>
+      </c>
+      <c r="E356" s="28" t="inlineStr">
+        <is>
+          <t>The Desk stops asking for a ledger the viewer may not open</t>
+        </is>
+      </c>
+      <c r="F356" s="28" t="inlineStr">
+        <is>
+          <t>Found walking the app as a SALES MEMBER. Every Desk load fired GET /ledger/summary and took a 403 back. Nothing looked wrong on screen - the money tile is correctly hidden either way - which is exactly why it survived: a guaranteed-to-fail request on the busiest page in the product, once per member per load, landing in the logs and in any monitoring as a permission error that nobody caused.</t>
+        </is>
+      </c>
+      <c r="G356" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H356" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I356" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. The query is gated on the same canLedger the Ledger page already used for its own copy, so the two agree about who may run it. Verified both directions: no non-2xx on the Desk as a member, and the owner's 'To collect' tile is intact. Only visible because the sweep collected every non-2xx per route - this one is invisible to the eye.</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (member-perspective sweep)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 255 of 354 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 63 of 71 Done.</t>
+          <t>Epic 6 progress: 256 of 354 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 63 of 71 Done.</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="I125" s="19" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J125" s="13" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
-          <t>Audited against the code 2026-10-02. RAISED P2 -&gt; P1, because this is not an absence, it is a LIE. InlineCapture's submit (OperatingScore.js:1291) clears the box, shows 'sent' for 2.4 seconds and makes NO request. It sits in the empty state a brand-new company sees first, so the one decision a founder types to turn their score on is silently discarded, and the page then goes on telling them they have no activity. Wire it to POST /api/voice-notes or take the box out; either is better than today.</t>
+          <t>SHIPPED 2026-10-02. It posts to /voice-notes/text - the same endpoint the Desk's Dex well and the mobile sheet use, with the same words on success - so a decision captured here is the same object as one captured anywhere else. THREE THINGS THE ORIGINAL DID NOT HAVE: it can fail out loud now (it was incapable of failing, which is its own kind of wrong) through formatApiError; it invalidates operating-score/tasks/decisions/desk-summary, because the whole point of typing here is to watch the page stop being empty; and it respects the voice_capture permission, so a member who may not capture gets the Desk's own sentence rather than a box whose request will be refused. PROVED END TO END in the browser, not just at the network boundary: the POST carried {text, file_ids: []}, and the database then held the voice note (status done) AND the decision the AI made from it, 'Ship the indigo lot before Friday', pending_approval. Probe data removed, verified zero left. 7 tests, one of which pins the exact shape of the old pretence (setSent / the 2.4s 'sent' flag) so it cannot come back by accident.</t>
         </is>
       </c>
       <c r="L125" s="13" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 256 of 354 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 63 of 71 Done.</t>
+          <t>Epic 6 progress: 258 of 356 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 65 of 73 Done.</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L356"/>
+  <dimension ref="A1:L358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26118,6 +26118,120 @@
       <c r="L356" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-02 (member-perspective sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.72</t>
+        </is>
+      </c>
+      <c r="B357" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/Leave.js, Journal.js, Calendar.js</t>
+        </is>
+      </c>
+      <c r="C357" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D357" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E357" s="28" t="inlineStr">
+        <is>
+          <t>Three more lists admit they failed instead of reading as empty</t>
+        </is>
+      </c>
+      <c r="F357" s="28" t="inlineStr">
+        <is>
+          <t>Asked whether the UI error work was finished, the honest answer was no: the pattern had been wired into 3 pages and a census found 17 more surfaces with an empty state that never ask isError. Forcing their endpoints to 500 in the browser caught three lying. /journal showed the diary chrome and no entries. /calendar showed 'Nothing this week' over 'Meetings 0 Payments 0 Tasks 0'. /leave sat on 'Loading your leave...' FOR EVER - react-query had given up, the sentence had not, so the page promised something that was never coming; waiting feels like progress, which an empty list at least does not.</t>
+        </is>
+      </c>
+      <c r="G357" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H357" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I357" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. All three ask isError before the empty state answers, and the calendar's filter counts (including All) read an en-dash rather than 0 when nothing arrived. NOTE FOR THE NEXT TESTER, written into the test file: the honest message takes about TEN SECONDS to appear because react-query retries three times with backoff first - measured at 3.4s these pages still looked broken and the fix looked like it had not landed.</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (is the UI error work finished?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.73</t>
+        </is>
+      </c>
+      <c r="B358" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/Notifications.js, finance/WhatsAppCard.js, components/mobile/blocks/BriefBlocks.jsx</t>
+        </is>
+      </c>
+      <c r="C358" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D358" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E358" s="28" t="inlineStr">
+        <is>
+          <t>Three more empty states, and the two mark-read buttons that failed in silence</t>
+        </is>
+      </c>
+      <c r="F358" s="28" t="inlineStr">
+        <is>
+          <t>Finishing the census list. 'You're all caught up.' is a congratulation - said to somebody whose notifications failed to load it promises no approval is waiting when one may be. The brief's detail sheet said 'Nothing here right now' about the very number the founder had just tapped. The WhatsApp log's empty state is a DIAGNOSIS that sends an owner into Meta's console to check a callback URL - said when the log merely failed to load, it is an afternoon spent debugging a working integration. SEPARATELY, asked of the same 14 surfaces: what do they say when a BUTTON fails? Notifications' 'Mark all read' and each row's 'Mark read' called a bare async handler - a failure changed nothing on screen, said nothing, left a dot that would not clear and an unhandled rejection in the console.</t>
+        </is>
+      </c>
+      <c r="G358" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H358" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I358" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-02. Both buttons report now (verified live against a 500); `open` still swallows the mark deliberately, because failing to mark something read must not stop somebody reaching the thing it is about - which is why the buttons got wrappers rather than markRead being changed. RECORDED AS CORRECT, so they are not 'fixed' later by someone counting catches the same way: Brain's ask turns its failure into a reply in the conversation, and Layout's workspace list stays quiet while the switch itself reports. The three empty-state fixes are code-verified rather than forced: react-query holds the last good answer and the layout's bell fetches /notifications on EVERY route, so that list is never cold in a page already open. pages/Contacts.js is referenced nowhere - dead code, left alone.</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-02 (error status messages across the 14)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 258 of 356 items Done  (72%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 65 of 73 Done.</t>
+          <t>Epic 6 progress: 261 of 359 items Done  (73%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 68 of 76 Done.</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L358"/>
+  <dimension ref="A1:L361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26232,6 +26232,177 @@
       <c r="L358" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-02 (error status messages across the 14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.74</t>
+        </is>
+      </c>
+      <c r="B359" s="28" t="inlineStr">
+        <is>
+          <t>frontend index.js (QueryClient defaults)</t>
+        </is>
+      </c>
+      <c r="C359" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D359" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E359" s="28" t="inlineStr">
+        <is>
+          <t>A screen says something quickly instead of sitting half-built</t>
+        </is>
+      </c>
+      <c r="F359" s="28" t="inlineStr">
+        <is>
+          <t>The honest 'couldn't load this' shipped in U7-25.72 took SEVEN AND A HALF SECONDS to appear, and for most of that the page was neither loading nor failed - half-built and silent, which is the state a founder reads as broken. Measured in the browser: 4 attempts at 1.0s/2.1s/4.1s, message at 7.67s. AND A REFUSAL WAS RETRIED LIKE A BLIP: a 403 took the same four attempts and the same 7.6s - asking a server that had just said no, three more times, to be told no three more times.</t>
+        </is>
+      </c>
+      <c r="G359" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H359" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I359" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. A 4xx is an ANSWER, so it is not retried; 408 and 429 are the exceptions because they are the server saying 'later' rather than 'never'. One retry for everything else. Measured after: 500 -&gt; 2 attempts, 1.30s; 403 -&gt; 1 attempt, 0.27s. The retry budget was cut, not the recovery - refetchOnWindowFocus, refetchOnReconnect and the Try again button on the failure state are what a real outage comes back through.</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (step 1 of 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.75</t>
+        </is>
+      </c>
+      <c r="B360" s="28" t="inlineStr">
+        <is>
+          <t>frontend components/karma/PartyPicker.jsx</t>
+        </is>
+      </c>
+      <c r="C360" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D360" s="28" t="inlineStr">
+        <is>
+          <t>Finance cluster</t>
+        </is>
+      </c>
+      <c r="E360" s="28" t="inlineStr">
+        <is>
+          <t>A picker does not invite a duplicate supplier when its list failed to load</t>
+        </is>
+      </c>
+      <c r="F360" s="28" t="inlineStr">
+        <is>
+          <t>Proving the surfaces that had only been READ. Four hold no query at all (DeskDexWell, WorkflowsTile, FinanceRecords, FinanceForms - they take props) and both contact profiles already handled error. ONE WAS REAL, and it is the most expensive finding of the whole sweep: with /ledger/parties answering 500 the supplier picker on the expense form showed no matches and a cheerful 'Add E as a supplier', while Erode Yarn Mills sat in the CRM unmatched because the list had never arrived. Verified against that real contact. The founder is mid-expense, takes the offer, and the company now has two suppliers with one name and a ledger split across them. Every other lie in this sweep cost a reader a wrong impression; THIS ONE WRITES BAD DATA, and the damage outlives the outage.</t>
+        </is>
+      </c>
+      <c r="G360" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H360" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I360" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. The picker says the list did not arrive, ABOVE the add-new row, because that row is the trap. The popover also refused to open on error (open &amp;&amp; (rows.length &gt; 0 || isSuccess)), so a warning would have had nowhere to appear - it opens on isError now. The cheerful 'No suppliers in CRM yet' stands down on error, being a fact about the company rather than about the request. Healthy path re-verified: Erode Yarn Mills still matches, no warning.</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (step 2 of 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.76</t>
+        </is>
+      </c>
+      <c r="B361" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/Contacts.js (deleted)</t>
+        </is>
+      </c>
+      <c r="C361" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D361" s="28" t="inlineStr">
+        <is>
+          <t>Housekeeping</t>
+        </is>
+      </c>
+      <c r="E361" s="28" t="inlineStr">
+        <is>
+          <t>The retired Contacts page is deleted</t>
+        </is>
+      </c>
+      <c r="F361" s="28" t="inlineStr">
+        <is>
+          <t>E2-01 retired /contacts to a redirect; the file stayed with nothing importing it - 240 lines, one unused export (ContactsPanel). It was not free: its last change was 28d4ac3, this session's own role-label sweep, which counted one of its 'six implementations' in a file nobody renders. Dead code had already cost a round of maintenance.</t>
+        </is>
+      </c>
+      <c r="G361" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H361" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I361" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Verified unreachable before deleting (no import of pages/Contacts anywhere, no reference to ContactsPanel) and verified afterwards in the browser: /contacts still redirects to /crm and /contacts/:id still opens a profile, so old links keep working. A test asserts both, and that nothing mentions it again.</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (step 3 of 3)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 261 of 359 items Done  (73%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 68 of 76 Done.</t>
+          <t>Epic 6 progress: 269 of 367 items Done  (73%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 76 of 84 Done.</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L361"/>
+  <dimension ref="A1:L369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26403,6 +26403,462 @@
       <c r="L361" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-03 (step 3 of 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.77</t>
+        </is>
+      </c>
+      <c r="B362" s="28" t="inlineStr">
+        <is>
+          <t>frontend lib/api.js + components/common.js + ConnectionNotice.js</t>
+        </is>
+      </c>
+      <c r="C362" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D362" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E362" s="28" t="inlineStr">
+        <is>
+          <t>A save with no signal says why it failed and whether it saved</t>
+        </is>
+      </c>
+      <c r="F362" s="28" t="inlineStr">
+        <is>
+          <t>Creating a task offline put 'Create failed' on screen and nothing else -- no cause, no answer to 'did it save?'. Screens that could not load told someone in a lift it was 'a problem on our side'. And nothing said the connection had dropped until a save failed.</t>
+        </is>
+      </c>
+      <c r="G362" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H362" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I362" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. The interceptor writes down that a request went unanswered (offline vs timeout, read vs write); formatApiError says that instead of the shrug, and every toast.error carries it as the description under its own title -- 'Create failed / We couldn't reach DecisionOS, so nothing was saved'. A timeout says it MAY have saved. LoadFailed reads it until the next answer. A fixed pill says 'You're offline' the moment the device does, and 'Back online' on return. Verified in the browser: offline create, offline load, offline/online events.</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.78</t>
+        </is>
+      </c>
+      <c r="B363" s="28" t="inlineStr">
+        <is>
+          <t>frontend App.js Protected + context/AuthContext.js</t>
+        </is>
+      </c>
+      <c r="C363" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D363" s="28" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="E363" s="28" t="inlineStr">
+        <is>
+          <t>A link opened signed out survives sign-in</t>
+        </is>
+      </c>
+      <c r="F363" s="28" t="inlineStr">
+        <is>
+          <t>Tapping a link from an email or reminder while signed out went to sign-in with nothing written down; after sign-in the founder landed on the Desk, the link spent.</t>
+        </is>
+      </c>
+      <c r="G363" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H363" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I363" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Protected writes the address for after sign-in, only on a load that has had nobody signed in -- a deliberate sign-out is not brought back. Verified: signed out, opened /finance?tab=inbox, signed in through the real OTP form, landed on Finance &gt; Inbox.</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.79</t>
+        </is>
+      </c>
+      <c r="B364" s="28" t="inlineStr">
+        <is>
+          <t>frontend App.js (route *)</t>
+        </is>
+      </c>
+      <c r="C364" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D364" s="28" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="E364" s="28" t="inlineStr">
+        <is>
+          <t>A mistyped or old address says it could not find the page</t>
+        </is>
+      </c>
+      <c r="F364" s="28" t="inlineStr">
+        <is>
+          <t>Route * redirected to '/', which forwarded a signed-in person to the Desk -- /taks landed somewhere unrelated with no word about why.</t>
+        </is>
+      </c>
+      <c r="G364" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H364" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I364" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. 'We couldn't find that page' inside the app (sidebar kept, Take me home) for someone signed in; on its own with Sign in for anyone else. Production serves the SPA for unknown paths (server.js app.get('*')), so this reaches real users.</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.80</t>
+        </is>
+      </c>
+      <c r="B365" s="28" t="inlineStr">
+        <is>
+          <t>frontend App.js (ErrorBoundary placement)</t>
+        </is>
+      </c>
+      <c r="C365" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D365" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E365" s="28" t="inlineStr">
+        <is>
+          <t>One broken page costs that page, not the whole app</t>
+        </is>
+      </c>
+      <c r="F365" s="28" t="inlineStr">
+        <is>
+          <t>The only crash boundary sat outside the Layout: a page that threw took the sidebar and dock with it, never reset (even Back showed the apology), and said 'the rest of the app should still work' with nothing left to click.</t>
+        </is>
+      </c>
+      <c r="G365" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H365" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I365" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. A boundary inside the Layout keyed to the address: the navigation survives and leaving the page clears it. The outer boundary stays as the last resort with honest copy (reload; nothing saved is lost). Verified by feeding the Coach page a malformed answer: page fell over, sidebar stayed, clicking My Work recovered.</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.81</t>
+        </is>
+      </c>
+      <c r="B366" s="28" t="inlineStr">
+        <is>
+          <t>frontend components/DecisionDialog.js</t>
+        </is>
+      </c>
+      <c r="C366" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D366" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E366" s="28" t="inlineStr">
+        <is>
+          <t>A deleted decision is not called a refusal</t>
+        </is>
+      </c>
+      <c r="F366" s="28" t="inlineStr">
+        <is>
+          <t>Every failure to load a decision read 'Access restricted -- You don't have access to this decision': a deleted one (the owner told they lack access to their own company), a 500, no signal.</t>
+        </is>
+      </c>
+      <c r="G366" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H366" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I366" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Reads the server's status (routers/decisions already answers 404 vs 403): 403 keeps Access restricted; 404 says 'This decision isn't here'; anything else says what happened with a Try again. All three verified in the browser.</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.82</t>
+        </is>
+      </c>
+      <c r="B367" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C367" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D367" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E367" s="28" t="inlineStr">
+        <is>
+          <t>A link to a deleted task does not claim it was removed while open</t>
+        </is>
+      </c>
+      <c r="F367" s="28" t="inlineStr">
+        <is>
+          <t>Following a link to an already-deleted task showed the right banner AND a toast saying it was 'removed while you had it open' -- it never was open.</t>
+        </is>
+      </c>
+      <c r="G367" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H367" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I367" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. The live toast fires only for a task that had loaded; the banner alone speaks for a link that was spent before it arrived. Verified: banner, address kept, no toast.</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.83</t>
+        </is>
+      </c>
+      <c r="B368" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/WorkCoach.js + onboarding/BasicsFlow.js</t>
+        </is>
+      </c>
+      <c r="C368" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D368" s="28" t="inlineStr">
+        <is>
+          <t>Copy</t>
+        </is>
+      </c>
+      <c r="E368" s="28" t="inlineStr">
+        <is>
+          <t>Two more screens stop printing the stored role key</t>
+        </is>
+      </c>
+      <c r="F368" s="28" t="inlineStr">
+        <is>
+          <t>Coach's header read 'ANAND RAO - ACCOUNTS_&amp;_BUYER_PAYMENTS'; sign-up's existing-workspace line read 'You're in this one as sales_&amp;_order_management'. The role sweep had not listed either.</t>
+        </is>
+      </c>
+      <c r="G368" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H368" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I368" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Coach uses roleLabel with the company's own labels; sign-up uses roleWords (a role in ANOTHER company, no label list here). Verified: 'ACCOUNTS &amp; BUYER PAYMENTS'.</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.84</t>
+        </is>
+      </c>
+      <c r="B369" s="28" t="inlineStr">
+        <is>
+          <t>frontend App.js AccessDenied + admin ComplianceSection</t>
+        </is>
+      </c>
+      <c r="C369" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D369" s="28" t="inlineStr">
+        <is>
+          <t>Visual consistency</t>
+        </is>
+      </c>
+      <c r="E369" s="28" t="inlineStr">
+        <is>
+          <t>Access Denied in the current style; an admin download failure in words</t>
+        </is>
+      </c>
+      <c r="F369" s="28" t="inlineStr">
+        <is>
+          <t>Access Denied was the last screen in the retired brutalist style (black borders, uppercase, a red square). The admin compliance export printed 'Download failed: ' + the browser's exception text.</t>
+        </is>
+      </c>
+      <c r="G369" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H369" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I369" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Access Denied and the new not-found page share one quiet layout ('This page isn't open to you'). The export failure says the file could not be saved and that the export itself was fetched.</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-product pass)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 269 of 367 items Done  (73%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 76 of 84 Done.</t>
+          <t>Epic 6 progress: 273 of 371 items Done  (74%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
         </is>
       </c>
     </row>
@@ -2436,17 +2436,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>88</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L369"/>
+  <dimension ref="A1:L373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26859,6 +26859,234 @@
       <c r="L369" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-03 (full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.85</t>
+        </is>
+      </c>
+      <c r="B370" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/PasswordReset.js + backend /auth/password/reset/check</t>
+        </is>
+      </c>
+      <c r="C370" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D370" s="28" t="inlineStr">
+        <is>
+          <t>Error states</t>
+        </is>
+      </c>
+      <c r="E370" s="28" t="inlineStr">
+        <is>
+          <t>A dead reset link says so before the form, not after</t>
+        </is>
+      </c>
+      <c r="F370" s="28" t="inlineStr">
+        <is>
+          <t>A spent or expired reset link showed 'Set a new password', let the founder choose one and type it twice, and only then said the link was dead.</t>
+        </is>
+      </c>
+      <c r="G370" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H370" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I370" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. New POST /auth/password/reset/check (auth_emails.is_live) previews consume() without spending the token; the page shows 'Checking your link…' then either the form or 'This link won't work'. If the check cannot be asked, the form shows and the reset decides. CSRF-exempt like reset; API baseline regenerated (+1 route). Verified: live token shows the form and stays unspent; dead token goes straight to the dead state.</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (minor ones from the full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.86</t>
+        </is>
+      </c>
+      <c r="B371" s="28" t="inlineStr">
+        <is>
+          <t>frontend admin Support/Config + pages/Tasks.js</t>
+        </is>
+      </c>
+      <c r="C371" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D371" s="28" t="inlineStr">
+        <is>
+          <t>Housekeeping</t>
+        </is>
+      </c>
+      <c r="E371" s="28" t="inlineStr">
+        <is>
+          <t>An &lt;option&gt; holds one string</t>
+        </is>
+      </c>
+      <c r="F371" s="28" t="inlineStr">
+        <is>
+          <t>Text plus expressions inside &lt;option&gt; rendered invalid markup in development -- the only console error across all 17 admin console tabs.</t>
+        </is>
+      </c>
+      <c r="G371" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H371" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I371" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Support status filter, Config's default-model option and the Tasks assignee picker each render one template string. Verified: zero console errors across all 17 admin tabs.</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (minor ones from the full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.87</t>
+        </is>
+      </c>
+      <c r="B372" s="28" t="inlineStr">
+        <is>
+          <t>frontend pages/admin/* (12 files) + adminStyle.js</t>
+        </is>
+      </c>
+      <c r="C372" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D372" s="28" t="inlineStr">
+        <is>
+          <t>Visual consistency</t>
+        </is>
+      </c>
+      <c r="E372" s="28" t="inlineStr">
+        <is>
+          <t>The admin console is drawn in the app's own style</t>
+        </is>
+      </c>
+      <c r="F372" s="28" t="inlineStr">
+        <is>
+          <t>The platform console was the last surface in the retired brutalist dark style: black ground, mono uppercase buttons, square borders, and six style constants copied into every section.</t>
+        </is>
+      </c>
+      <c r="G372" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H372" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I372" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. One shared adminStyle.js (glass cards, pills, quiet labels from components/karma/glass); every section imports it. Shell and login rewritten by hand; the red stays as the console's mark so it is never mistaken for a tenant screen. Measured in the browser: every text element on all 17 tabs passes 4.5:1 contrast (status colours darkened for a light ground), no horizontal overflow at 390px, zero console errors. All data-testids kept.</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (minor ones from the full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="28" t="inlineStr">
+        <is>
+          <t>U7-25.88</t>
+        </is>
+      </c>
+      <c r="B373" s="28" t="inlineStr">
+        <is>
+          <t>backend routers/admin.py GET /admin/tenants (+ admin_support counts)</t>
+        </is>
+      </c>
+      <c r="C373" s="28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D373" s="28" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E373" s="28" t="inlineStr">
+        <is>
+          <t>The workspace list loads in under a second instead of 24</t>
+        </is>
+      </c>
+      <c r="F373" s="28" t="inlineStr">
+        <is>
+          <t>Found while checking the restyle: Workspaces sat on Loading… -- the endpoint asked four questions PER workspace in sequence (52 round trips for 13 workspaces), 24 s against the hosted database and growing with every customer.</t>
+        </is>
+      </c>
+      <c r="G373" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H373" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I373" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Four grouped aggregations for all workspaces, run concurrently: 24 s -&gt; 0.8 s warm, response byte-identical to the old one (compared in the browser). Support ticket status counts also asked together instead of in series.</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (minor ones from the full-product pass)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 273 of 371 items Done  (74%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 31 of 32 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
+          <t>Epic 6 progress: 285 of 386 items Done  (74%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 43 of 47 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
         </is>
       </c>
     </row>
@@ -2368,15 +2368,19 @@
           <t>Settings, Team and access (RBAC)</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>31</v>
-      </c>
-      <c r="D28" t="n">
-        <v>32</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6043,7 +6047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L373"/>
+  <dimension ref="A1:L388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27087,6 +27091,861 @@
       <c r="L373" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-03 (minor ones from the full-product pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.32</t>
+        </is>
+      </c>
+      <c r="B374" s="28" t="inlineStr">
+        <is>
+          <t>routers/voice_notes.py</t>
+        </is>
+      </c>
+      <c r="C374" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D374" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E374" s="28" t="inlineStr">
+        <is>
+          <t>A voice note's transcript follows the same rule as its recording</t>
+        </is>
+      </c>
+      <c r="F374" s="28" t="inlineStr">
+        <is>
+          <t>The recording was limited to the owner, the person who recorded it and the decision's people; the transcript of the same words, and every other note's, was returned to any member by GET /voice-notes and /voice-notes/{id}. An owner's 12 dictated notes were readable by a member with no access at all.</t>
+        </is>
+      </c>
+      <c r="G374" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H374" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I374" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. List and detail use the audio rule (_may_read_note). Measured: members 12 -&gt; 0, owner unchanged. The app only reads a member's own note (capture progress), so nothing visible changed.</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-application RBAC audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.33</t>
+        </is>
+      </c>
+      <c r="B375" s="28" t="inlineStr">
+        <is>
+          <t>routers: dashboard, inbox, meetings, tenant_settings, team, complaints, brain_context_api, brain_docs, brain_router, finance, workflows</t>
+        </is>
+      </c>
+      <c r="C375" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D375" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E375" s="28" t="inlineStr">
+        <is>
+          <t>Reads with no gate are closed</t>
+        </is>
+      </c>
+      <c r="F375" s="28" t="inlineStr">
+        <is>
+          <t>Endpoints that checked only sign-in: /dashboard (every pending decision, purchase, overdue task), /inbox (decision prices, complaints) and its status write, /meetings (retired; transcripts), /invites (phone numbers), /attendance, /memory, /brain/context, /brain/documents, /brain/agent (+run, create-task), /ingest (uploaded bills), and every workflow read. Several are used by no screen at all.</t>
+        </is>
+      </c>
+      <c r="G375" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H375" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I375" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Owner-only where unused and owner-level (dashboard, inbox, meetings); team_manage for invites/attendance; brain for memory/context/documents; ask for the agent (as /ask); workflows for workflow reads (as the writes); finance or data_input for ingest (new require_any_perm).</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-application RBAC audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.34</t>
+        </is>
+      </c>
+      <c r="B376" s="28" t="inlineStr">
+        <is>
+          <t>routers/complaints.py, crm.py, calendar.py</t>
+        </is>
+      </c>
+      <c r="C376" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D376" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E376" s="28" t="inlineStr">
+        <is>
+          <t>Complaints, money owed and the calendar show what each screen shows</t>
+        </is>
+      </c>
+      <c r="F376" s="28" t="inlineStr">
+        <is>
+          <t>GET /complaints listed every complaint to everyone though raising one follows the contact; /crm/outstanding gave unpaid amounts per customer and supplier to anyone; /calendar listed every task in the company (the Tasks page shows a member their own), every complaint, every contact birthday and every delivery.</t>
+        </is>
+      </c>
+      <c r="G376" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H376" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I376" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. complaint_scope (contacts you may open + your own); outstanding filtered by crm_types; calendar tasks via task_list_query, complaints via complaint_scope, birthdays by crm_types, deliveries need workflows. Measured calendar: Priya 10 -&gt; 5 days, Anand 10 -&gt; 3, owner unchanged.</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-application RBAC audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.35</t>
+        </is>
+      </c>
+      <c r="B377" s="28" t="inlineStr">
+        <is>
+          <t>routers/decisions.py, captures.py</t>
+        </is>
+      </c>
+      <c r="C377" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D377" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E377" s="28" t="inlineStr">
+        <is>
+          <t>A decision's moves follow the decision; a draft's queue is one rule</t>
+        </is>
+      </c>
+      <c r="F377" s="28" t="inlineStr">
+        <is>
+          <t>GET /decisions/{id}/moves (the cards it moves and their open tasks) had no access check while the decision itself was refused. Captures: the queue showed a draft to its reviewer role OR reviewer permission, acting on it checked the role alone -- 'Not your review queue' on a draft in your queue.</t>
+        </is>
+      </c>
+      <c r="G377" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H377" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I377" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. moves checks _decision_participants; _get_draft accepts the reviewer permission as the list does.</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-application RBAC audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.36</t>
+        </is>
+      </c>
+      <c r="B378" s="28" t="inlineStr">
+        <is>
+          <t>lib/perms.js, AuthContext.js, 6 server sites, 17 UI sites</t>
+        </is>
+      </c>
+      <c r="C378" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D378" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E378" s="28" t="inlineStr">
+        <is>
+          <t>What owners were switched off from stays off, everywhere</t>
+        </is>
+      </c>
+      <c r="F378" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; What owners can open removed keys server-side in require_perm, but 6 server shortcuts and 17 UI checks of the form 'owner OR permission' walked around it, and the UI's hasPerm answered true for any owner. Sign-in responses carried no resolved permissions, so until a reload the UI used built-in role defaults (ignoring the company's role settings).</t>
+        </is>
+      </c>
+      <c r="G378" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H378" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I378" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. userPerms/hasPerm read effective_permissions for owners too; persist() refreshes /auth/me after any sign-in; shortcuts read permissions only. Verified: Finance switched off for owners -&gt; money tiles gone, Finance shows only the upload Inbox, zero refused requests on 7 pages; switched back.</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-application RBAC audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.37</t>
+        </is>
+      </c>
+      <c r="B379" s="28" t="inlineStr">
+        <is>
+          <t>Captures.js, AskAI.js, DecisionDialog.js, Desk.js, Brain.js, MyWork.js, WorkflowLink.js</t>
+        </is>
+      </c>
+      <c r="C379" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D379" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E379" s="28" t="inlineStr">
+        <is>
+          <t>Screens offer only what the server will do</t>
+        </is>
+      </c>
+      <c r="F379" s="28" t="inlineStr">
+        <is>
+          <t>AI-draft Approve/Reassign/Clarify/Reject never checked captures_approve; Brain export never checked brain_export; a named approver without decisions_approve saw Approve; the Desk read workflows for people without Workflows; task cards linked to a Workflows page the member could not open; asking the Brain without Ask access said 'AI service error'.</t>
+        </is>
+      </c>
+      <c r="G379" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H379" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I379" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Each gated on the same permission the server checks; WorkflowLink renders the name as text without access; Brain says plainly that Ask needs access. Browser sweep as owner, default member, finance member and a no-access member: zero refused requests and zero console errors on page loads.</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-application RBAC audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.38</t>
+        </is>
+      </c>
+      <c r="B380" s="28" t="inlineStr">
+        <is>
+          <t>tests/test_rbac_reads_are_gated.py</t>
+        </is>
+      </c>
+      <c r="C380" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D380" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E380" s="28" t="inlineStr">
+        <is>
+          <t>Every read says who may make it</t>
+        </is>
+      </c>
+      <c r="F380" s="28" t="inlineStr">
+        <is>
+          <t>Writes have had to declare a gate since test_s3_role_matrix; reads never did, which is how the leaks above arrived unnoticed.</t>
+        </is>
+      </c>
+      <c r="G380" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H380" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I380" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Inventory test: a read open to every signed-in member must be on a reviewed list with its reason. Proven to fail when an entry is removed. 39 tests in the file.</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-application RBAC audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.39</t>
+        </is>
+      </c>
+      <c r="B381" s="28" t="inlineStr">
+        <is>
+          <t>core/permissions.py ROLE_DEFAULT_PERMS</t>
+        </is>
+      </c>
+      <c r="C381" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D381" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E381" s="28" t="inlineStr">
+        <is>
+          <t>Built-in Sales/Finance defaults never reach a real company's roles</t>
+        </is>
+      </c>
+      <c r="F381" s="28" t="inlineStr">
+        <is>
+          <t>The defaults that give Sales its customers and Finance its ledger apply only to a role literally keyed 'sales' or 'finance'. Onboarding names roles from the business ('Sales &amp; Order Management', 'Accounts &amp; Buyer Payments'), so a sales person starts with no CRM until the owner ticks it in Settings.</t>
+        </is>
+      </c>
+      <c r="G381" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H381" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I381" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Not changed: needs a product decision -- map onboarding roles to a default by function, or ask during onboarding which roles sell and which handle money.</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-application RBAC audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.40</t>
+        </is>
+      </c>
+      <c r="B382" s="28" t="inlineStr">
+        <is>
+          <t>routers/files.py</t>
+        </is>
+      </c>
+      <c r="C382" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D382" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E382" s="28" t="inlineStr">
+        <is>
+          <t>File downloads rely on unguessable ids, not on access to the record</t>
+        </is>
+      </c>
+      <c r="F382" s="28" t="inlineStr">
+        <is>
+          <t>GET /files/{id}/download serves any file in the company to any member who has the id. Ids are random and only reach people through records they may see, so the practical risk is low.</t>
+        </is>
+      </c>
+      <c r="G382" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H382" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I382" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Not changed: a record-aware check needs each file to know its owning record and kind -- a contained follow-up.</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (full-application RBAC audit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.41</t>
+        </is>
+      </c>
+      <c r="B383" s="28" t="inlineStr">
+        <is>
+          <t>pages/Team.js MemberDialog, components/Layout.js NAV</t>
+        </is>
+      </c>
+      <c r="C383" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D383" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E383" s="28" t="inlineStr">
+        <is>
+          <t>"They will see these menus" shows the real menus</t>
+        </is>
+      </c>
+      <c r="F383" s="28" t="inlineStr">
+        <is>
+          <t>The add-member preview was a hand-kept list: CEO Brief and Meeting Notes (retired), CRM called People, no Finance. An Accounts member with Finance on was previewed without Finance; one with Suppliers access was shown People crossed out though they would get CRM.</t>
+        </is>
+      </c>
+      <c r="G383" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H383" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I383" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Built from Layout's exported NAV with the same visibility rule (navEntryOpen), plus Workflows and Approvals from More; 'Finance (upload only)' when only Data Input. Verified live: toggling Finance/CRM/Approvals updates the preview.</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (role system product review, browser end to end)</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.42</t>
+        </is>
+      </c>
+      <c r="B384" s="28" t="inlineStr">
+        <is>
+          <t>CompanyDetails.js, Team.js</t>
+        </is>
+      </c>
+      <c r="C384" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D384" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E384" s="28" t="inlineStr">
+        <is>
+          <t>Owner access is described truthfully</t>
+        </is>
+      </c>
+      <c r="F384" s="28" t="inlineStr">
+        <is>
+          <t>'owners always have everything' (Teams editor) and 'Owners can open and manage everything... individual permissions don't apply' (member dialog) stopped being true when 'What owners can open' shipped; the member profile listed every area for an owner regardless.</t>
+        </is>
+      </c>
+      <c r="G384" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H384" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I384" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Copy names the Workspace switch; the profile reads the server-resolved list.</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (role system product review, browser end to end)</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.43</t>
+        </is>
+      </c>
+      <c r="B385" s="28" t="inlineStr">
+        <is>
+          <t>lib/perms.js PERMISSION_GROUPS; CompanyDetails.js; Team.js</t>
+        </is>
+      </c>
+      <c r="C385" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D385" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E385" s="28" t="inlineStr">
+        <is>
+          <t>Access is grouped by area, not a flat list of nineteen</t>
+        </is>
+      </c>
+      <c r="F385" s="28" t="inlineStr">
+        <is>
+          <t>Both access editors listed all nineteen permissions in one grid; finding the money or the approvals meant reading every one. Teams also showed their internal key (sales_&amp;_order_management) beside the name.</t>
+        </is>
+      </c>
+      <c r="G385" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H385" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I385" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Six groups: Everyday work, Customers &amp; suppliers, Money, Company Brain, Approvals, Running the team; every key in exactly one (tested). Internal keys removed from the Teams list.</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (role system product review, browser end to end)</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.44</t>
+        </is>
+      </c>
+      <c r="B386" s="28" t="inlineStr">
+        <is>
+          <t>pages/desk/useDeskMetrics.js</t>
+        </is>
+      </c>
+      <c r="C386" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D386" s="28" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="E386" s="28" t="inlineStr">
+        <is>
+          <t>"Spend, this month" is this month, and ₹0 is ₹0</t>
+        </is>
+      </c>
+      <c r="F386" s="28" t="inlineStr">
+        <is>
+          <t>The tile showed the last month that had any spend (August, in October, if nothing was booked since), and with no rows at all it showed '…' -- loading, forever.</t>
+        </is>
+      </c>
+      <c r="G386" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H386" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I386" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Reads the current local calendar month from by_month; a loaded ledger with nothing this month shows ₹0.</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (role system product review, browser end to end)</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.45</t>
+        </is>
+      </c>
+      <c r="B387" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Teams &gt; Access; Team &gt; Add member</t>
+        </is>
+      </c>
+      <c r="C387" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D387" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E387" s="28" t="inlineStr">
+        <is>
+          <t>The access chain verified end to end</t>
+        </is>
+      </c>
+      <c r="F387" s="28" t="inlineStr">
+        <is>
+          <t>Owner sets a team's access -&gt; adds a member with 'Use the team's access' -&gt; the member gets it -&gt; a later team change reaches them, and not a member with their own access.</t>
+        </is>
+      </c>
+      <c r="G387" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H387" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I387" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Walked in the browser as the owner on the scratch DB (Accounts team given Finance, Suppliers, Approve AI drafts; new member resolved to exactly that; removing one permission from the team removed it from her, Anand's own access untouched). Test data removed after.</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (role system product review, browser end to end)</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.46</t>
+        </is>
+      </c>
+      <c r="B388" s="28" t="inlineStr">
+        <is>
+          <t>workflows / operating_model pipelines</t>
+        </is>
+      </c>
+      <c r="C388" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D388" s="28" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="E388" s="28" t="inlineStr">
+        <is>
+          <t>Workflows access is all-or-nothing across pipelines</t>
+        </is>
+      </c>
+      <c r="F388" s="28" t="inlineStr">
+        <is>
+          <t>A Sales member with no Finance sees and can advance Buyer Payments cards (Desk 'Next up: Bluewave - 30% Advance Invoice Raised -&gt; Advance to Advance Received'). Every stage already records its owning team (owner_role), so scoping is possible.</t>
+        </is>
+      </c>
+      <c r="G388" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H388" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I388" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Design decision: show/advance a pipeline's cards only to teams that own one of its stages (owners and 'See all tasks' see all), or keep one Workflows switch.</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (role system product review, browser end to end)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 285 of 386 items Done  (74%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 43 of 47 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
+          <t>Epic 6 progress: 287 of 386 items Done  (74%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 45 of 47 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -27536,12 +27536,12 @@
       </c>
       <c r="I381" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Not changed: needs a product decision -- map onboarding roles to a default by function, or ask during onboarding which roles sell and which handle money.</t>
+          <t>SHIPPED 2026-10-03 (founder: build both). shared/roles.starting_perms now also runs when an owner adds a team in Settings (it ran only at sign-up): money teams start with Finance, Suppliers and Approve AI drafts; selling teams with Customers &amp; dealers; HR/payroll with Approve leave; the rest on everyday work. Purchasing keeps Finance as the existing founder rule had it. Existing teams are untouched. The add-team toast says what it started with. Verified: 'HR &amp; Payroll' added -&gt; leave_approve; toast shown.</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -27935,12 +27935,12 @@
       </c>
       <c r="I388" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Design decision: show/advance a pipeline's cards only to teams that own one of its stages (owners and 'See all tasks' see all), or keep one Workflows switch.</t>
+          <t>SHIPPED 2026-10-03 (founder: build both). services/workflows.workflow_scope: a member sees and moves a pipeline's cards when their team owns a stage (stage.role / stage task role, resolved by shared/roles); owner and 'See all tasks' see all; pre-model types follow the switch. Enforced on list, counts, detail, create, edit, leftover, advance, approve-stage, calendar deliveries, Ask, the agent tool and Brain search; /auth/me carries workflow_scope for the board tabs and WorkflowLink. Brain search also narrowed: decisions by the Decisions list rule (visible_decisions_clause), contacts by CRM side. Verified: Sales no longer sees Buyer Payments (403 on read/advance), Desk Next up became its own order card; Accounts and owner see both.</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 287 of 386 items Done  (74%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 45 of 47 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
+          <t>Epic 6 progress: 288 of 386 items Done  (75%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 46 of 47 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -27593,12 +27593,12 @@
       </c>
       <c r="I382" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Not changed: a record-aware check needs each file to know its owning record and kind -- a contained follow-up.</t>
+          <t>SHIPPED 2026-10-03 (founder). routers/files.may_read_file: avatars to the company; your own uploads; a task's attachment to whoever may open the task (may_read_task, extracted from get_task); a capture's or decision's reference to whoever may open that note or decision; the owner everything. The legacy /files/{name} route asks the same, plus Finance/Data Input for uploaded bills, Finance for ledger attachments and the review queue for AI-draft previews. Verified: a photo on Priya's task opened for her and the owner, 403 for Anand, on both routes.</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 288 of 386 items Done  (75%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 46 of 47 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
+          <t>Epic 6 progress: 292 of 395 items Done  (74%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 50 of 56 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
         </is>
       </c>
     </row>
@@ -2370,17 +2370,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L388"/>
+  <dimension ref="A1:L397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27946,6 +27946,519 @@
       <c r="L388" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-03 (role system product review, browser end to end)</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.47</t>
+        </is>
+      </c>
+      <c r="B389" s="28" t="inlineStr">
+        <is>
+          <t>routers/tenant_settings.py read_audit_log; Settings.js</t>
+        </is>
+      </c>
+      <c r="C389" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D389" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E389" s="28" t="inlineStr">
+        <is>
+          <t>The audit log names people</t>
+        </is>
+      </c>
+      <c r="F389" s="28" t="inlineStr">
+        <is>
+          <t>Every member who signs in by mobile has no email, so the owner's audit log read 'Logout — A member' for all of them.</t>
+        </is>
+      </c>
+      <c r="G389" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H389" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I389" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. The endpoint resolves actor ids to names; the table shows name, else email. Verified: Priya Nair, Anand Rao, Kavya Raman.</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.48</t>
+        </is>
+      </c>
+      <c r="B390" s="28" t="inlineStr">
+        <is>
+          <t>Settings.js AiKeysCard; Leave.js</t>
+        </is>
+      </c>
+      <c r="C390" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D390" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E390" s="28" t="inlineStr">
+        <is>
+          <t>Keys and approvers described in words</t>
+        </is>
+      </c>
+      <c r="F390" s="28" t="inlineStr">
+        <is>
+          <t>'AI keys' listed Wa_access_token and Wa_phone_number_id as if they were AI providers; Leave approvers pointed at 'People → Employees', retired.</t>
+        </is>
+      </c>
+      <c r="G390" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H390" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I390" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. WhatsApp rows named; card titled 'AI and WhatsApp keys'; leave copy points at the Team card.</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.49</t>
+        </is>
+      </c>
+      <c r="B391" s="28" t="inlineStr">
+        <is>
+          <t>Settings.js DelegationCard</t>
+        </is>
+      </c>
+      <c r="C391" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D391" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E391" s="28" t="inlineStr">
+        <is>
+          <t>The hand-over is offered only to people with approvals</t>
+        </is>
+      </c>
+      <c r="F391" s="28" t="inlineStr">
+        <is>
+          <t>'While you're away — hand your approvals' showed to a member who approves nothing.</t>
+        </is>
+      </c>
+      <c r="G391" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="H391" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I391" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Shows for the owner, approval-permission holders, anyone with direct reports, or a hand-over already running. Verified: Priya no card, Anand card.</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.50</t>
+        </is>
+      </c>
+      <c r="B392" s="28" t="inlineStr">
+        <is>
+          <t>Ledger.js; mobile/InstallPrompt.jsx</t>
+        </is>
+      </c>
+      <c r="C392" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D392" s="28" t="inlineStr">
+        <is>
+          <t>Desktop</t>
+        </is>
+      </c>
+      <c r="E392" s="28" t="inlineStr">
+        <is>
+          <t>Desktop shows only what a desktop can use</t>
+        </is>
+      </c>
+      <c r="F392" s="28" t="inlineStr">
+        <is>
+          <t>Finance on desktop offered 'Photo', which opened the same file picker as 'Upload bill / receipt'; desktop Chrome was offered the phone app's install bar.</t>
+        </is>
+      </c>
+      <c r="G392" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H392" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I392" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-03. Photo kept on the phone only; install bar phone-only. Swept 14 desktop pages for phone-only wording or camera buttons: none left.</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.51</t>
+        </is>
+      </c>
+      <c r="B393" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Workspace &gt; Plan and seats; routers/billing.py</t>
+        </is>
+      </c>
+      <c r="C393" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D393" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E393" s="28" t="inlineStr">
+        <is>
+          <t>An owner can pay: Upgrade / Choose plan</t>
+        </is>
+      </c>
+      <c r="F393" s="28" t="inlineStr">
+        <is>
+          <t>The plan card shows 'Trial · ends 5 Oct · 3 of 15 seats' with no way to upgrade. POST /api/billing/checkout (Razorpay) exists; no screen calls it.</t>
+        </is>
+      </c>
+      <c r="G393" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H393" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I393" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Needs Razorpay keys configured (billing_configured is false) and plan-picker UI.</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.52</t>
+        </is>
+      </c>
+      <c r="B394" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Account &gt; Password &amp; Security</t>
+        </is>
+      </c>
+      <c r="C394" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D394" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E394" s="28" t="inlineStr">
+        <is>
+          <t>Active sessions and sign out everywhere</t>
+        </is>
+      </c>
+      <c r="F394" s="28" t="inlineStr">
+        <is>
+          <t>GET/DELETE /api/auth/me/sessions exist; Settings offers only 'Sign out' of this device. A lost phone cannot be signed out from a laptop.</t>
+        </is>
+      </c>
+      <c r="G394" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H394" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I394" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Small: list sessions with device + last seen, sign out one / all others.</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.53</t>
+        </is>
+      </c>
+      <c r="B395" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Account</t>
+        </is>
+      </c>
+      <c r="C395" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D395" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E395" s="28" t="inlineStr">
+        <is>
+          <t>Notification preferences</t>
+        </is>
+      </c>
+      <c r="F395" s="28" t="inlineStr">
+        <is>
+          <t>No control over what reaches someone by email/WhatsApp/push; owners can only switch overdue-owner emails in Deadlines.</t>
+        </is>
+      </c>
+      <c r="G395" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H395" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I395" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Decide channels per event type (approvals, overdue, leave, mentions).</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.54</t>
+        </is>
+      </c>
+      <c r="B396" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Workspace</t>
+        </is>
+      </c>
+      <c r="C396" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D396" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E396" s="28" t="inlineStr">
+        <is>
+          <t>Owner self-serve export of company data</t>
+        </is>
+      </c>
+      <c r="F396" s="28" t="inlineStr">
+        <is>
+          <t>DPDP export exists only in the platform admin console; an owner cannot download their own company's data.</t>
+        </is>
+      </c>
+      <c r="G396" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H396" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I396" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Reuse the admin DSAR export, scoped to the owner's tenant.</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.55</t>
+        </is>
+      </c>
+      <c r="B397" s="28" t="inlineStr">
+        <is>
+          <t>Settings &gt; Business &gt; Company Details</t>
+        </is>
+      </c>
+      <c r="C397" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D397" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E397" s="28" t="inlineStr">
+        <is>
+          <t>Teams &amp; access deserve their own tab</t>
+        </is>
+      </c>
+      <c r="F397" s="28" t="inlineStr">
+        <is>
+          <t>Teams and their Access editor sit at the bottom of the Company Details card on the Business tab; owners look for them under Team or a 'Team &amp; access' tab.</t>
+        </is>
+      </c>
+      <c r="G397" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H397" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I397" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Design: move Teams + Access (and Leave approvers) to a 'Team &amp; access' tab, or link from the Team page.</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 292 of 395 items Done  (74%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 50 of 56 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
+          <t>Epic 6 progress: 299 of 401 items Done  (75%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 57 of 62 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
         </is>
       </c>
     </row>
@@ -2370,17 +2370,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L397"/>
+  <dimension ref="A1:L403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28448,17 +28448,359 @@
       </c>
       <c r="I397" s="28" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>Design: move Teams + Access (and Leave approvers) to a 'Team &amp; access' tab, or link from the Team page.</t>
+          <t>SHIPPED 2026-10-05 (founder). Settings › Team &amp; access: Teams with their Access editor (components/settings/TeamsCard), Who approves leave (from Operations) and What owners can open (from Workspace). Head-count per team; delete disabled with a reason while a team has people; link to the Team page to add or move people. Task templates moved to Operations as their own card. Verified in the browser as owner: 6 tabs, all cards load, no failed requests.</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-03 (Settings product review + desktop pass, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.56</t>
+        </is>
+      </c>
+      <c r="B398" s="28" t="inlineStr">
+        <is>
+          <t>CompanyDetails, BusinessVocabulary, OperatingModelEditor, Leave approvers, RegenerateWithAi</t>
+        </is>
+      </c>
+      <c r="C398" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D398" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E398" s="28" t="inlineStr">
+        <is>
+          <t>Every Settings card in one style</t>
+        </is>
+      </c>
+      <c r="F398" s="28" t="inlineStr">
+        <is>
+          <t>Four cards were still on the old style — solid white tiles with square grey-bordered boxes and square UPPERCASE buttons — beside rounded glass cards on the same page (191 old borders on the Operating Model alone).</t>
+        </is>
+      </c>
+      <c r="G398" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H398" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I398" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-05. Glass card frame, glass fields, ink Save pills and glass secondary pills throughout; Company Details now only the company (fields, WhatsApp code, products) with one save. A computed-style sweep of all six tabs finds no old-style element left (the red Delete account is deliberate).</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (Settings UI/UX review, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.57</t>
+        </is>
+      </c>
+      <c r="B399" s="28" t="inlineStr">
+        <is>
+          <t>pages/Settings.js tab row</t>
+        </is>
+      </c>
+      <c r="C399" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D399" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E399" s="28" t="inlineStr">
+        <is>
+          <t>Settings tabs read whole on a phone</t>
+        </is>
+      </c>
+      <c r="F399" s="28" t="inlineStr">
+        <is>
+          <t>With six tabs each got 56px on a phone and the labels were cut ('Team &amp; a…', 'Operati…'). The row also said role=tablist while its buttons said aria-pressed.</t>
+        </is>
+      </c>
+      <c r="G399" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H399" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I399" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-05. Below lg the row scrolls with whole labels and brings the open tab into view; from lg up the tabs share the row. Buttons are role=tab with aria-selected.</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (Settings UI/UX review, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.58</t>
+        </is>
+      </c>
+      <c r="B400" s="28" t="inlineStr">
+        <is>
+          <t>pages/Settings.js YourAccessCard</t>
+        </is>
+      </c>
+      <c r="C400" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D400" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E400" s="28" t="inlineStr">
+        <is>
+          <t>A member can see what they can open</t>
+        </is>
+      </c>
+      <c r="F400" s="28" t="inlineStr">
+        <is>
+          <t>Nothing told a member what their access was; something missing might be access or a fault, and only the owner could say which.</t>
+        </is>
+      </c>
+      <c r="G400" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H400" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I400" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-05. Read-only 'Your access' card on a member's Settings (and a manager's Account tab), grouped like the editors, from the server-resolved list. Verified as Priya.</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (Settings UI/UX review, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.59</t>
+        </is>
+      </c>
+      <c r="B401" s="28" t="inlineStr">
+        <is>
+          <t>backend/scripts/run_scratch_backend.py; .claude/launch.json</t>
+        </is>
+      </c>
+      <c r="C401" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D401" s="28" t="inlineStr">
+        <is>
+          <t>Housekeeping</t>
+        </is>
+      </c>
+      <c r="E401" s="28" t="inlineStr">
+        <is>
+          <t>The scratch backend really has messaging off</t>
+        </is>
+      </c>
+      <c r="F401" s="28" t="inlineStr">
+        <is>
+          <t>The Windows launch entry blanked keys with cmd.exe `set NAME=`, which DELETES the variable; load_dotenv then refilled it from backend/.env with the live keys. DB stayed on the scratch database, but during this session's checks one login SMS went to the seeded number +91 98450 21921 and one owner-alert email to rajesh70595@kaveri-70595.in.</t>
+        </is>
+      </c>
+      <c r="G401" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H401" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I401" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-05. A Python start script sets every outbound key to EMPTY before the app loads (load_dotenv never overrides an existing variable) and refuses a non-scratch DB_NAME; both launch.json files use it. Verified: OTP request returns dev_mode true, sent false.</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (Settings UI/UX review, browser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.60</t>
+        </is>
+      </c>
+      <c r="B402" s="28" t="inlineStr">
+        <is>
+          <t>pages/Settings.js SettingsShell / Section</t>
+        </is>
+      </c>
+      <c r="C402" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D402" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E402" s="28" t="inlineStr">
+        <is>
+          <t>Settings uses a desktop screen: two panes</t>
+        </is>
+      </c>
+      <c r="F402" s="28" t="inlineStr">
+        <is>
+          <t>On desktop Settings was one 600px column pinned to the left of a 1300px screen, the rest empty (founder screenshot: 'lot of space, no design').</t>
+        </is>
+      </c>
+      <c r="G402" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H402" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I402" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-05. From lg up: a sticky side panel (who you are: name, team, company; then the sections — the owner's six tabs with a one-line description, the open tab listing its cards as jump links; a member's cards as jump links) beside a content column up to 52rem, centred. Links are read live from the cards on screen (MutationObserver; a card that renders nothing is never offered) and mark the card in view. Phone unchanged (tab row / single stack). Measured: 1366 side 252px + content 742px; 1024 side 230 + content 699; 1920 content ~1000; no horizontal scroll at 390/1024/1920.</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (screenshot of member Settings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.61</t>
+        </is>
+      </c>
+      <c r="B403" s="28" t="inlineStr">
+        <is>
+          <t>components/settings/AccessSwitch.js; TeamsCard.js; pages/Settings.js; pages/Team.js</t>
+        </is>
+      </c>
+      <c r="C403" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D403" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E403" s="28" t="inlineStr">
+        <is>
+          <t>Access is a switch, not a black tile</t>
+        </is>
+      </c>
+      <c r="F403" s="28" t="inlineStr">
+        <is>
+          <t>Every access area (team Access editor, What owners can open, the add/edit member dialog) was a tile that turned solid black when on; nearly every area IS on, so the cards were walls of black (founder screenshot: 'I don't like the black dark highlighting').</t>
+        </is>
+      </c>
+      <c r="G403" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H403" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I403" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-05. One shared AccessSwitch: a light row with the label and a switch in the app's primary colour (role=switch, aria-checked); an area that is off reads off (muted label, grey switch). Owners' Manage Team shows '· always on' and cannot be switched off. The member dialog's switches stay disabled while 'Use the team's access' is ticked. Menu preview chips and the open Access button moved from black to a light primary tint. Browser-checked: 19 switches per editor, toggles flip aria-checked and colour, no black tiles left.</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (screenshot of What owners can open)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -1586,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 299 of 401 items Done  (75%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 57 of 62 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
+          <t>Epic 6 progress: 301 of 403 items Done  (75%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 59 of 64 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L403"/>
+  <dimension ref="A1:L405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28801,6 +28801,120 @@
       <c r="L403" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-05 (screenshot of What owners can open)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.62</t>
+        </is>
+      </c>
+      <c r="B404" s="28" t="inlineStr">
+        <is>
+          <t>components/OperatingModelEditor.js</t>
+        </is>
+      </c>
+      <c r="C404" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D404" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E404" s="28" t="inlineStr">
+        <is>
+          <t>Operating Model: one pipeline open at a time; whole category names</t>
+        </is>
+      </c>
+      <c r="F404" s="28" t="inlineStr">
+        <is>
+          <t>On a phone the Operating Model card was 8,443px (~14 screens) because every pipeline showed every stage with every field, so Operations was 12,076px and Task templates / Deadlines sat below all of it. Task category fields were a fixed 112px, cutting 'Order Management' to 'Order Managen'.</t>
+        </is>
+      </c>
+      <c r="G404" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H404" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I404" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-05. Each pipeline is a one-line summary (name; N stages · N tasks · stage path) that opens on tap, one at a time; a lone pipeline starts open, a new one opens for its name. Category fields size to their name. Pipeline/category delete are tap targets. Measured at 390px: card 8,443 -&gt; 722px closed, Operations 12,076 -&gt; 2,424px; all 7 category names whole; no horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (check the settings page in mobile view)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="28" t="inlineStr">
+        <is>
+          <t>U7-23.63</t>
+        </is>
+      </c>
+      <c r="B405" s="28" t="inlineStr">
+        <is>
+          <t>pages/Settings.js AuditLogCard; phone tab row</t>
+        </is>
+      </c>
+      <c r="C405" s="28" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D405" s="28" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E405" s="28" t="inlineStr">
+        <is>
+          <t>Audit log and tab row fit a phone</t>
+        </is>
+      </c>
+      <c r="F405" s="28" t="inlineStr">
+        <is>
+          <t>The audit table had a 32rem floor, so on a phone 'Who' sat behind a sideways scroll (512px table in a 403px box). With Workspace open, the active pill was scrolled flush to the tab row's rounded end and clipped.</t>
+        </is>
+      </c>
+      <c r="G405" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H405" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I405" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>SHIPPED 2026-10-05. Table floor removed (three short columns fit, text wraps); tab row has scroll padding so the open tab lands inside the row. Measured at 390px: audit box 403/403 (no scroll), open Workspace tab 3px inside the row end. Whole Settings checked at 390px on every owner tab: no horizontal scroll, last card clears the bottom bar.</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-05 (check the settings page in mobile view)</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -619,6 +619,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -643,6 +644,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -655,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -667,6 +670,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -679,6 +683,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -686,6 +691,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -729,6 +735,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -772,6 +779,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -815,6 +823,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
@@ -858,6 +867,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -901,6 +911,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
@@ -944,6 +955,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
@@ -987,6 +999,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
@@ -1030,6 +1043,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
@@ -1073,6 +1087,7 @@
         </is>
       </c>
     </row>
+    <row r="59"/>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
@@ -1116,6 +1131,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
@@ -1159,6 +1175,7 @@
         </is>
       </c>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
@@ -1202,6 +1219,7 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
@@ -1245,6 +1263,7 @@
         </is>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
@@ -1288,6 +1307,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
@@ -1331,6 +1351,7 @@
         </is>
       </c>
     </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
@@ -1374,6 +1395,7 @@
         </is>
       </c>
     </row>
+    <row r="94"/>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
@@ -1417,6 +1439,7 @@
         </is>
       </c>
     </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
@@ -1460,6 +1483,7 @@
         </is>
       </c>
     </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
@@ -1503,6 +1527,7 @@
         </is>
       </c>
     </row>
+    <row r="109"/>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
@@ -1543,6 +1568,50 @@
       <c r="B113" t="inlineStr">
         <is>
           <t>In progress -- 12 of 13 Done; open: Phase 5 capture feedback</t>
+        </is>
+      </c>
+    </row>
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Sprint 26 -- Requests (raise, approve, book the expense)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Files</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>services/staff_requests.py, routers/staff_requests.py, components/requests/*, pages/Requests.js, pages/MyWork.js</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Employees had no way to ask for material, money or equipment and get a yes that reached Finance; it happened by word of mouth and the expense was typed again by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>In progress -- 14 of 18 Done; open: Phase 3 (voice via Dex, bill-photo reading, reports, WhatsApp)</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1586,7 +1655,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 301 of 403 items Done  (75%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 59 of 64 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
+          <t>Epic 6 progress: 315 of 421 items Done  (75%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 59 of 64 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.  Sprint 26 (Requests) added 2026-10-21: 14 of 18 Done.</t>
         </is>
       </c>
     </row>
@@ -2461,6 +2530,39 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>Added 2026-09-21 after auditing the workflow + task sections from the Desk (docs/WORKFLOW_OPERATIONS_PLAN.md). The engine was real — stage gates, auto-advance, evidence, escalation — and the HUMAN half was missing: a person could not attach a task to a workflow, move a due date, repeat work or see more than one stage's slice. 19 items across continuity, control, visibility and continuous operations. A multi-user run (four people, two industries) found stage work going to nobody (departments never matched) — fixed — plus three findings for the founder. A 26-step walk by hand in the browser (3 people, real log-outs) fixed three more and logged the rest (docs/BROWSER_SCENARIOS_0921.md). The routines promised at sign-up are now confirmed once and repeat (U7-25.25). 2026-09-22: the workflow gets a clock — stage durations date the stage's work, stuck cards are reported, cards can carry a target date with a forecast, and the card shows planned vs actual per stage; the Desk's Delayed and Workflows tiles read it (U7-25.26–29).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sprint 26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Requests (raise, approve, book the expense)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>14</v>
+      </c>
+      <c r="D31" t="n">
+        <v>18</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Added 2026-10-21 from the client's Requests plan (docs/REQUESTS_PLAN.md): employees raise a request with one or many items, send it to their reporting manager (default) or the owner, approval books the expense in Finance, Finance marks it paid and purchases go into stock. Web first; Phase 3 (voice via Dex, bill-photo reading, reports, WhatsApp) is later. General requests are not financial: approval closes them, nothing goes to Finance.</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L405"/>
+  <dimension ref="A1:L423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28915,6 +29017,996 @@
       <c r="L405" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-05 (check the settings page in mobile view)</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.1</t>
+        </is>
+      </c>
+      <c r="B406" s="28" t="inlineStr">
+        <is>
+          <t>services/staff_requests.py, models/staff_requests.py</t>
+        </is>
+      </c>
+      <c r="C406" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D406" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E406" s="28" t="inlineStr">
+        <is>
+          <t>The rules: seven types, approver choice, who may read / decide / fulfil</t>
+        </is>
+      </c>
+      <c r="F406" s="28" t="inlineStr">
+        <is>
+          <t>Types (Purchase &amp; materials, Expense reimbursement, Advance, Travel, Equipment &amp; assets, Repairs &amp; services, General) with their expense-category hint; approver = the requester's choice, reporting manager by default or the owner, no amount rule; no manager falls to the owner and says so; an owner's own request is recorded approved. Access: requester, approver or delegate, owner, Finance once approved; everyone else 404.</t>
+        </is>
+      </c>
+      <c r="G406" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H406" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I406" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K406" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L406" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.2</t>
+        </is>
+      </c>
+      <c r="B407" s="28" t="inlineStr">
+        <is>
+          <t>routers/staff_requests.py</t>
+        </is>
+      </c>
+      <c r="C407" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D407" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E407" s="28" t="inlineStr">
+        <is>
+          <t>The HTTP surface, every state change an atomic claim</t>
+        </is>
+      </c>
+      <c r="F407" s="28" t="inlineStr">
+        <is>
+          <t>GET /api/requests?view=mine|approvals|fulfil|all, GET approver-options, GET one; POST create, approve, reject (reason required), request-info, respond, withdraw, fulfil. Each update names the status it moves from, so two Approves make one approval and one expense; REQ-0001 numbering is one atomic increment per company with a unique index behind it.</t>
+        </is>
+      </c>
+      <c r="G407" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H407" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I407" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K407" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L407" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.3</t>
+        </is>
+      </c>
+      <c r="B408" s="28" t="inlineStr">
+        <is>
+          <t>routers/staff_requests.py _book_expense, routers/ledger.py create_expense</t>
+        </is>
+      </c>
+      <c r="C408" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D408" s="28" t="inlineStr">
+        <is>
+          <t>Requests / Finance</t>
+        </is>
+      </c>
+      <c r="E408" s="28" t="inlineStr">
+        <is>
+          <t>Approval books the expense in Finance</t>
+        </is>
+      </c>
+      <c r="F408" s="28" t="inlineStr">
+        <is>
+          <t>create_expense(source='request', request_id); the category is found in the company's own words (Raw Materials, Machine Maintenance) before the keyword guess; equipment books Asset Purchase so the asset register gets it; a reimbursement names the employee as payee. A failed booking keeps the approval and says so on the request.</t>
+        </is>
+      </c>
+      <c r="G408" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H408" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I408" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K408" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L408" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.4</t>
+        </is>
+      </c>
+      <c r="B409" s="28" t="inlineStr">
+        <is>
+          <t>routers/staff_requests.py fulfil, routers/ledger.py update_expense / delete_expense</t>
+        </is>
+      </c>
+      <c r="C409" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D409" s="28" t="inlineStr">
+        <is>
+          <t>Requests / Finance</t>
+        </is>
+      </c>
+      <c r="E409" s="28" t="inlineStr">
+        <is>
+          <t>Finance closes it: paid, and purchases into stock</t>
+        </is>
+      </c>
+      <c r="F409" s="28" t="inlineStr">
+        <is>
+          <t>Mark paid marks the booked expense paid and can put purchase items with a quantity into inventory (unit cost = line amount / quantity). Paying the expense in Finance closes the request on its own; deleting it unlinks the request and says why.</t>
+        </is>
+      </c>
+      <c r="G409" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H409" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I409" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K409" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L409" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.5</t>
+        </is>
+      </c>
+      <c r="B410" s="28" t="inlineStr">
+        <is>
+          <t>services/notifications.py, routers/staff_requests.py</t>
+        </is>
+      </c>
+      <c r="C410" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D410" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E410" s="28" t="inlineStr">
+        <is>
+          <t>Told at every step</t>
+        </is>
+      </c>
+      <c r="F410" s="28" t="inlineStr">
+        <is>
+          <t>Approver (and delegates) on a new request and an answer; requester on approve / reject / question / done; Finance and owners when something is approved to pay; approver when a request is withdrawn. Push titles: Request declined, Request withdrawn.</t>
+        </is>
+      </c>
+      <c r="G410" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H410" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I410" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K410" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L410" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.6</t>
+        </is>
+      </c>
+      <c r="B411" s="28" t="inlineStr">
+        <is>
+          <t>bootstrap/routing.py, bootstrap/lifecycle.py, services/tenant_wipe.py, routers/pulse.py, routers/files.py</t>
+        </is>
+      </c>
+      <c r="C411" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D411" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E411" s="28" t="inlineStr">
+        <is>
+          <t>Wired in on day one</t>
+        </is>
+      </c>
+      <c r="F411" s="28" t="inlineStr">
+        <is>
+          <t>Router registered; indexes (tenant+created, requester, approver+status, status, unique number); 'requests' in the tenant wipe list; pulse watches it; a bill attached to a request opens for whoever may open the request; read-gate inventory and API-parity baseline (+10 routes) updated.</t>
+        </is>
+      </c>
+      <c r="G411" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H411" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I411" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K411" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L411" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.7</t>
+        </is>
+      </c>
+      <c r="B412" s="28" t="inlineStr">
+        <is>
+          <t>tests/test_staff_requests.py, tests/fake_mongo.py</t>
+        </is>
+      </c>
+      <c r="C412" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D412" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E412" s="28" t="inlineStr">
+        <is>
+          <t>31 tests: routing, access, money, ask-back, attachments</t>
+        </is>
+      </c>
+      <c r="F412" s="28" t="inlineStr">
+        <is>
+          <t>Manager default / owner choice / no-manager fallback, numbering per company, validation, owner auto-record; access 404s, no self-approval, owner and delegate decide; one expense under two simultaneous approvals, failed booking keeps the yes, company categories, equipment asset, reimbursement payee, fulfil -&gt; paid + stock, expense paid -&gt; request done, delete unlinks; reject needs a reason, question/answer, withdraw rules; own-files-only attachments. FakeDB gains $push and find_one_and_update.</t>
+        </is>
+      </c>
+      <c r="G412" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H412" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I412" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K412" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L412" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.8</t>
+        </is>
+      </c>
+      <c r="B413" s="28" t="inlineStr">
+        <is>
+          <t>components/requests/NewWorkMenu.jsx, pages/MyWork.js, pages/Tasks.js</t>
+        </is>
+      </c>
+      <c r="C413" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D413" s="28" t="inlineStr">
+        <is>
+          <t>My Work</t>
+        </is>
+      </c>
+      <c r="E413" s="28" t="inlineStr">
+        <is>
+          <t>The + asks: New task or New request</t>
+        </is>
+      </c>
+      <c r="F413" s="28" t="inlineStr">
+        <is>
+          <t>My Work's + (phone circle and desktop '+ New') opens a glass menu with the two choices, the CRM add-menu pattern. NewTaskDialog gains a controlled mode (open / hideTrigger) so the menu can open it.</t>
+        </is>
+      </c>
+      <c r="G413" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H413" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I413" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K413" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L413" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.9</t>
+        </is>
+      </c>
+      <c r="B414" s="28" t="inlineStr">
+        <is>
+          <t>components/requests/NewRequestDialog.jsx, lib/requests.js</t>
+        </is>
+      </c>
+      <c r="C414" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D414" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E414" s="28" t="inlineStr">
+        <is>
+          <t>New request form</t>
+        </is>
+      </c>
+      <c r="F414" s="28" t="inlineStr">
+        <is>
+          <t>Type chips; many items with quantity / unit / amount and a live total; needed-by date; bill or photo attached; why it is needed; Send to: reporting manager (default) or owner, with the no-manager and owner-records-it cases said up front. Words kept as a draft. Same sheet shape as New Task.</t>
+        </is>
+      </c>
+      <c r="G414" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H414" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I414" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K414" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L414" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.10</t>
+        </is>
+      </c>
+      <c r="B415" s="28" t="inlineStr">
+        <is>
+          <t>components/requests/RequestCard.jsx</t>
+        </is>
+      </c>
+      <c r="C415" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D415" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E415" s="28" t="inlineStr">
+        <is>
+          <t>The request card</t>
+        </is>
+      </c>
+      <c r="F415" s="28" t="inlineStr">
+        <is>
+          <t>Status and type chips, number, total, items, reason, files, question and answer together, reject reason, where the money is (in Finance / paid / in stock / why not), history timeline; Approve / Reject / Ask, Send answer, Withdraw and Mark paid shown from the server's can-flags.</t>
+        </is>
+      </c>
+      <c r="G415" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H415" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I415" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K415" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L415" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.11</t>
+        </is>
+      </c>
+      <c r="B416" s="28" t="inlineStr">
+        <is>
+          <t>pages/Requests.js, components/requests/RequestsPanel.jsx, pages/MyWork.js</t>
+        </is>
+      </c>
+      <c r="C416" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D416" s="28" t="inlineStr">
+        <is>
+          <t>Requests / My Work</t>
+        </is>
+      </c>
+      <c r="E416" s="28" t="inlineStr">
+        <is>
+          <t>Requests page and My requests in My Work</t>
+        </is>
+      </c>
+      <c r="F416" s="28" t="inlineStr">
+        <is>
+          <t>/requests: Mine, To approve, To pay, All (owner), summary, ?tab= and ?request= deep links. My Work gets a 'My requests' view (phone view picker and desktop segment) with its own + New.</t>
+        </is>
+      </c>
+      <c r="G416" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H416" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I416" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K416" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L416" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.12</t>
+        </is>
+      </c>
+      <c r="B417" s="28" t="inlineStr">
+        <is>
+          <t>pages/MyWork.js approvals hub, pages/Desk.js</t>
+        </is>
+      </c>
+      <c r="C417" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D417" s="28" t="inlineStr">
+        <is>
+          <t>Approvals / Desk</t>
+        </is>
+      </c>
+      <c r="E417" s="28" t="inlineStr">
+        <is>
+          <t>Approvals hub Requests tab and a Desk card</t>
+        </is>
+      </c>
+      <c r="F417" s="28" t="inlineStr">
+        <is>
+          <t>Approvals gets a Requests tab beside Tasks and Leave, counted in the number on the way in; the Desk's Watch column shows a Requests card when something waits on you.</t>
+        </is>
+      </c>
+      <c r="G417" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H417" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I417" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K417" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L417" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.13</t>
+        </is>
+      </c>
+      <c r="B418" s="28" t="inlineStr">
+        <is>
+          <t>components/mobile/AllAppsPanel.jsx, lib/notif.js, hooks/usePulse.js, App.js</t>
+        </is>
+      </c>
+      <c r="C418" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D418" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E418" s="28" t="inlineStr">
+        <is>
+          <t>Phone More tile, notification links, live refresh</t>
+        </is>
+      </c>
+      <c r="F418" s="28" t="inlineStr">
+        <is>
+          <t>More -&gt; Requests; a request notification opens the approver's queue, Finance's list to pay or the requester's own list on the card; pulse refreshes requests, the Desk and expenses.</t>
+        </is>
+      </c>
+      <c r="G418" s="28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H418" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I418" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K418" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L418" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.14</t>
+        </is>
+      </c>
+      <c r="B419" s="28" t="inlineStr">
+        <is>
+          <t>services/voice.py, Dex</t>
+        </is>
+      </c>
+      <c r="C419" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D419" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E419" s="28" t="inlineStr">
+        <is>
+          <t>Raise a request by voice through Dex</t>
+        </is>
+      </c>
+      <c r="F419" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3.</t>
+        </is>
+      </c>
+      <c r="G419" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H419" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I419" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K419" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3 (later) per the client plan - not in this build</t>
+        </is>
+      </c>
+      <c r="L419" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.15</t>
+        </is>
+      </c>
+      <c r="B420" s="28" t="inlineStr">
+        <is>
+          <t>services/ingestion.py</t>
+        </is>
+      </c>
+      <c r="C420" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D420" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E420" s="28" t="inlineStr">
+        <is>
+          <t>Reimbursement read from a bill photo</t>
+        </is>
+      </c>
+      <c r="F420" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3: fill the items and amount from the photographed bill.</t>
+        </is>
+      </c>
+      <c r="G420" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H420" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I420" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K420" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3 (later) per the client plan - not in this build</t>
+        </is>
+      </c>
+      <c r="L420" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.16</t>
+        </is>
+      </c>
+      <c r="B421" s="28" t="inlineStr">
+        <is>
+          <t>reports</t>
+        </is>
+      </c>
+      <c r="C421" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D421" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E421" s="28" t="inlineStr">
+        <is>
+          <t>Spend reports from requests</t>
+        </is>
+      </c>
+      <c r="F421" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3: who asked for what, approved and paid, by type and month.</t>
+        </is>
+      </c>
+      <c r="G421" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H421" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I421" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K421" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3 (later) per the client plan - not in this build</t>
+        </is>
+      </c>
+      <c r="L421" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.17</t>
+        </is>
+      </c>
+      <c r="B422" s="28" t="inlineStr">
+        <is>
+          <t>services/whatsapp.py</t>
+        </is>
+      </c>
+      <c r="C422" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D422" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E422" s="28" t="inlineStr">
+        <is>
+          <t>Requests on WhatsApp</t>
+        </is>
+      </c>
+      <c r="F422" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3: raise and approve from WhatsApp.</t>
+        </is>
+      </c>
+      <c r="G422" s="28" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H422" s="28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I422" s="28" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="K422" s="28" t="inlineStr">
+        <is>
+          <t>Phase 3 (later) per the client plan - not in this build</t>
+        </is>
+      </c>
+      <c r="L422" s="28" t="inlineStr">
+        <is>
+          <t>Client plan 2026-10-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="28" t="inlineStr">
+        <is>
+          <t>U7-26.18</t>
+        </is>
+      </c>
+      <c r="B423" s="28" t="inlineStr">
+        <is>
+          <t>services/staff_requests.py goes_to_finance, routers/staff_requests.py, components/requests/*</t>
+        </is>
+      </c>
+      <c r="C423" s="28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D423" s="28" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="E423" s="28" t="inlineStr">
+        <is>
+          <t>A General request is a yes, not money</t>
+        </is>
+      </c>
+      <c r="F423" s="28" t="inlineStr">
+        <is>
+          <t>Yokesh 2026-10-21: General is not financial. No amount on the form (any sent are dropped); approval closes it - no expense booked, Finance not told, never in To pay and cannot open it, Mark paid refused (409). The card reads 'Approved' and sits with the closed ones; the owner's own General request is recorded with no money. 3 tests.</t>
+        </is>
+      </c>
+      <c r="G423" s="28" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H423" s="28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I423" s="28" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K423" s="28" t="inlineStr">
+        <is>
+          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
+        </is>
+      </c>
+      <c r="L423" s="28" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-21</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
+++ b/docs/DecisionOS_Epic6_UX_UI_Optimization.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -619,7 +619,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -644,7 +643,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -657,7 +655,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -670,7 +667,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
@@ -683,7 +679,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -691,7 +686,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
@@ -735,7 +729,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
@@ -779,7 +772,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
@@ -823,7 +815,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
@@ -867,7 +858,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
@@ -911,7 +901,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
@@ -955,7 +944,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
@@ -999,7 +987,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
@@ -1043,7 +1030,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
@@ -1087,7 +1073,6 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
@@ -1131,7 +1116,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
@@ -1175,7 +1159,6 @@
         </is>
       </c>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
@@ -1219,7 +1202,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
@@ -1263,7 +1245,6 @@
         </is>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
@@ -1307,7 +1288,6 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
@@ -1351,7 +1331,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
@@ -1395,7 +1374,6 @@
         </is>
       </c>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
@@ -1439,7 +1417,6 @@
         </is>
       </c>
     </row>
-    <row r="99"/>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
@@ -1483,7 +1460,6 @@
         </is>
       </c>
     </row>
-    <row r="104"/>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
@@ -1527,7 +1503,6 @@
         </is>
       </c>
     </row>
-    <row r="109"/>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
@@ -1568,50 +1543,6 @@
       <c r="B113" t="inlineStr">
         <is>
           <t>In progress -- 12 of 13 Done; open: Phase 5 capture feedback</t>
-        </is>
-      </c>
-    </row>
-    <row r="114"/>
-    <row r="115">
-      <c r="A115" s="4" t="inlineStr">
-        <is>
-          <t>Sprint 26 -- Requests (raise, approve, book the expense)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Files</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>services/staff_requests.py, routers/staff_requests.py, components/requests/*, pages/Requests.js, pages/MyWork.js</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Employees had no way to ask for material, money or equipment and get a yes that reached Finance; it happened by word of mouth and the expense was typed again by hand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>In progress -- 14 of 18 Done; open: Phase 3 (voice via Dex, bill-photo reading, reports, WhatsApp)</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1655,7 +1586,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Epic 6 progress: 315 of 421 items Done  (75%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 59 of 64 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.  Sprint 26 (Requests) added 2026-10-21: 14 of 18 Done.</t>
+          <t>Epic 6 progress: 301 of 403 items Done  (75%).  7 items removed as obsolete after the karma redesign (logged with reasons in the 'Dropped (karma)' sheet).  UI rebuild recorded in the 'UI Redesign Log' sheet.  Backlog validated screen-by-screen vs the new UI on 2026-08-20.  Sprint 21 (My Work task management) added 2026-09-15: 14 of 16 Done.  Sprint 22 (Decision Desk decision flow) added 2026-09-15: 16 of 18 Done.  Sprint 23 (Settings, Team and access) added 2026-09-15: 59 of 64 Done.  Sprint 24 (Onboarding + auth) added 2026-09-17: 32 of 38 Done.  Sprint 25 (Workflows + tasks) added 2026-09-21: 80 of 88 Done.</t>
         </is>
       </c>
     </row>
@@ -2530,39 +2461,6 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>Added 2026-09-21 after auditing the workflow + task sections from the Desk (docs/WORKFLOW_OPERATIONS_PLAN.md). The engine was real — stage gates, auto-advance, evidence, escalation — and the HUMAN half was missing: a person could not attach a task to a workflow, move a due date, repeat work or see more than one stage's slice. 19 items across continuity, control, visibility and continuous operations. A multi-user run (four people, two industries) found stage work going to nobody (departments never matched) — fixed — plus three findings for the founder. A 26-step walk by hand in the browser (3 people, real log-outs) fixed three more and logged the rest (docs/BROWSER_SCENARIOS_0921.md). The routines promised at sign-up are now confirmed once and repeat (U7-25.25). 2026-09-22: the workflow gets a clock — stage durations date the stage's work, stuck cards are reported, cards can carry a target date with a forecast, and the card shows planned vs actual per stage; the Desk's Delayed and Workflows tiles read it (U7-25.26–29).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sprint 26</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Requests (raise, approve, book the expense)</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>14</v>
-      </c>
-      <c r="D31" t="n">
-        <v>18</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Added 2026-10-21 from the client's Requests plan (docs/REQUESTS_PLAN.md): employees raise a request with one or many items, send it to their reporting manager (default) or the owner, approval books the expense in Finance, Finance marks it paid and purchases go into stock. Web first; Phase 3 (voice via Dex, bill-photo reading, reports, WhatsApp) is later. General requests are not financial: approval closes them, nothing goes to Finance.</t>
         </is>
       </c>
     </row>
@@ -6149,7 +6047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L423"/>
+  <dimension ref="A1:L405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -29017,996 +28915,6 @@
       <c r="L405" t="inlineStr">
         <is>
           <t>Yokesh 2026-10-05 (check the settings page in mobile view)</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.1</t>
-        </is>
-      </c>
-      <c r="B406" s="28" t="inlineStr">
-        <is>
-          <t>services/staff_requests.py, models/staff_requests.py</t>
-        </is>
-      </c>
-      <c r="C406" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D406" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E406" s="28" t="inlineStr">
-        <is>
-          <t>The rules: seven types, approver choice, who may read / decide / fulfil</t>
-        </is>
-      </c>
-      <c r="F406" s="28" t="inlineStr">
-        <is>
-          <t>Types (Purchase &amp; materials, Expense reimbursement, Advance, Travel, Equipment &amp; assets, Repairs &amp; services, General) with their expense-category hint; approver = the requester's choice, reporting manager by default or the owner, no amount rule; no manager falls to the owner and says so; an owner's own request is recorded approved. Access: requester, approver or delegate, owner, Finance once approved; everyone else 404.</t>
-        </is>
-      </c>
-      <c r="G406" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H406" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I406" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K406" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L406" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.2</t>
-        </is>
-      </c>
-      <c r="B407" s="28" t="inlineStr">
-        <is>
-          <t>routers/staff_requests.py</t>
-        </is>
-      </c>
-      <c r="C407" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D407" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E407" s="28" t="inlineStr">
-        <is>
-          <t>The HTTP surface, every state change an atomic claim</t>
-        </is>
-      </c>
-      <c r="F407" s="28" t="inlineStr">
-        <is>
-          <t>GET /api/requests?view=mine|approvals|fulfil|all, GET approver-options, GET one; POST create, approve, reject (reason required), request-info, respond, withdraw, fulfil. Each update names the status it moves from, so two Approves make one approval and one expense; REQ-0001 numbering is one atomic increment per company with a unique index behind it.</t>
-        </is>
-      </c>
-      <c r="G407" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H407" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I407" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K407" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L407" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.3</t>
-        </is>
-      </c>
-      <c r="B408" s="28" t="inlineStr">
-        <is>
-          <t>routers/staff_requests.py _book_expense, routers/ledger.py create_expense</t>
-        </is>
-      </c>
-      <c r="C408" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D408" s="28" t="inlineStr">
-        <is>
-          <t>Requests / Finance</t>
-        </is>
-      </c>
-      <c r="E408" s="28" t="inlineStr">
-        <is>
-          <t>Approval books the expense in Finance</t>
-        </is>
-      </c>
-      <c r="F408" s="28" t="inlineStr">
-        <is>
-          <t>create_expense(source='request', request_id); the category is found in the company's own words (Raw Materials, Machine Maintenance) before the keyword guess; equipment books Asset Purchase so the asset register gets it; a reimbursement names the employee as payee. A failed booking keeps the approval and says so on the request.</t>
-        </is>
-      </c>
-      <c r="G408" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H408" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I408" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K408" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L408" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.4</t>
-        </is>
-      </c>
-      <c r="B409" s="28" t="inlineStr">
-        <is>
-          <t>routers/staff_requests.py fulfil, routers/ledger.py update_expense / delete_expense</t>
-        </is>
-      </c>
-      <c r="C409" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D409" s="28" t="inlineStr">
-        <is>
-          <t>Requests / Finance</t>
-        </is>
-      </c>
-      <c r="E409" s="28" t="inlineStr">
-        <is>
-          <t>Finance closes it: paid, and purchases into stock</t>
-        </is>
-      </c>
-      <c r="F409" s="28" t="inlineStr">
-        <is>
-          <t>Mark paid marks the booked expense paid and can put purchase items with a quantity into inventory (unit cost = line amount / quantity). Paying the expense in Finance closes the request on its own; deleting it unlinks the request and says why.</t>
-        </is>
-      </c>
-      <c r="G409" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H409" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I409" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K409" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L409" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.5</t>
-        </is>
-      </c>
-      <c r="B410" s="28" t="inlineStr">
-        <is>
-          <t>services/notifications.py, routers/staff_requests.py</t>
-        </is>
-      </c>
-      <c r="C410" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D410" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E410" s="28" t="inlineStr">
-        <is>
-          <t>Told at every step</t>
-        </is>
-      </c>
-      <c r="F410" s="28" t="inlineStr">
-        <is>
-          <t>Approver (and delegates) on a new request and an answer; requester on approve / reject / question / done; Finance and owners when something is approved to pay; approver when a request is withdrawn. Push titles: Request declined, Request withdrawn.</t>
-        </is>
-      </c>
-      <c r="G410" s="28" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H410" s="28" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I410" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K410" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L410" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.6</t>
-        </is>
-      </c>
-      <c r="B411" s="28" t="inlineStr">
-        <is>
-          <t>bootstrap/routing.py, bootstrap/lifecycle.py, services/tenant_wipe.py, routers/pulse.py, routers/files.py</t>
-        </is>
-      </c>
-      <c r="C411" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D411" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E411" s="28" t="inlineStr">
-        <is>
-          <t>Wired in on day one</t>
-        </is>
-      </c>
-      <c r="F411" s="28" t="inlineStr">
-        <is>
-          <t>Router registered; indexes (tenant+created, requester, approver+status, status, unique number); 'requests' in the tenant wipe list; pulse watches it; a bill attached to a request opens for whoever may open the request; read-gate inventory and API-parity baseline (+10 routes) updated.</t>
-        </is>
-      </c>
-      <c r="G411" s="28" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H411" s="28" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I411" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K411" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L411" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.7</t>
-        </is>
-      </c>
-      <c r="B412" s="28" t="inlineStr">
-        <is>
-          <t>tests/test_staff_requests.py, tests/fake_mongo.py</t>
-        </is>
-      </c>
-      <c r="C412" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D412" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E412" s="28" t="inlineStr">
-        <is>
-          <t>31 tests: routing, access, money, ask-back, attachments</t>
-        </is>
-      </c>
-      <c r="F412" s="28" t="inlineStr">
-        <is>
-          <t>Manager default / owner choice / no-manager fallback, numbering per company, validation, owner auto-record; access 404s, no self-approval, owner and delegate decide; one expense under two simultaneous approvals, failed booking keeps the yes, company categories, equipment asset, reimbursement payee, fulfil -&gt; paid + stock, expense paid -&gt; request done, delete unlinks; reject needs a reason, question/answer, withdraw rules; own-files-only attachments. FakeDB gains $push and find_one_and_update.</t>
-        </is>
-      </c>
-      <c r="G412" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H412" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I412" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K412" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L412" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.8</t>
-        </is>
-      </c>
-      <c r="B413" s="28" t="inlineStr">
-        <is>
-          <t>components/requests/NewWorkMenu.jsx, pages/MyWork.js, pages/Tasks.js</t>
-        </is>
-      </c>
-      <c r="C413" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D413" s="28" t="inlineStr">
-        <is>
-          <t>My Work</t>
-        </is>
-      </c>
-      <c r="E413" s="28" t="inlineStr">
-        <is>
-          <t>The + asks: New task or New request</t>
-        </is>
-      </c>
-      <c r="F413" s="28" t="inlineStr">
-        <is>
-          <t>My Work's + (phone circle and desktop '+ New') opens a glass menu with the two choices, the CRM add-menu pattern. NewTaskDialog gains a controlled mode (open / hideTrigger) so the menu can open it.</t>
-        </is>
-      </c>
-      <c r="G413" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H413" s="28" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I413" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K413" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L413" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.9</t>
-        </is>
-      </c>
-      <c r="B414" s="28" t="inlineStr">
-        <is>
-          <t>components/requests/NewRequestDialog.jsx, lib/requests.js</t>
-        </is>
-      </c>
-      <c r="C414" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D414" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E414" s="28" t="inlineStr">
-        <is>
-          <t>New request form</t>
-        </is>
-      </c>
-      <c r="F414" s="28" t="inlineStr">
-        <is>
-          <t>Type chips; many items with quantity / unit / amount and a live total; needed-by date; bill or photo attached; why it is needed; Send to: reporting manager (default) or owner, with the no-manager and owner-records-it cases said up front. Words kept as a draft. Same sheet shape as New Task.</t>
-        </is>
-      </c>
-      <c r="G414" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H414" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I414" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K414" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L414" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.10</t>
-        </is>
-      </c>
-      <c r="B415" s="28" t="inlineStr">
-        <is>
-          <t>components/requests/RequestCard.jsx</t>
-        </is>
-      </c>
-      <c r="C415" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D415" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E415" s="28" t="inlineStr">
-        <is>
-          <t>The request card</t>
-        </is>
-      </c>
-      <c r="F415" s="28" t="inlineStr">
-        <is>
-          <t>Status and type chips, number, total, items, reason, files, question and answer together, reject reason, where the money is (in Finance / paid / in stock / why not), history timeline; Approve / Reject / Ask, Send answer, Withdraw and Mark paid shown from the server's can-flags.</t>
-        </is>
-      </c>
-      <c r="G415" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H415" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I415" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K415" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L415" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.11</t>
-        </is>
-      </c>
-      <c r="B416" s="28" t="inlineStr">
-        <is>
-          <t>pages/Requests.js, components/requests/RequestsPanel.jsx, pages/MyWork.js</t>
-        </is>
-      </c>
-      <c r="C416" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D416" s="28" t="inlineStr">
-        <is>
-          <t>Requests / My Work</t>
-        </is>
-      </c>
-      <c r="E416" s="28" t="inlineStr">
-        <is>
-          <t>Requests page and My requests in My Work</t>
-        </is>
-      </c>
-      <c r="F416" s="28" t="inlineStr">
-        <is>
-          <t>/requests: Mine, To approve, To pay, All (owner), summary, ?tab= and ?request= deep links. My Work gets a 'My requests' view (phone view picker and desktop segment) with its own + New.</t>
-        </is>
-      </c>
-      <c r="G416" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H416" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I416" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K416" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L416" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.12</t>
-        </is>
-      </c>
-      <c r="B417" s="28" t="inlineStr">
-        <is>
-          <t>pages/MyWork.js approvals hub, pages/Desk.js</t>
-        </is>
-      </c>
-      <c r="C417" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D417" s="28" t="inlineStr">
-        <is>
-          <t>Approvals / Desk</t>
-        </is>
-      </c>
-      <c r="E417" s="28" t="inlineStr">
-        <is>
-          <t>Approvals hub Requests tab and a Desk card</t>
-        </is>
-      </c>
-      <c r="F417" s="28" t="inlineStr">
-        <is>
-          <t>Approvals gets a Requests tab beside Tasks and Leave, counted in the number on the way in; the Desk's Watch column shows a Requests card when something waits on you.</t>
-        </is>
-      </c>
-      <c r="G417" s="28" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H417" s="28" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I417" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K417" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L417" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.13</t>
-        </is>
-      </c>
-      <c r="B418" s="28" t="inlineStr">
-        <is>
-          <t>components/mobile/AllAppsPanel.jsx, lib/notif.js, hooks/usePulse.js, App.js</t>
-        </is>
-      </c>
-      <c r="C418" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D418" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E418" s="28" t="inlineStr">
-        <is>
-          <t>Phone More tile, notification links, live refresh</t>
-        </is>
-      </c>
-      <c r="F418" s="28" t="inlineStr">
-        <is>
-          <t>More -&gt; Requests; a request notification opens the approver's queue, Finance's list to pay or the requester's own list on the card; pulse refreshes requests, the Desk and expenses.</t>
-        </is>
-      </c>
-      <c r="G418" s="28" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="H418" s="28" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I418" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K418" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L418" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.14</t>
-        </is>
-      </c>
-      <c r="B419" s="28" t="inlineStr">
-        <is>
-          <t>services/voice.py, Dex</t>
-        </is>
-      </c>
-      <c r="C419" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D419" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E419" s="28" t="inlineStr">
-        <is>
-          <t>Raise a request by voice through Dex</t>
-        </is>
-      </c>
-      <c r="F419" s="28" t="inlineStr">
-        <is>
-          <t>Phase 3.</t>
-        </is>
-      </c>
-      <c r="G419" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H419" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I419" s="28" t="inlineStr">
-        <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="K419" s="28" t="inlineStr">
-        <is>
-          <t>Phase 3 (later) per the client plan - not in this build</t>
-        </is>
-      </c>
-      <c r="L419" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.15</t>
-        </is>
-      </c>
-      <c r="B420" s="28" t="inlineStr">
-        <is>
-          <t>services/ingestion.py</t>
-        </is>
-      </c>
-      <c r="C420" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D420" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E420" s="28" t="inlineStr">
-        <is>
-          <t>Reimbursement read from a bill photo</t>
-        </is>
-      </c>
-      <c r="F420" s="28" t="inlineStr">
-        <is>
-          <t>Phase 3: fill the items and amount from the photographed bill.</t>
-        </is>
-      </c>
-      <c r="G420" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H420" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I420" s="28" t="inlineStr">
-        <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="K420" s="28" t="inlineStr">
-        <is>
-          <t>Phase 3 (later) per the client plan - not in this build</t>
-        </is>
-      </c>
-      <c r="L420" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.16</t>
-        </is>
-      </c>
-      <c r="B421" s="28" t="inlineStr">
-        <is>
-          <t>reports</t>
-        </is>
-      </c>
-      <c r="C421" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D421" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E421" s="28" t="inlineStr">
-        <is>
-          <t>Spend reports from requests</t>
-        </is>
-      </c>
-      <c r="F421" s="28" t="inlineStr">
-        <is>
-          <t>Phase 3: who asked for what, approved and paid, by type and month.</t>
-        </is>
-      </c>
-      <c r="G421" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H421" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I421" s="28" t="inlineStr">
-        <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="K421" s="28" t="inlineStr">
-        <is>
-          <t>Phase 3 (later) per the client plan - not in this build</t>
-        </is>
-      </c>
-      <c r="L421" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.17</t>
-        </is>
-      </c>
-      <c r="B422" s="28" t="inlineStr">
-        <is>
-          <t>services/whatsapp.py</t>
-        </is>
-      </c>
-      <c r="C422" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D422" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E422" s="28" t="inlineStr">
-        <is>
-          <t>Requests on WhatsApp</t>
-        </is>
-      </c>
-      <c r="F422" s="28" t="inlineStr">
-        <is>
-          <t>Phase 3: raise and approve from WhatsApp.</t>
-        </is>
-      </c>
-      <c r="G422" s="28" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="H422" s="28" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I422" s="28" t="inlineStr">
-        <is>
-          <t>Backlog</t>
-        </is>
-      </c>
-      <c r="K422" s="28" t="inlineStr">
-        <is>
-          <t>Phase 3 (later) per the client plan - not in this build</t>
-        </is>
-      </c>
-      <c r="L422" s="28" t="inlineStr">
-        <is>
-          <t>Client plan 2026-10-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" s="28" t="inlineStr">
-        <is>
-          <t>U7-26.18</t>
-        </is>
-      </c>
-      <c r="B423" s="28" t="inlineStr">
-        <is>
-          <t>services/staff_requests.py goes_to_finance, routers/staff_requests.py, components/requests/*</t>
-        </is>
-      </c>
-      <c r="C423" s="28" t="n">
-        <v>26</v>
-      </c>
-      <c r="D423" s="28" t="inlineStr">
-        <is>
-          <t>Requests</t>
-        </is>
-      </c>
-      <c r="E423" s="28" t="inlineStr">
-        <is>
-          <t>A General request is a yes, not money</t>
-        </is>
-      </c>
-      <c r="F423" s="28" t="inlineStr">
-        <is>
-          <t>Yokesh 2026-10-21: General is not financial. No amount on the form (any sent are dropped); approval closes it - no expense booked, Finance not told, never in To pay and cannot open it, Mark paid refused (409). The card reads 'Approved' and sits with the closed ones; the owner's own General request is recorded with no money. 3 tests.</t>
-        </is>
-      </c>
-      <c r="G423" s="28" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="H423" s="28" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="I423" s="28" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K423" s="28" t="inlineStr">
-        <is>
-          <t>Done 2026-10-21 (awaiting push). docs/REQUESTS_PLAN.md</t>
-        </is>
-      </c>
-      <c r="L423" s="28" t="inlineStr">
-        <is>
-          <t>Founder 2026-10-21</t>
         </is>
       </c>
     </row>
